--- a/docs/SLMS2026_import_matrix_dot2.xlsx
+++ b/docs/SLMS2026_import_matrix_dot2.xlsx
@@ -404,9 +404,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
-  <cols>
-    <col min="1" max="1" width="41.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -443,17 +440,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I15"/>
-  <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -804,11 +790,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C22"/>
-  <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1014,11 +995,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C9"/>
-  <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="23.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1129,15 +1105,6 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G13"/>
-  <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="24.83203125" customWidth="1"/>
-    <col min="5" max="5" width="17.83203125" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1448,13 +1415,6 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E11"/>
-  <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="23.83203125" customWidth="1"/>
-    <col min="3" max="3" width="24.83203125" customWidth="1"/>
-    <col min="4" max="4" width="25.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1652,20 +1612,21 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:M11"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="17.83203125" customWidth="1"/>
-    <col min="4" max="4" width="24.83203125" customWidth="1"/>
-    <col min="5" max="5" width="23.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
-    <col min="8" max="8" width="17.83203125" customWidth="1"/>
-    <col min="9" max="9" width="21.83203125" customWidth="1"/>
-    <col min="10" max="10" width="25.83203125" customWidth="1"/>
-    <col min="11" max="11" width="21.83203125" customWidth="1"/>
-    <col min="12" max="12" width="19.83203125" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
+    <col min="5" max="5" width="21.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" customWidth="1"/>
+    <col min="9" max="9" width="19.83203125" customWidth="1"/>
+    <col min="10" max="10" width="23.83203125" customWidth="1"/>
+    <col min="11" max="11" width="19.83203125" customWidth="1"/>
+    <col min="12" max="12" width="29.83203125" customWidth="1"/>
+    <col min="13" max="13" width="17.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1703,6 +1664,9 @@
         <v>Ngày hết bảo hành</v>
       </c>
       <c r="L1" t="str">
+        <v>Giá phạt hết bảo hành (VNĐ)</v>
+      </c>
+      <c r="M1" t="str">
         <v>Ghi chú lắp đặt</v>
       </c>
     </row>
@@ -1740,7 +1704,10 @@
       <c r="K2" t="str">
         <v>2028-04-30</v>
       </c>
-      <c r="L2" t="str">
+      <c r="L2">
+        <v>3000000</v>
+      </c>
+      <c r="M2" t="str">
         <v/>
       </c>
     </row>
@@ -1778,7 +1745,10 @@
       <c r="K3" t="str">
         <v>2028-04-30</v>
       </c>
-      <c r="L3" t="str">
+      <c r="L3">
+        <v>2000000</v>
+      </c>
+      <c r="M3" t="str">
         <v/>
       </c>
     </row>
@@ -1816,7 +1786,10 @@
       <c r="K4" t="str">
         <v>2029-05-31</v>
       </c>
-      <c r="L4" t="str">
+      <c r="L4">
+        <v>3500000</v>
+      </c>
+      <c r="M4" t="str">
         <v/>
       </c>
     </row>
@@ -1854,7 +1827,10 @@
       <c r="K5" t="str">
         <v>2027-05-31</v>
       </c>
-      <c r="L5" t="str">
+      <c r="L5">
+        <v>800000</v>
+      </c>
+      <c r="M5" t="str">
         <v/>
       </c>
     </row>
@@ -1892,7 +1868,10 @@
       <c r="K6" t="str">
         <v>2027-06-28</v>
       </c>
-      <c r="L6" t="str">
+      <c r="L6">
+        <v>1500000</v>
+      </c>
+      <c r="M6" t="str">
         <v>TB mới phòng 101</v>
       </c>
     </row>
@@ -1930,7 +1909,10 @@
       <c r="K7" t="str">
         <v>2028-06-28</v>
       </c>
-      <c r="L7" t="str">
+      <c r="L7">
+        <v>2500000</v>
+      </c>
+      <c r="M7" t="str">
         <v>TB mới phòng 102</v>
       </c>
     </row>
@@ -1968,7 +1950,10 @@
       <c r="K8" t="str">
         <v>2027-06-28</v>
       </c>
-      <c r="L8" t="str">
+      <c r="L8">
+        <v>700000</v>
+      </c>
+      <c r="M8" t="str">
         <v>TB mới phòng 103</v>
       </c>
     </row>
@@ -2006,7 +1991,10 @@
       <c r="K9" t="str">
         <v>2027-07-28</v>
       </c>
-      <c r="L9" t="str">
+      <c r="L9">
+        <v>1500000</v>
+      </c>
+      <c r="M9" t="str">
         <v>TB mới phòng 101</v>
       </c>
     </row>
@@ -2044,7 +2032,10 @@
       <c r="K10" t="str">
         <v>2028-07-28</v>
       </c>
-      <c r="L10" t="str">
+      <c r="L10">
+        <v>2500000</v>
+      </c>
+      <c r="M10" t="str">
         <v>TB mới phòng 102</v>
       </c>
     </row>
@@ -2082,13 +2073,16 @@
       <c r="K11" t="str">
         <v>2027-07-28</v>
       </c>
-      <c r="L11" t="str">
+      <c r="L11">
+        <v>700000</v>
+      </c>
+      <c r="M11" t="str">
         <v>TB mới phòng 103</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/SLMS2026_import_matrix_dot2.xlsx
+++ b/docs/SLMS2026_import_matrix_dot2.xlsx
@@ -403,11 +403,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
+  <cols>
+    <col min="1" max="1" width="50.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Hướng dẫn — Ma trận 8 TH RENO (đợt 2)</v>
+        <v>Hướng dẫn — Ma trận RENO + căn full NT (đợt 2)</v>
       </c>
     </row>
     <row r="2">
@@ -417,7 +420,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Chỉ import sau khi đã import đợt 1 (#3–#10).</v>
+        <v>Chỉ import sau khi đã import đợt 1 (các HĐ RENO).</v>
       </c>
     </row>
     <row r="4">
@@ -430,16 +433,32 @@
         <v>Sheet "0. Ma_Tran_Onboarding": đối chiếu từng HĐ.</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>#12 NGUYEN_CAN full NT khu vực chung | #13–#14 mỗi phòng Quạt+Giường.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I20"/>
+  <cols>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="16.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -761,28 +780,149 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
-        <v/>
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>HD-MTX-11-NORENO-FULL</v>
+      </c>
+      <c r="C12" t="str">
+        <v>NORENO</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E12" t="str">
+        <v>—</v>
+      </c>
+      <c r="F12" t="str">
+        <v>—</v>
+      </c>
+      <c r="G12" t="str">
+        <v>—</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Không</v>
+      </c>
+      <c r="I12" t="str">
+        <v>#11 NORENO | Nguyên căn full NT bàn giao | Đợt 2: —</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
-        <v>Tổng: 10 trường hợp onboarding hợp lệ (2 NORENO + 8 RENO).</v>
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>HD-MTX-12-RENO-WH-FULL</v>
+      </c>
+      <c r="C13" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E13" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Có</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I13" t="str">
+        <v>#12 RENO | NGUYEN_CAN full NT | TB bàn giao + cải tạo + TB mua khu vực chung</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>HD-MTX-13-RENO-RM-FULL</v>
+      </c>
+      <c r="C14" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Có</v>
+      </c>
+      <c r="E14" t="str">
+        <v>THEO_PHONG (4)</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Có</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I14" t="str">
+        <v>#13 RENO | THEO_PHONG (4) full NT | mỗi phòng 1 Quạt + 1 Giường (+ ĐH, nóng lạnh)</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>HD-MTX-14-RENO-RM-BEDFAN</v>
+      </c>
+      <c r="C15" t="str">
+        <v>RENO</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Không</v>
+      </c>
+      <c r="E15" t="str">
+        <v>THEO_PHONG (5)</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Có (≥1 dòng)</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Có</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Có</v>
+      </c>
+      <c r="I15" t="str">
+        <v>#14 RENO | THEO_PHONG (5) | mỗi phòng đúng 1 Quạt + 1 Giường</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Tổng: 14 HĐ onboarding (#1–#10 ma trận + #11–#14 nội thất đầy đủ).</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
         <v>NORENO: import đợt 1 xong → tự gửi Host. RENO: cần import đợt 2.</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="str">
+    <row r="19">
+      <c r="A19" t="str">
         <v>RENO bắt buộc ≥1 hạng mục cải tạo ở sheet 3 trước khi gửi Host.</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>#11–#14: demo full NT — nguyên căn / theo phòng (mỗi phòng ≥ 1 Quạt + 1 Giường).</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I20"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -790,6 +930,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C22"/>
+  <cols>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -994,7 +1139,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C12"/>
+  <cols>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="23.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1095,16 +1245,58 @@
         <v>3</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>HD-MTX-12-RENO-WH-FULL</v>
+      </c>
+      <c r="B10" t="str">
+        <v>NGUYEN_CAN</v>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>HD-MTX-13-RENO-RM-FULL</v>
+      </c>
+      <c r="B11" t="str">
+        <v>THEO_PHONG</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>HD-MTX-14-RENO-RM-BEDFAN</v>
+      </c>
+      <c r="B12" t="str">
+        <v>THEO_PHONG</v>
+      </c>
+      <c r="C12">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G22"/>
+  <cols>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="24.83203125" customWidth="1"/>
+    <col min="5" max="5" width="17.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1405,16 +1597,230 @@
         <v>Phòng 103</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>HD-MTX-13-RENO-RM-FULL</v>
+      </c>
+      <c r="B14" t="str">
+        <v>101</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>30</v>
+      </c>
+      <c r="E14">
+        <v>6.5</v>
+      </c>
+      <c r="F14">
+        <v>4.6</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Phòng 101</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>HD-MTX-13-RENO-RM-FULL</v>
+      </c>
+      <c r="B15" t="str">
+        <v>102</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>30</v>
+      </c>
+      <c r="E15">
+        <v>6.5</v>
+      </c>
+      <c r="F15">
+        <v>4.6</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Phòng 102</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>HD-MTX-13-RENO-RM-FULL</v>
+      </c>
+      <c r="B16" t="str">
+        <v>103</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>30</v>
+      </c>
+      <c r="E16">
+        <v>6.5</v>
+      </c>
+      <c r="F16">
+        <v>4.6</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Phòng 103</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>HD-MTX-13-RENO-RM-FULL</v>
+      </c>
+      <c r="B17" t="str">
+        <v>104</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>30</v>
+      </c>
+      <c r="E17">
+        <v>6.5</v>
+      </c>
+      <c r="F17">
+        <v>4.6</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Phòng 104</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>HD-MTX-14-RENO-RM-BEDFAN</v>
+      </c>
+      <c r="B18" t="str">
+        <v>101</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>18</v>
+      </c>
+      <c r="E18">
+        <v>5</v>
+      </c>
+      <c r="F18">
+        <v>3.6</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Phòng 101</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>HD-MTX-14-RENO-RM-BEDFAN</v>
+      </c>
+      <c r="B19" t="str">
+        <v>102</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>18</v>
+      </c>
+      <c r="E19">
+        <v>5</v>
+      </c>
+      <c r="F19">
+        <v>3.6</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Phòng 102</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>HD-MTX-14-RENO-RM-BEDFAN</v>
+      </c>
+      <c r="B20" t="str">
+        <v>103</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>18</v>
+      </c>
+      <c r="E20">
+        <v>5</v>
+      </c>
+      <c r="F20">
+        <v>3.6</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Phòng 103</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>HD-MTX-14-RENO-RM-BEDFAN</v>
+      </c>
+      <c r="B21" t="str">
+        <v>104</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>18</v>
+      </c>
+      <c r="E21">
+        <v>5</v>
+      </c>
+      <c r="F21">
+        <v>3.6</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Phòng 104</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>HD-MTX-14-RENO-RM-BEDFAN</v>
+      </c>
+      <c r="B22" t="str">
+        <v>105</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>18</v>
+      </c>
+      <c r="E22">
+        <v>5</v>
+      </c>
+      <c r="F22">
+        <v>3.6</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Phòng 105</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G22"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E19"/>
+  <cols>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="23.83203125" customWidth="1"/>
+    <col min="3" max="3" width="24.83203125" customWidth="1"/>
+    <col min="4" max="4" width="25.83203125" customWidth="1"/>
+    <col min="5" max="5" width="20.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1603,30 +2009,165 @@
         <v/>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>HD-MTX-12-RENO-WH-FULL</v>
+      </c>
+      <c r="B12" t="str">
+        <v>PAINTING</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Sơn sửa</v>
+      </c>
+      <c r="D12">
+        <v>12000000</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Sơn lại toàn bộ</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>HD-MTX-12-RENO-WH-FULL</v>
+      </c>
+      <c r="B13" t="str">
+        <v>FURNITURE</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Nội thất</v>
+      </c>
+      <c r="D13">
+        <v>5000000</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Lắp đặt NT mới</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>HD-MTX-12-RENO-WH-FULL</v>
+      </c>
+      <c r="B14" t="str">
+        <v>FLOORING</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Sàn nhà</v>
+      </c>
+      <c r="D14">
+        <v>18000000</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Lát gạch tầng trệt</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>HD-MTX-13-RENO-RM-FULL</v>
+      </c>
+      <c r="B15" t="str">
+        <v>PAINTING</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Sơn sửa</v>
+      </c>
+      <c r="D15">
+        <v>14000000</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Sơn 4 phòng</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>HD-MTX-13-RENO-RM-FULL</v>
+      </c>
+      <c r="B16" t="str">
+        <v>PLUMBING</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Điện nước</v>
+      </c>
+      <c r="D16">
+        <v>10000000</v>
+      </c>
+      <c r="E16" t="str">
+        <v>WC từng phòng</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>HD-MTX-13-RENO-RM-FULL</v>
+      </c>
+      <c r="B17" t="str">
+        <v>STRUCTURAL</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Kết cấu</v>
+      </c>
+      <c r="D17">
+        <v>20000000</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Ngăn phòng</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>HD-MTX-14-RENO-RM-BEDFAN</v>
+      </c>
+      <c r="B18" t="str">
+        <v>PAINTING</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Sơn sửa</v>
+      </c>
+      <c r="D18">
+        <v>11000000</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Sơn 5 phòng</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>HD-MTX-14-RENO-RM-BEDFAN</v>
+      </c>
+      <c r="B19" t="str">
+        <v>FURNITURE</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Nội thất</v>
+      </c>
+      <c r="D19">
+        <v>4000000</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Lắp giường quạt từng phòng</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E19"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:L47"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="21.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" customWidth="1"/>
-    <col min="9" max="9" width="19.83203125" customWidth="1"/>
-    <col min="10" max="10" width="23.83203125" customWidth="1"/>
-    <col min="11" max="11" width="19.83203125" customWidth="1"/>
-    <col min="12" max="12" width="29.83203125" customWidth="1"/>
-    <col min="13" max="13" width="17.83203125" customWidth="1"/>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" customWidth="1"/>
+    <col min="4" max="4" width="24.83203125" customWidth="1"/>
+    <col min="5" max="5" width="23.83203125" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="17.83203125" customWidth="1"/>
+    <col min="9" max="9" width="21.83203125" customWidth="1"/>
+    <col min="10" max="10" width="25.83203125" customWidth="1"/>
+    <col min="11" max="11" width="21.83203125" customWidth="1"/>
+    <col min="12" max="12" width="19.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1664,9 +2205,6 @@
         <v>Ngày hết bảo hành</v>
       </c>
       <c r="L1" t="str">
-        <v>Giá phạt hết bảo hành (VNĐ)</v>
-      </c>
-      <c r="M1" t="str">
         <v>Ghi chú lắp đặt</v>
       </c>
     </row>
@@ -1704,10 +2242,7 @@
       <c r="K2" t="str">
         <v>2028-04-30</v>
       </c>
-      <c r="L2">
-        <v>3000000</v>
-      </c>
-      <c r="M2" t="str">
+      <c r="L2" t="str">
         <v/>
       </c>
     </row>
@@ -1745,10 +2280,7 @@
       <c r="K3" t="str">
         <v>2028-04-30</v>
       </c>
-      <c r="L3">
-        <v>2000000</v>
-      </c>
-      <c r="M3" t="str">
+      <c r="L3" t="str">
         <v/>
       </c>
     </row>
@@ -1786,10 +2318,7 @@
       <c r="K4" t="str">
         <v>2029-05-31</v>
       </c>
-      <c r="L4">
-        <v>3500000</v>
-      </c>
-      <c r="M4" t="str">
+      <c r="L4" t="str">
         <v/>
       </c>
     </row>
@@ -1827,10 +2356,7 @@
       <c r="K5" t="str">
         <v>2027-05-31</v>
       </c>
-      <c r="L5">
-        <v>800000</v>
-      </c>
-      <c r="M5" t="str">
+      <c r="L5" t="str">
         <v/>
       </c>
     </row>
@@ -1868,10 +2394,7 @@
       <c r="K6" t="str">
         <v>2027-06-28</v>
       </c>
-      <c r="L6">
-        <v>1500000</v>
-      </c>
-      <c r="M6" t="str">
+      <c r="L6" t="str">
         <v>TB mới phòng 101</v>
       </c>
     </row>
@@ -1909,10 +2432,7 @@
       <c r="K7" t="str">
         <v>2028-06-28</v>
       </c>
-      <c r="L7">
-        <v>2500000</v>
-      </c>
-      <c r="M7" t="str">
+      <c r="L7" t="str">
         <v>TB mới phòng 102</v>
       </c>
     </row>
@@ -1950,10 +2470,7 @@
       <c r="K8" t="str">
         <v>2027-06-28</v>
       </c>
-      <c r="L8">
-        <v>700000</v>
-      </c>
-      <c r="M8" t="str">
+      <c r="L8" t="str">
         <v>TB mới phòng 103</v>
       </c>
     </row>
@@ -1991,10 +2508,7 @@
       <c r="K9" t="str">
         <v>2027-07-28</v>
       </c>
-      <c r="L9">
-        <v>1500000</v>
-      </c>
-      <c r="M9" t="str">
+      <c r="L9" t="str">
         <v>TB mới phòng 101</v>
       </c>
     </row>
@@ -2032,10 +2546,7 @@
       <c r="K10" t="str">
         <v>2028-07-28</v>
       </c>
-      <c r="L10">
-        <v>2500000</v>
-      </c>
-      <c r="M10" t="str">
+      <c r="L10" t="str">
         <v>TB mới phòng 102</v>
       </c>
     </row>
@@ -2073,16 +2584,1381 @@
       <c r="K11" t="str">
         <v>2027-07-28</v>
       </c>
-      <c r="L11">
-        <v>700000</v>
-      </c>
-      <c r="M11" t="str">
+      <c r="L11" t="str">
         <v>TB mới phòng 103</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>HD-MTX-12-RENO-WH-FULL</v>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v>LIVING_ROOM</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="E12" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F12" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>14000000</v>
+      </c>
+      <c r="I12">
+        <v>36</v>
+      </c>
+      <c r="J12" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="K12" t="str">
+        <v>2029-08-31</v>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>HD-MTX-12-RENO-WH-FULL</v>
+      </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v>LIVING_ROOM</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E13" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F13" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1200000</v>
+      </c>
+      <c r="I13">
+        <v>12</v>
+      </c>
+      <c r="J13" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="K13" t="str">
+        <v>2027-08-31</v>
+      </c>
+      <c r="L13" t="str">
+        <v>Quạt trần phòng khách</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>HD-MTX-12-RENO-WH-FULL</v>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v>LIVING_ROOM</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E14" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F14" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>5500000</v>
+      </c>
+      <c r="I14">
+        <v>12</v>
+      </c>
+      <c r="J14" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="K14" t="str">
+        <v>2027-08-31</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Giường phòng ngủ chính</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>HD-MTX-12-RENO-WH-FULL</v>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v>LIVING_ROOM</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E15" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F15" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>4800000</v>
+      </c>
+      <c r="I15">
+        <v>12</v>
+      </c>
+      <c r="J15" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="K15" t="str">
+        <v>2027-08-31</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Giường phòng ngủ 2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>HD-MTX-12-RENO-WH-FULL</v>
+      </c>
+      <c r="B16" t="str">
+        <v/>
+      </c>
+      <c r="C16" t="str">
+        <v>LIVING_ROOM</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E16" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F16" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>750000</v>
+      </c>
+      <c r="I16">
+        <v>12</v>
+      </c>
+      <c r="J16" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="K16" t="str">
+        <v>2027-08-31</v>
+      </c>
+      <c r="L16" t="str">
+        <v>Quạt phòng ngủ 1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>HD-MTX-12-RENO-WH-FULL</v>
+      </c>
+      <c r="B17" t="str">
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <v>LIVING_ROOM</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E17" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F17" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>750000</v>
+      </c>
+      <c r="I17">
+        <v>12</v>
+      </c>
+      <c r="J17" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="K17" t="str">
+        <v>2027-08-31</v>
+      </c>
+      <c r="L17" t="str">
+        <v>Quạt phòng ngủ 2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>HD-MTX-12-RENO-WH-FULL</v>
+      </c>
+      <c r="B18" t="str">
+        <v/>
+      </c>
+      <c r="C18" t="str">
+        <v>KITCHEN</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Tủ lạnh</v>
+      </c>
+      <c r="E18" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F18" t="str">
+        <v>THAY_THE</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>8500000</v>
+      </c>
+      <c r="I18">
+        <v>24</v>
+      </c>
+      <c r="J18" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="K18" t="str">
+        <v>2028-08-31</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Thay tủ cũ</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>HD-MTX-12-RENO-WH-FULL</v>
+      </c>
+      <c r="B19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <v>KITCHEN</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Máy giặt</v>
+      </c>
+      <c r="E19" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F19" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>9500000</v>
+      </c>
+      <c r="I19">
+        <v>24</v>
+      </c>
+      <c r="J19" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="K19" t="str">
+        <v>2028-08-31</v>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>HD-MTX-12-RENO-WH-FULL</v>
+      </c>
+      <c r="B20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v>BATHROOM</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="E20" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F20" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>3200000</v>
+      </c>
+      <c r="I20">
+        <v>12</v>
+      </c>
+      <c r="J20" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="K20" t="str">
+        <v>2027-08-31</v>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>HD-MTX-12-RENO-WH-FULL</v>
+      </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <v>BALCONY</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E21" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F21" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>650000</v>
+      </c>
+      <c r="I21">
+        <v>12</v>
+      </c>
+      <c r="J21" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="K21" t="str">
+        <v>2027-08-31</v>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>HD-MTX-13-RENO-RM-FULL</v>
+      </c>
+      <c r="B22" t="str">
+        <v>101</v>
+      </c>
+      <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E22" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F22" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>4500000</v>
+      </c>
+      <c r="I22">
+        <v>12</v>
+      </c>
+      <c r="J22" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="K22" t="str">
+        <v>2027-09-28</v>
+      </c>
+      <c r="L22" t="str">
+        <v>Giường phòng 101</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>HD-MTX-13-RENO-RM-FULL</v>
+      </c>
+      <c r="B23" t="str">
+        <v>101</v>
+      </c>
+      <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E23" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F23" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>800000</v>
+      </c>
+      <c r="I23">
+        <v>12</v>
+      </c>
+      <c r="J23" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="K23" t="str">
+        <v>2027-09-28</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Quạt phòng 101</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>HD-MTX-13-RENO-RM-FULL</v>
+      </c>
+      <c r="B24" t="str">
+        <v>101</v>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="E24" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F24" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>9200000</v>
+      </c>
+      <c r="I24">
+        <v>24</v>
+      </c>
+      <c r="J24" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="K24" t="str">
+        <v>2028-09-28</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Điều hòa phòng 101</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>HD-MTX-13-RENO-RM-FULL</v>
+      </c>
+      <c r="B25" t="str">
+        <v>101</v>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="E25" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F25" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>2600000</v>
+      </c>
+      <c r="I25">
+        <v>12</v>
+      </c>
+      <c r="J25" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="K25" t="str">
+        <v>2027-09-28</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Nóng lạnh phòng 101</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>HD-MTX-13-RENO-RM-FULL</v>
+      </c>
+      <c r="B26" t="str">
+        <v>102</v>
+      </c>
+      <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E26" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F26" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>4500000</v>
+      </c>
+      <c r="I26">
+        <v>12</v>
+      </c>
+      <c r="J26" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="K26" t="str">
+        <v>2027-09-28</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Giường phòng 102</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>HD-MTX-13-RENO-RM-FULL</v>
+      </c>
+      <c r="B27" t="str">
+        <v>102</v>
+      </c>
+      <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E27" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F27" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>800000</v>
+      </c>
+      <c r="I27">
+        <v>12</v>
+      </c>
+      <c r="J27" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="K27" t="str">
+        <v>2027-09-28</v>
+      </c>
+      <c r="L27" t="str">
+        <v>Quạt phòng 102</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>HD-MTX-13-RENO-RM-FULL</v>
+      </c>
+      <c r="B28" t="str">
+        <v>102</v>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="E28" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F28" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>9200000</v>
+      </c>
+      <c r="I28">
+        <v>24</v>
+      </c>
+      <c r="J28" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="K28" t="str">
+        <v>2028-09-28</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Điều hòa phòng 102</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>HD-MTX-13-RENO-RM-FULL</v>
+      </c>
+      <c r="B29" t="str">
+        <v>102</v>
+      </c>
+      <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="E29" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F29" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>2600000</v>
+      </c>
+      <c r="I29">
+        <v>12</v>
+      </c>
+      <c r="J29" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="K29" t="str">
+        <v>2027-09-28</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Nóng lạnh phòng 102</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>HD-MTX-13-RENO-RM-FULL</v>
+      </c>
+      <c r="B30" t="str">
+        <v>103</v>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E30" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F30" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>4500000</v>
+      </c>
+      <c r="I30">
+        <v>12</v>
+      </c>
+      <c r="J30" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="K30" t="str">
+        <v>2027-09-28</v>
+      </c>
+      <c r="L30" t="str">
+        <v>Giường phòng 103</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>HD-MTX-13-RENO-RM-FULL</v>
+      </c>
+      <c r="B31" t="str">
+        <v>103</v>
+      </c>
+      <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="D31" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E31" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F31" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>800000</v>
+      </c>
+      <c r="I31">
+        <v>12</v>
+      </c>
+      <c r="J31" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="K31" t="str">
+        <v>2027-09-28</v>
+      </c>
+      <c r="L31" t="str">
+        <v>Quạt phòng 103</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>HD-MTX-13-RENO-RM-FULL</v>
+      </c>
+      <c r="B32" t="str">
+        <v>103</v>
+      </c>
+      <c r="C32" t="str">
+        <v/>
+      </c>
+      <c r="D32" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="E32" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F32" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>9200000</v>
+      </c>
+      <c r="I32">
+        <v>24</v>
+      </c>
+      <c r="J32" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="K32" t="str">
+        <v>2028-09-28</v>
+      </c>
+      <c r="L32" t="str">
+        <v>Điều hòa phòng 103</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>HD-MTX-13-RENO-RM-FULL</v>
+      </c>
+      <c r="B33" t="str">
+        <v>103</v>
+      </c>
+      <c r="C33" t="str">
+        <v/>
+      </c>
+      <c r="D33" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="E33" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F33" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <v>2600000</v>
+      </c>
+      <c r="I33">
+        <v>12</v>
+      </c>
+      <c r="J33" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="K33" t="str">
+        <v>2027-09-28</v>
+      </c>
+      <c r="L33" t="str">
+        <v>Nóng lạnh phòng 103</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>HD-MTX-13-RENO-RM-FULL</v>
+      </c>
+      <c r="B34" t="str">
+        <v>104</v>
+      </c>
+      <c r="C34" t="str">
+        <v/>
+      </c>
+      <c r="D34" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E34" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F34" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34">
+        <v>4500000</v>
+      </c>
+      <c r="I34">
+        <v>12</v>
+      </c>
+      <c r="J34" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="K34" t="str">
+        <v>2027-09-28</v>
+      </c>
+      <c r="L34" t="str">
+        <v>Giường phòng 104</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>HD-MTX-13-RENO-RM-FULL</v>
+      </c>
+      <c r="B35" t="str">
+        <v>104</v>
+      </c>
+      <c r="C35" t="str">
+        <v/>
+      </c>
+      <c r="D35" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E35" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F35" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <v>800000</v>
+      </c>
+      <c r="I35">
+        <v>12</v>
+      </c>
+      <c r="J35" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="K35" t="str">
+        <v>2027-09-28</v>
+      </c>
+      <c r="L35" t="str">
+        <v>Quạt phòng 104</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>HD-MTX-13-RENO-RM-FULL</v>
+      </c>
+      <c r="B36" t="str">
+        <v>104</v>
+      </c>
+      <c r="C36" t="str">
+        <v/>
+      </c>
+      <c r="D36" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="E36" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F36" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36">
+        <v>9200000</v>
+      </c>
+      <c r="I36">
+        <v>24</v>
+      </c>
+      <c r="J36" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="K36" t="str">
+        <v>2028-09-28</v>
+      </c>
+      <c r="L36" t="str">
+        <v>Điều hòa phòng 104</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>HD-MTX-13-RENO-RM-FULL</v>
+      </c>
+      <c r="B37" t="str">
+        <v>104</v>
+      </c>
+      <c r="C37" t="str">
+        <v/>
+      </c>
+      <c r="D37" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="E37" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F37" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37">
+        <v>2600000</v>
+      </c>
+      <c r="I37">
+        <v>12</v>
+      </c>
+      <c r="J37" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="K37" t="str">
+        <v>2027-09-28</v>
+      </c>
+      <c r="L37" t="str">
+        <v>Nóng lạnh phòng 104</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>HD-MTX-14-RENO-RM-BEDFAN</v>
+      </c>
+      <c r="B38" t="str">
+        <v>101</v>
+      </c>
+      <c r="C38" t="str">
+        <v/>
+      </c>
+      <c r="D38" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E38" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F38" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+      <c r="H38">
+        <v>4200000</v>
+      </c>
+      <c r="I38">
+        <v>12</v>
+      </c>
+      <c r="J38" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="K38" t="str">
+        <v>2027-09-28</v>
+      </c>
+      <c r="L38" t="str">
+        <v>1 giường phòng 101</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>HD-MTX-14-RENO-RM-BEDFAN</v>
+      </c>
+      <c r="B39" t="str">
+        <v>101</v>
+      </c>
+      <c r="C39" t="str">
+        <v/>
+      </c>
+      <c r="D39" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E39" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F39" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39">
+        <v>750000</v>
+      </c>
+      <c r="I39">
+        <v>12</v>
+      </c>
+      <c r="J39" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="K39" t="str">
+        <v>2027-09-28</v>
+      </c>
+      <c r="L39" t="str">
+        <v>1 quạt phòng 101</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>HD-MTX-14-RENO-RM-BEDFAN</v>
+      </c>
+      <c r="B40" t="str">
+        <v>102</v>
+      </c>
+      <c r="C40" t="str">
+        <v/>
+      </c>
+      <c r="D40" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E40" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F40" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+      <c r="H40">
+        <v>4200000</v>
+      </c>
+      <c r="I40">
+        <v>12</v>
+      </c>
+      <c r="J40" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="K40" t="str">
+        <v>2027-09-28</v>
+      </c>
+      <c r="L40" t="str">
+        <v>1 giường phòng 102</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>HD-MTX-14-RENO-RM-BEDFAN</v>
+      </c>
+      <c r="B41" t="str">
+        <v>102</v>
+      </c>
+      <c r="C41" t="str">
+        <v/>
+      </c>
+      <c r="D41" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E41" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F41" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41">
+        <v>750000</v>
+      </c>
+      <c r="I41">
+        <v>12</v>
+      </c>
+      <c r="J41" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="K41" t="str">
+        <v>2027-09-28</v>
+      </c>
+      <c r="L41" t="str">
+        <v>1 quạt phòng 102</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>HD-MTX-14-RENO-RM-BEDFAN</v>
+      </c>
+      <c r="B42" t="str">
+        <v>103</v>
+      </c>
+      <c r="C42" t="str">
+        <v/>
+      </c>
+      <c r="D42" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E42" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F42" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+      <c r="H42">
+        <v>4200000</v>
+      </c>
+      <c r="I42">
+        <v>12</v>
+      </c>
+      <c r="J42" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="K42" t="str">
+        <v>2027-09-28</v>
+      </c>
+      <c r="L42" t="str">
+        <v>1 giường phòng 103</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>HD-MTX-14-RENO-RM-BEDFAN</v>
+      </c>
+      <c r="B43" t="str">
+        <v>103</v>
+      </c>
+      <c r="C43" t="str">
+        <v/>
+      </c>
+      <c r="D43" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E43" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F43" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+      <c r="H43">
+        <v>750000</v>
+      </c>
+      <c r="I43">
+        <v>12</v>
+      </c>
+      <c r="J43" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="K43" t="str">
+        <v>2027-09-28</v>
+      </c>
+      <c r="L43" t="str">
+        <v>1 quạt phòng 103</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>HD-MTX-14-RENO-RM-BEDFAN</v>
+      </c>
+      <c r="B44" t="str">
+        <v>104</v>
+      </c>
+      <c r="C44" t="str">
+        <v/>
+      </c>
+      <c r="D44" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E44" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F44" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44">
+        <v>4200000</v>
+      </c>
+      <c r="I44">
+        <v>12</v>
+      </c>
+      <c r="J44" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="K44" t="str">
+        <v>2027-09-28</v>
+      </c>
+      <c r="L44" t="str">
+        <v>1 giường phòng 104</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>HD-MTX-14-RENO-RM-BEDFAN</v>
+      </c>
+      <c r="B45" t="str">
+        <v>104</v>
+      </c>
+      <c r="C45" t="str">
+        <v/>
+      </c>
+      <c r="D45" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E45" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F45" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+      <c r="H45">
+        <v>750000</v>
+      </c>
+      <c r="I45">
+        <v>12</v>
+      </c>
+      <c r="J45" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="K45" t="str">
+        <v>2027-09-28</v>
+      </c>
+      <c r="L45" t="str">
+        <v>1 quạt phòng 104</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>HD-MTX-14-RENO-RM-BEDFAN</v>
+      </c>
+      <c r="B46" t="str">
+        <v>105</v>
+      </c>
+      <c r="C46" t="str">
+        <v/>
+      </c>
+      <c r="D46" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E46" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F46" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+      <c r="H46">
+        <v>4200000</v>
+      </c>
+      <c r="I46">
+        <v>12</v>
+      </c>
+      <c r="J46" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="K46" t="str">
+        <v>2027-09-28</v>
+      </c>
+      <c r="L46" t="str">
+        <v>1 giường phòng 105</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>HD-MTX-14-RENO-RM-BEDFAN</v>
+      </c>
+      <c r="B47" t="str">
+        <v>105</v>
+      </c>
+      <c r="C47" t="str">
+        <v/>
+      </c>
+      <c r="D47" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E47" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F47" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+      <c r="H47">
+        <v>750000</v>
+      </c>
+      <c r="I47">
+        <v>12</v>
+      </c>
+      <c r="J47" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="K47" t="str">
+        <v>2027-09-28</v>
+      </c>
+      <c r="L47" t="str">
+        <v>1 quạt phòng 105</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L47"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/SLMS2026_import_matrix_dot2.xlsx
+++ b/docs/SLMS2026_import_matrix_dot2.xlsx
@@ -2154,7 +2154,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:M47"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2167,7 +2167,8 @@
     <col min="9" max="9" width="21.83203125" customWidth="1"/>
     <col min="10" max="10" width="25.83203125" customWidth="1"/>
     <col min="11" max="11" width="21.83203125" customWidth="1"/>
-    <col min="12" max="12" width="19.83203125" customWidth="1"/>
+    <col min="12" max="12" width="31.83203125" customWidth="1"/>
+    <col min="13" max="13" width="19.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2205,6 +2206,9 @@
         <v>Ngày hết bảo hành</v>
       </c>
       <c r="L1" t="str">
+        <v>Giá phạt hết bảo hành (VNĐ)</v>
+      </c>
+      <c r="M1" t="str">
         <v>Ghi chú lắp đặt</v>
       </c>
     </row>
@@ -2242,7 +2246,10 @@
       <c r="K2" t="str">
         <v>2028-04-30</v>
       </c>
-      <c r="L2" t="str">
+      <c r="L2">
+        <v>3300000</v>
+      </c>
+      <c r="M2" t="str">
         <v/>
       </c>
     </row>
@@ -2280,7 +2287,10 @@
       <c r="K3" t="str">
         <v>2028-04-30</v>
       </c>
-      <c r="L3" t="str">
+      <c r="L3">
+        <v>2250000</v>
+      </c>
+      <c r="M3" t="str">
         <v/>
       </c>
     </row>
@@ -2318,7 +2328,10 @@
       <c r="K4" t="str">
         <v>2029-05-31</v>
       </c>
-      <c r="L4" t="str">
+      <c r="L4">
+        <v>3900000</v>
+      </c>
+      <c r="M4" t="str">
         <v/>
       </c>
     </row>
@@ -2356,7 +2369,10 @@
       <c r="K5" t="str">
         <v>2027-05-31</v>
       </c>
-      <c r="L5" t="str">
+      <c r="L5">
+        <v>840000</v>
+      </c>
+      <c r="M5" t="str">
         <v/>
       </c>
     </row>
@@ -2394,7 +2410,10 @@
       <c r="K6" t="str">
         <v>2027-06-28</v>
       </c>
-      <c r="L6" t="str">
+      <c r="L6">
+        <v>1200000</v>
+      </c>
+      <c r="M6" t="str">
         <v>TB mới phòng 101</v>
       </c>
     </row>
@@ -2432,7 +2451,10 @@
       <c r="K7" t="str">
         <v>2028-06-28</v>
       </c>
-      <c r="L7" t="str">
+      <c r="L7">
+        <v>2550000</v>
+      </c>
+      <c r="M7" t="str">
         <v>TB mới phòng 102</v>
       </c>
     </row>
@@ -2470,7 +2492,10 @@
       <c r="K8" t="str">
         <v>2027-06-28</v>
       </c>
-      <c r="L8" t="str">
+      <c r="L8">
+        <v>720000</v>
+      </c>
+      <c r="M8" t="str">
         <v>TB mới phòng 103</v>
       </c>
     </row>
@@ -2508,7 +2533,10 @@
       <c r="K9" t="str">
         <v>2027-07-28</v>
       </c>
-      <c r="L9" t="str">
+      <c r="L9">
+        <v>1200000</v>
+      </c>
+      <c r="M9" t="str">
         <v>TB mới phòng 101</v>
       </c>
     </row>
@@ -2546,7 +2574,10 @@
       <c r="K10" t="str">
         <v>2028-07-28</v>
       </c>
-      <c r="L10" t="str">
+      <c r="L10">
+        <v>2550000</v>
+      </c>
+      <c r="M10" t="str">
         <v>TB mới phòng 102</v>
       </c>
     </row>
@@ -2584,7 +2615,10 @@
       <c r="K11" t="str">
         <v>2027-07-28</v>
       </c>
-      <c r="L11" t="str">
+      <c r="L11">
+        <v>720000</v>
+      </c>
+      <c r="M11" t="str">
         <v>TB mới phòng 103</v>
       </c>
     </row>
@@ -2622,7 +2656,10 @@
       <c r="K12" t="str">
         <v>2029-08-31</v>
       </c>
-      <c r="L12" t="str">
+      <c r="L12">
+        <v>4200000</v>
+      </c>
+      <c r="M12" t="str">
         <v/>
       </c>
     </row>
@@ -2660,7 +2697,10 @@
       <c r="K13" t="str">
         <v>2027-08-31</v>
       </c>
-      <c r="L13" t="str">
+      <c r="L13">
+        <v>360000</v>
+      </c>
+      <c r="M13" t="str">
         <v>Quạt trần phòng khách</v>
       </c>
     </row>
@@ -2698,7 +2738,10 @@
       <c r="K14" t="str">
         <v>2027-08-31</v>
       </c>
-      <c r="L14" t="str">
+      <c r="L14">
+        <v>1650000</v>
+      </c>
+      <c r="M14" t="str">
         <v>Giường phòng ngủ chính</v>
       </c>
     </row>
@@ -2736,7 +2779,10 @@
       <c r="K15" t="str">
         <v>2027-08-31</v>
       </c>
-      <c r="L15" t="str">
+      <c r="L15">
+        <v>1440000</v>
+      </c>
+      <c r="M15" t="str">
         <v>Giường phòng ngủ 2</v>
       </c>
     </row>
@@ -2774,7 +2820,10 @@
       <c r="K16" t="str">
         <v>2027-08-31</v>
       </c>
-      <c r="L16" t="str">
+      <c r="L16">
+        <v>225000</v>
+      </c>
+      <c r="M16" t="str">
         <v>Quạt phòng ngủ 1</v>
       </c>
     </row>
@@ -2812,7 +2861,10 @@
       <c r="K17" t="str">
         <v>2027-08-31</v>
       </c>
-      <c r="L17" t="str">
+      <c r="L17">
+        <v>225000</v>
+      </c>
+      <c r="M17" t="str">
         <v>Quạt phòng ngủ 2</v>
       </c>
     </row>
@@ -2850,7 +2902,10 @@
       <c r="K18" t="str">
         <v>2028-08-31</v>
       </c>
-      <c r="L18" t="str">
+      <c r="L18">
+        <v>2550000</v>
+      </c>
+      <c r="M18" t="str">
         <v>Thay tủ cũ</v>
       </c>
     </row>
@@ -2888,7 +2943,10 @@
       <c r="K19" t="str">
         <v>2028-08-31</v>
       </c>
-      <c r="L19" t="str">
+      <c r="L19">
+        <v>2850000</v>
+      </c>
+      <c r="M19" t="str">
         <v/>
       </c>
     </row>
@@ -2926,7 +2984,10 @@
       <c r="K20" t="str">
         <v>2027-08-31</v>
       </c>
-      <c r="L20" t="str">
+      <c r="L20">
+        <v>960000</v>
+      </c>
+      <c r="M20" t="str">
         <v/>
       </c>
     </row>
@@ -2964,7 +3025,10 @@
       <c r="K21" t="str">
         <v>2027-08-31</v>
       </c>
-      <c r="L21" t="str">
+      <c r="L21">
+        <v>195000</v>
+      </c>
+      <c r="M21" t="str">
         <v/>
       </c>
     </row>
@@ -3002,7 +3066,10 @@
       <c r="K22" t="str">
         <v>2027-09-28</v>
       </c>
-      <c r="L22" t="str">
+      <c r="L22">
+        <v>1350000</v>
+      </c>
+      <c r="M22" t="str">
         <v>Giường phòng 101</v>
       </c>
     </row>
@@ -3040,7 +3107,10 @@
       <c r="K23" t="str">
         <v>2027-09-28</v>
       </c>
-      <c r="L23" t="str">
+      <c r="L23">
+        <v>240000</v>
+      </c>
+      <c r="M23" t="str">
         <v>Quạt phòng 101</v>
       </c>
     </row>
@@ -3078,7 +3148,10 @@
       <c r="K24" t="str">
         <v>2028-09-28</v>
       </c>
-      <c r="L24" t="str">
+      <c r="L24">
+        <v>2760000</v>
+      </c>
+      <c r="M24" t="str">
         <v>Điều hòa phòng 101</v>
       </c>
     </row>
@@ -3116,7 +3189,10 @@
       <c r="K25" t="str">
         <v>2027-09-28</v>
       </c>
-      <c r="L25" t="str">
+      <c r="L25">
+        <v>780000</v>
+      </c>
+      <c r="M25" t="str">
         <v>Nóng lạnh phòng 101</v>
       </c>
     </row>
@@ -3154,7 +3230,10 @@
       <c r="K26" t="str">
         <v>2027-09-28</v>
       </c>
-      <c r="L26" t="str">
+      <c r="L26">
+        <v>1350000</v>
+      </c>
+      <c r="M26" t="str">
         <v>Giường phòng 102</v>
       </c>
     </row>
@@ -3192,7 +3271,10 @@
       <c r="K27" t="str">
         <v>2027-09-28</v>
       </c>
-      <c r="L27" t="str">
+      <c r="L27">
+        <v>240000</v>
+      </c>
+      <c r="M27" t="str">
         <v>Quạt phòng 102</v>
       </c>
     </row>
@@ -3230,7 +3312,10 @@
       <c r="K28" t="str">
         <v>2028-09-28</v>
       </c>
-      <c r="L28" t="str">
+      <c r="L28">
+        <v>2760000</v>
+      </c>
+      <c r="M28" t="str">
         <v>Điều hòa phòng 102</v>
       </c>
     </row>
@@ -3268,7 +3353,10 @@
       <c r="K29" t="str">
         <v>2027-09-28</v>
       </c>
-      <c r="L29" t="str">
+      <c r="L29">
+        <v>780000</v>
+      </c>
+      <c r="M29" t="str">
         <v>Nóng lạnh phòng 102</v>
       </c>
     </row>
@@ -3306,7 +3394,10 @@
       <c r="K30" t="str">
         <v>2027-09-28</v>
       </c>
-      <c r="L30" t="str">
+      <c r="L30">
+        <v>1350000</v>
+      </c>
+      <c r="M30" t="str">
         <v>Giường phòng 103</v>
       </c>
     </row>
@@ -3344,7 +3435,10 @@
       <c r="K31" t="str">
         <v>2027-09-28</v>
       </c>
-      <c r="L31" t="str">
+      <c r="L31">
+        <v>240000</v>
+      </c>
+      <c r="M31" t="str">
         <v>Quạt phòng 103</v>
       </c>
     </row>
@@ -3382,7 +3476,10 @@
       <c r="K32" t="str">
         <v>2028-09-28</v>
       </c>
-      <c r="L32" t="str">
+      <c r="L32">
+        <v>2760000</v>
+      </c>
+      <c r="M32" t="str">
         <v>Điều hòa phòng 103</v>
       </c>
     </row>
@@ -3420,7 +3517,10 @@
       <c r="K33" t="str">
         <v>2027-09-28</v>
       </c>
-      <c r="L33" t="str">
+      <c r="L33">
+        <v>780000</v>
+      </c>
+      <c r="M33" t="str">
         <v>Nóng lạnh phòng 103</v>
       </c>
     </row>
@@ -3458,7 +3558,10 @@
       <c r="K34" t="str">
         <v>2027-09-28</v>
       </c>
-      <c r="L34" t="str">
+      <c r="L34">
+        <v>1350000</v>
+      </c>
+      <c r="M34" t="str">
         <v>Giường phòng 104</v>
       </c>
     </row>
@@ -3496,7 +3599,10 @@
       <c r="K35" t="str">
         <v>2027-09-28</v>
       </c>
-      <c r="L35" t="str">
+      <c r="L35">
+        <v>240000</v>
+      </c>
+      <c r="M35" t="str">
         <v>Quạt phòng 104</v>
       </c>
     </row>
@@ -3534,7 +3640,10 @@
       <c r="K36" t="str">
         <v>2028-09-28</v>
       </c>
-      <c r="L36" t="str">
+      <c r="L36">
+        <v>2760000</v>
+      </c>
+      <c r="M36" t="str">
         <v>Điều hòa phòng 104</v>
       </c>
     </row>
@@ -3572,7 +3681,10 @@
       <c r="K37" t="str">
         <v>2027-09-28</v>
       </c>
-      <c r="L37" t="str">
+      <c r="L37">
+        <v>780000</v>
+      </c>
+      <c r="M37" t="str">
         <v>Nóng lạnh phòng 104</v>
       </c>
     </row>
@@ -3610,7 +3722,10 @@
       <c r="K38" t="str">
         <v>2027-09-28</v>
       </c>
-      <c r="L38" t="str">
+      <c r="L38">
+        <v>1260000</v>
+      </c>
+      <c r="M38" t="str">
         <v>1 giường phòng 101</v>
       </c>
     </row>
@@ -3648,7 +3763,10 @@
       <c r="K39" t="str">
         <v>2027-09-28</v>
       </c>
-      <c r="L39" t="str">
+      <c r="L39">
+        <v>225000</v>
+      </c>
+      <c r="M39" t="str">
         <v>1 quạt phòng 101</v>
       </c>
     </row>
@@ -3686,7 +3804,10 @@
       <c r="K40" t="str">
         <v>2027-09-28</v>
       </c>
-      <c r="L40" t="str">
+      <c r="L40">
+        <v>1260000</v>
+      </c>
+      <c r="M40" t="str">
         <v>1 giường phòng 102</v>
       </c>
     </row>
@@ -3724,7 +3845,10 @@
       <c r="K41" t="str">
         <v>2027-09-28</v>
       </c>
-      <c r="L41" t="str">
+      <c r="L41">
+        <v>225000</v>
+      </c>
+      <c r="M41" t="str">
         <v>1 quạt phòng 102</v>
       </c>
     </row>
@@ -3762,7 +3886,10 @@
       <c r="K42" t="str">
         <v>2027-09-28</v>
       </c>
-      <c r="L42" t="str">
+      <c r="L42">
+        <v>1260000</v>
+      </c>
+      <c r="M42" t="str">
         <v>1 giường phòng 103</v>
       </c>
     </row>
@@ -3800,7 +3927,10 @@
       <c r="K43" t="str">
         <v>2027-09-28</v>
       </c>
-      <c r="L43" t="str">
+      <c r="L43">
+        <v>225000</v>
+      </c>
+      <c r="M43" t="str">
         <v>1 quạt phòng 103</v>
       </c>
     </row>
@@ -3838,7 +3968,10 @@
       <c r="K44" t="str">
         <v>2027-09-28</v>
       </c>
-      <c r="L44" t="str">
+      <c r="L44">
+        <v>1260000</v>
+      </c>
+      <c r="M44" t="str">
         <v>1 giường phòng 104</v>
       </c>
     </row>
@@ -3876,7 +4009,10 @@
       <c r="K45" t="str">
         <v>2027-09-28</v>
       </c>
-      <c r="L45" t="str">
+      <c r="L45">
+        <v>225000</v>
+      </c>
+      <c r="M45" t="str">
         <v>1 quạt phòng 104</v>
       </c>
     </row>
@@ -3914,7 +4050,10 @@
       <c r="K46" t="str">
         <v>2027-09-28</v>
       </c>
-      <c r="L46" t="str">
+      <c r="L46">
+        <v>1260000</v>
+      </c>
+      <c r="M46" t="str">
         <v>1 giường phòng 105</v>
       </c>
     </row>
@@ -3952,13 +4091,16 @@
       <c r="K47" t="str">
         <v>2027-09-28</v>
       </c>
-      <c r="L47" t="str">
+      <c r="L47">
+        <v>225000</v>
+      </c>
+      <c r="M47" t="str">
         <v>1 quạt phòng 105</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L47"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M47"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/SLMS2026_import_matrix_dot2.xlsx
+++ b/docs/SLMS2026_import_matrix_dot2.xlsx
@@ -404,9 +404,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A6"/>
-  <cols>
-    <col min="1" max="1" width="50.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -448,17 +445,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I20"/>
-  <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -930,11 +916,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C22"/>
-  <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1140,11 +1121,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C12"/>
-  <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="23.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1288,15 +1264,6 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G22"/>
-  <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="24.83203125" customWidth="1"/>
-    <col min="5" max="5" width="17.83203125" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1814,13 +1781,6 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E19"/>
-  <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="23.83203125" customWidth="1"/>
-    <col min="3" max="3" width="24.83203125" customWidth="1"/>
-    <col min="4" max="4" width="25.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2155,21 +2115,6 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M47"/>
-  <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="17.83203125" customWidth="1"/>
-    <col min="4" max="4" width="24.83203125" customWidth="1"/>
-    <col min="5" max="5" width="23.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
-    <col min="8" max="8" width="17.83203125" customWidth="1"/>
-    <col min="9" max="9" width="21.83203125" customWidth="1"/>
-    <col min="10" max="10" width="25.83203125" customWidth="1"/>
-    <col min="11" max="11" width="21.83203125" customWidth="1"/>
-    <col min="12" max="12" width="31.83203125" customWidth="1"/>
-    <col min="13" max="13" width="19.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2885,7 +2830,7 @@
         <v>NEW</v>
       </c>
       <c r="F18" t="str">
-        <v>THAY_THE</v>
+        <v>THEM_MOI</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -2906,7 +2851,7 @@
         <v>2550000</v>
       </c>
       <c r="M18" t="str">
-        <v>Thay tủ cũ</v>
+        <v>Mua tủ lạnh mới (bổ sung tủ bàn giao)</v>
       </c>
     </row>
     <row r="19">

--- a/docs/SLMS2026_import_matrix_dot2.xlsx
+++ b/docs/SLMS2026_import_matrix_dot2.xlsx
@@ -5251,7 +5251,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M145"/>
+  <dimension ref="A1:M190"/>
   <cols>
     <col min="1" max="1" width="17.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -5358,10 +5358,10 @@
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>KITCHEN</v>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D3" t="str">
-        <v>Tủ lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="E3" t="str">
         <v>NEW</v>
@@ -5373,27 +5373,27 @@
         <v>1</v>
       </c>
       <c r="H3">
-        <v>7500000</v>
+        <v>900000</v>
       </c>
       <c r="I3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J3" t="str">
         <v>2026-08-01</v>
       </c>
       <c r="K3" t="str">
-        <v>2028-08-01</v>
+        <v>2027-08-01</v>
       </c>
       <c r="L3">
-        <v>2250000</v>
+        <v>270000</v>
       </c>
       <c r="M3" t="str">
-        <v/>
+        <v>Quạt trần PK</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HD-MTX-23-RENO-WH-BASIC-BUY</v>
+        <v>HD-MTX-22-RENO-WH-BASIC-BUY</v>
       </c>
       <c r="B4" t="str">
         <v/>
@@ -5402,7 +5402,7 @@
         <v>LIVING_ROOM</v>
       </c>
       <c r="D4" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="E4" t="str">
         <v>NEW</v>
@@ -5414,36 +5414,36 @@
         <v>1</v>
       </c>
       <c r="H4">
-        <v>11000000</v>
+        <v>5000000</v>
       </c>
       <c r="I4">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J4" t="str">
-        <v>2026-09-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K4" t="str">
-        <v>2028-09-01</v>
+        <v>2027-08-01</v>
       </c>
       <c r="L4">
-        <v>3300000</v>
+        <v>1500000</v>
       </c>
       <c r="M4" t="str">
-        <v>ĐH phòng khách</v>
+        <v>Giường PN 1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HD-MTX-23-RENO-WH-BASIC-BUY</v>
+        <v>HD-MTX-22-RENO-WH-BASIC-BUY</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>KITCHEN</v>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D5" t="str">
-        <v>Tủ lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="E5" t="str">
         <v>NEW</v>
@@ -5455,36 +5455,36 @@
         <v>1</v>
       </c>
       <c r="H5">
-        <v>7500000</v>
+        <v>4200000</v>
       </c>
       <c r="I5">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J5" t="str">
-        <v>2026-09-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K5" t="str">
-        <v>2028-09-01</v>
+        <v>2027-08-01</v>
       </c>
       <c r="L5">
-        <v>2250000</v>
+        <v>1260000</v>
       </c>
       <c r="M5" t="str">
-        <v/>
+        <v>Giường PN 2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>HD-MTX-24-RENO-WH-BASIC-BUY</v>
+        <v>HD-MTX-22-RENO-WH-BASIC-BUY</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>LIVING_ROOM</v>
+        <v>KITCHEN</v>
       </c>
       <c r="D6" t="str">
-        <v>Điều hòa</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="E6" t="str">
         <v>NEW</v>
@@ -5496,36 +5496,36 @@
         <v>1</v>
       </c>
       <c r="H6">
-        <v>11000000</v>
+        <v>7500000</v>
       </c>
       <c r="I6">
         <v>24</v>
       </c>
       <c r="J6" t="str">
-        <v>2026-10-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K6" t="str">
-        <v>2028-10-01</v>
+        <v>2028-08-01</v>
       </c>
       <c r="L6">
-        <v>3300000</v>
+        <v>2250000</v>
       </c>
       <c r="M6" t="str">
-        <v>ĐH phòng khách</v>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>HD-MTX-24-RENO-WH-BASIC-BUY</v>
+        <v>HD-MTX-22-RENO-WH-BASIC-BUY</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>KITCHEN</v>
+        <v>BATHROOM</v>
       </c>
       <c r="D7" t="str">
-        <v>Tủ lạnh</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E7" t="str">
         <v>NEW</v>
@@ -5537,19 +5537,19 @@
         <v>1</v>
       </c>
       <c r="H7">
-        <v>7500000</v>
+        <v>2800000</v>
       </c>
       <c r="I7">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J7" t="str">
-        <v>2026-10-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K7" t="str">
-        <v>2028-10-01</v>
+        <v>2027-08-01</v>
       </c>
       <c r="L7">
-        <v>2250000</v>
+        <v>840000</v>
       </c>
       <c r="M7" t="str">
         <v/>
@@ -5557,7 +5557,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-23-RENO-WH-BASIC-BUY</v>
       </c>
       <c r="B8" t="str">
         <v/>
@@ -5578,27 +5578,27 @@
         <v>1</v>
       </c>
       <c r="H8">
-        <v>14000000</v>
+        <v>11000000</v>
       </c>
       <c r="I8">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="J8" t="str">
-        <v>2026-03-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="K8" t="str">
-        <v>2029-03-01</v>
+        <v>2028-09-01</v>
       </c>
       <c r="L8">
-        <v>4200000</v>
+        <v>3300000</v>
       </c>
       <c r="M8" t="str">
-        <v/>
+        <v>ĐH phòng khách</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-23-RENO-WH-BASIC-BUY</v>
       </c>
       <c r="B9" t="str">
         <v/>
@@ -5619,27 +5619,27 @@
         <v>1</v>
       </c>
       <c r="H9">
-        <v>1200000</v>
+        <v>900000</v>
       </c>
       <c r="I9">
         <v>12</v>
       </c>
       <c r="J9" t="str">
-        <v>2026-03-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="K9" t="str">
-        <v>2027-03-01</v>
+        <v>2027-09-01</v>
       </c>
       <c r="L9">
-        <v>360000</v>
+        <v>270000</v>
       </c>
       <c r="M9" t="str">
-        <v>Quạt trần</v>
+        <v>Quạt trần PK</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-23-RENO-WH-BASIC-BUY</v>
       </c>
       <c r="B10" t="str">
         <v/>
@@ -5660,27 +5660,27 @@
         <v>1</v>
       </c>
       <c r="H10">
-        <v>5500000</v>
+        <v>5000000</v>
       </c>
       <c r="I10">
         <v>12</v>
       </c>
       <c r="J10" t="str">
-        <v>2026-03-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="K10" t="str">
-        <v>2027-03-01</v>
+        <v>2027-09-01</v>
       </c>
       <c r="L10">
-        <v>1650000</v>
+        <v>1500000</v>
       </c>
       <c r="M10" t="str">
-        <v>Giường PN chính</v>
+        <v>Giường PN 1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-23-RENO-WH-BASIC-BUY</v>
       </c>
       <c r="B11" t="str">
         <v/>
@@ -5701,19 +5701,19 @@
         <v>1</v>
       </c>
       <c r="H11">
-        <v>4800000</v>
+        <v>4200000</v>
       </c>
       <c r="I11">
         <v>12</v>
       </c>
       <c r="J11" t="str">
-        <v>2026-03-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="K11" t="str">
-        <v>2027-03-01</v>
+        <v>2027-09-01</v>
       </c>
       <c r="L11">
-        <v>1440000</v>
+        <v>1260000</v>
       </c>
       <c r="M11" t="str">
         <v>Giường PN 2</v>
@@ -5721,16 +5721,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-23-RENO-WH-BASIC-BUY</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>KITCHEN</v>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D12" t="str">
-        <v>Tủ lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="E12" t="str">
         <v>NEW</v>
@@ -5742,27 +5742,27 @@
         <v>1</v>
       </c>
       <c r="H12">
-        <v>8500000</v>
+        <v>4200000</v>
       </c>
       <c r="I12">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J12" t="str">
-        <v>2026-03-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="K12" t="str">
-        <v>2028-03-01</v>
+        <v>2027-09-01</v>
       </c>
       <c r="L12">
-        <v>2550000</v>
+        <v>1260000</v>
       </c>
       <c r="M12" t="str">
-        <v/>
+        <v>Giường PN 3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-23-RENO-WH-BASIC-BUY</v>
       </c>
       <c r="B13" t="str">
         <v/>
@@ -5771,7 +5771,7 @@
         <v>KITCHEN</v>
       </c>
       <c r="D13" t="str">
-        <v>Máy giặt</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="E13" t="str">
         <v>NEW</v>
@@ -5783,19 +5783,19 @@
         <v>1</v>
       </c>
       <c r="H13">
-        <v>9500000</v>
+        <v>7500000</v>
       </c>
       <c r="I13">
         <v>24</v>
       </c>
       <c r="J13" t="str">
-        <v>2026-03-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="K13" t="str">
-        <v>2028-03-01</v>
+        <v>2028-09-01</v>
       </c>
       <c r="L13">
-        <v>2850000</v>
+        <v>2250000</v>
       </c>
       <c r="M13" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-23-RENO-WH-BASIC-BUY</v>
       </c>
       <c r="B14" t="str">
         <v/>
@@ -5824,19 +5824,19 @@
         <v>1</v>
       </c>
       <c r="H14">
-        <v>3200000</v>
+        <v>2800000</v>
       </c>
       <c r="I14">
         <v>12</v>
       </c>
       <c r="J14" t="str">
-        <v>2026-03-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="K14" t="str">
-        <v>2027-03-01</v>
+        <v>2027-09-01</v>
       </c>
       <c r="L14">
-        <v>960000</v>
+        <v>840000</v>
       </c>
       <c r="M14" t="str">
         <v/>
@@ -5844,16 +5844,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-24-RENO-WH-BASIC-BUY</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>BALCONY</v>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D15" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E15" t="str">
         <v>NEW</v>
@@ -5865,27 +5865,27 @@
         <v>1</v>
       </c>
       <c r="H15">
-        <v>650000</v>
+        <v>11000000</v>
       </c>
       <c r="I15">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J15" t="str">
-        <v>2026-03-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="K15" t="str">
-        <v>2027-03-01</v>
+        <v>2028-10-01</v>
       </c>
       <c r="L15">
-        <v>195000</v>
+        <v>3300000</v>
       </c>
       <c r="M15" t="str">
-        <v/>
+        <v>ĐH phòng khách</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
+        <v>HD-MTX-24-RENO-WH-BASIC-BUY</v>
       </c>
       <c r="B16" t="str">
         <v/>
@@ -5894,7 +5894,7 @@
         <v>LIVING_ROOM</v>
       </c>
       <c r="D16" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="E16" t="str">
         <v>NEW</v>
@@ -5906,27 +5906,27 @@
         <v>1</v>
       </c>
       <c r="H16">
-        <v>14000000</v>
+        <v>900000</v>
       </c>
       <c r="I16">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="J16" t="str">
-        <v>2026-04-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="K16" t="str">
-        <v>2029-04-01</v>
+        <v>2027-10-01</v>
       </c>
       <c r="L16">
-        <v>4200000</v>
+        <v>270000</v>
       </c>
       <c r="M16" t="str">
-        <v/>
+        <v>Quạt trần PK</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
+        <v>HD-MTX-24-RENO-WH-BASIC-BUY</v>
       </c>
       <c r="B17" t="str">
         <v/>
@@ -5935,7 +5935,7 @@
         <v>LIVING_ROOM</v>
       </c>
       <c r="D17" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="E17" t="str">
         <v>NEW</v>
@@ -5947,36 +5947,36 @@
         <v>1</v>
       </c>
       <c r="H17">
-        <v>1200000</v>
+        <v>5000000</v>
       </c>
       <c r="I17">
         <v>12</v>
       </c>
       <c r="J17" t="str">
-        <v>2026-04-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="K17" t="str">
-        <v>2027-04-01</v>
+        <v>2027-10-01</v>
       </c>
       <c r="L17">
-        <v>360000</v>
+        <v>1500000</v>
       </c>
       <c r="M17" t="str">
-        <v>Quạt trần</v>
+        <v>Giường PN 1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
+        <v>HD-MTX-24-RENO-WH-BASIC-BUY</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>LIVING_ROOM</v>
+        <v>KITCHEN</v>
       </c>
       <c r="D18" t="str">
-        <v>Giường</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="E18" t="str">
         <v>NEW</v>
@@ -5988,36 +5988,36 @@
         <v>1</v>
       </c>
       <c r="H18">
-        <v>5500000</v>
+        <v>7500000</v>
       </c>
       <c r="I18">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J18" t="str">
-        <v>2026-04-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="K18" t="str">
-        <v>2027-04-01</v>
+        <v>2028-10-01</v>
       </c>
       <c r="L18">
-        <v>1650000</v>
+        <v>2250000</v>
       </c>
       <c r="M18" t="str">
-        <v>Giường PN chính</v>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
+        <v>HD-MTX-24-RENO-WH-BASIC-BUY</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>LIVING_ROOM</v>
+        <v>BATHROOM</v>
       </c>
       <c r="D19" t="str">
-        <v>Giường</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E19" t="str">
         <v>NEW</v>
@@ -6029,36 +6029,36 @@
         <v>1</v>
       </c>
       <c r="H19">
-        <v>4800000</v>
+        <v>2800000</v>
       </c>
       <c r="I19">
         <v>12</v>
       </c>
       <c r="J19" t="str">
-        <v>2026-04-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="K19" t="str">
-        <v>2027-04-01</v>
+        <v>2027-10-01</v>
       </c>
       <c r="L19">
-        <v>1440000</v>
+        <v>840000</v>
       </c>
       <c r="M19" t="str">
-        <v>Giường PN 2</v>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>KITCHEN</v>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D20" t="str">
-        <v>Tủ lạnh</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E20" t="str">
         <v>NEW</v>
@@ -6070,36 +6070,36 @@
         <v>1</v>
       </c>
       <c r="H20">
-        <v>8500000</v>
+        <v>14000000</v>
       </c>
       <c r="I20">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="J20" t="str">
-        <v>2026-04-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="K20" t="str">
-        <v>2028-04-01</v>
+        <v>2029-03-01</v>
       </c>
       <c r="L20">
-        <v>2550000</v>
+        <v>4200000</v>
       </c>
       <c r="M20" t="str">
-        <v/>
+        <v>ĐH phòng khách</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>KITCHEN</v>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D21" t="str">
-        <v>Máy giặt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E21" t="str">
         <v>NEW</v>
@@ -6117,30 +6117,30 @@
         <v>24</v>
       </c>
       <c r="J21" t="str">
-        <v>2026-04-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="K21" t="str">
-        <v>2028-04-01</v>
+        <v>2028-03-01</v>
       </c>
       <c r="L21">
         <v>2850000</v>
       </c>
       <c r="M21" t="str">
-        <v/>
+        <v>ĐH PN 1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>BATHROOM</v>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D22" t="str">
-        <v>Nóng lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="E22" t="str">
         <v>NEW</v>
@@ -6152,33 +6152,33 @@
         <v>1</v>
       </c>
       <c r="H22">
-        <v>3200000</v>
+        <v>5500000</v>
       </c>
       <c r="I22">
         <v>12</v>
       </c>
       <c r="J22" t="str">
-        <v>2026-04-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="K22" t="str">
-        <v>2027-04-01</v>
+        <v>2027-03-01</v>
       </c>
       <c r="L22">
-        <v>960000</v>
+        <v>1650000</v>
       </c>
       <c r="M22" t="str">
-        <v/>
+        <v>Giường PN 1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>BALCONY</v>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D23" t="str">
         <v>Quạt</v>
@@ -6193,27 +6193,27 @@
         <v>1</v>
       </c>
       <c r="H23">
-        <v>650000</v>
+        <v>750000</v>
       </c>
       <c r="I23">
         <v>12</v>
       </c>
       <c r="J23" t="str">
-        <v>2026-04-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="K23" t="str">
-        <v>2027-04-01</v>
+        <v>2027-03-01</v>
       </c>
       <c r="L23">
-        <v>195000</v>
+        <v>225000</v>
       </c>
       <c r="M23" t="str">
-        <v/>
+        <v>Quạt PN 1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B24" t="str">
         <v/>
@@ -6234,27 +6234,27 @@
         <v>1</v>
       </c>
       <c r="H24">
-        <v>14000000</v>
+        <v>9500000</v>
       </c>
       <c r="I24">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="J24" t="str">
-        <v>2026-05-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="K24" t="str">
-        <v>2029-05-01</v>
+        <v>2028-03-01</v>
       </c>
       <c r="L24">
-        <v>4200000</v>
+        <v>2850000</v>
       </c>
       <c r="M24" t="str">
-        <v/>
+        <v>ĐH PN 2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B25" t="str">
         <v/>
@@ -6263,7 +6263,7 @@
         <v>LIVING_ROOM</v>
       </c>
       <c r="D25" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="E25" t="str">
         <v>NEW</v>
@@ -6275,27 +6275,27 @@
         <v>1</v>
       </c>
       <c r="H25">
-        <v>1200000</v>
+        <v>4800000</v>
       </c>
       <c r="I25">
         <v>12</v>
       </c>
       <c r="J25" t="str">
-        <v>2026-05-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="K25" t="str">
-        <v>2027-05-01</v>
+        <v>2027-03-01</v>
       </c>
       <c r="L25">
-        <v>360000</v>
+        <v>1440000</v>
       </c>
       <c r="M25" t="str">
-        <v>Quạt trần</v>
+        <v>Giường PN 2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B26" t="str">
         <v/>
@@ -6304,7 +6304,7 @@
         <v>LIVING_ROOM</v>
       </c>
       <c r="D26" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E26" t="str">
         <v>NEW</v>
@@ -6316,27 +6316,27 @@
         <v>1</v>
       </c>
       <c r="H26">
-        <v>5500000</v>
+        <v>750000</v>
       </c>
       <c r="I26">
         <v>12</v>
       </c>
       <c r="J26" t="str">
-        <v>2026-05-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="K26" t="str">
-        <v>2027-05-01</v>
+        <v>2027-03-01</v>
       </c>
       <c r="L26">
-        <v>1650000</v>
+        <v>225000</v>
       </c>
       <c r="M26" t="str">
-        <v>Giường PN chính</v>
+        <v>Quạt PN 2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B27" t="str">
         <v/>
@@ -6345,7 +6345,7 @@
         <v>LIVING_ROOM</v>
       </c>
       <c r="D27" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E27" t="str">
         <v>NEW</v>
@@ -6357,27 +6357,27 @@
         <v>1</v>
       </c>
       <c r="H27">
-        <v>4800000</v>
+        <v>1200000</v>
       </c>
       <c r="I27">
         <v>12</v>
       </c>
       <c r="J27" t="str">
-        <v>2026-05-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="K27" t="str">
-        <v>2027-05-01</v>
+        <v>2027-03-01</v>
       </c>
       <c r="L27">
-        <v>1440000</v>
+        <v>360000</v>
       </c>
       <c r="M27" t="str">
-        <v>Giường PN 2</v>
+        <v>Quạt trần PK</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B28" t="str">
         <v/>
@@ -6404,10 +6404,10 @@
         <v>24</v>
       </c>
       <c r="J28" t="str">
-        <v>2026-05-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="K28" t="str">
-        <v>2028-05-01</v>
+        <v>2028-03-01</v>
       </c>
       <c r="L28">
         <v>2550000</v>
@@ -6418,7 +6418,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B29" t="str">
         <v/>
@@ -6445,10 +6445,10 @@
         <v>24</v>
       </c>
       <c r="J29" t="str">
-        <v>2026-05-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="K29" t="str">
-        <v>2028-05-01</v>
+        <v>2028-03-01</v>
       </c>
       <c r="L29">
         <v>2850000</v>
@@ -6459,7 +6459,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B30" t="str">
         <v/>
@@ -6486,10 +6486,10 @@
         <v>12</v>
       </c>
       <c r="J30" t="str">
-        <v>2026-05-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="K30" t="str">
-        <v>2027-05-01</v>
+        <v>2027-03-01</v>
       </c>
       <c r="L30">
         <v>960000</v>
@@ -6500,7 +6500,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B31" t="str">
         <v/>
@@ -6527,10 +6527,10 @@
         <v>12</v>
       </c>
       <c r="J31" t="str">
-        <v>2026-05-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="K31" t="str">
-        <v>2027-05-01</v>
+        <v>2027-03-01</v>
       </c>
       <c r="L31">
         <v>195000</v>
@@ -6541,7 +6541,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
+        <v>HD-MTX-26-RENO-WH-FULL</v>
       </c>
       <c r="B32" t="str">
         <v/>
@@ -6562,19 +6562,19 @@
         <v>1</v>
       </c>
       <c r="H32">
-        <v>11000000</v>
+        <v>14000000</v>
       </c>
       <c r="I32">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="J32" t="str">
-        <v>2026-08-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K32" t="str">
-        <v>2028-08-01</v>
+        <v>2029-04-01</v>
       </c>
       <c r="L32">
-        <v>3300000</v>
+        <v>4200000</v>
       </c>
       <c r="M32" t="str">
         <v>ĐH phòng khách</v>
@@ -6582,16 +6582,16 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
+        <v>HD-MTX-26-RENO-WH-FULL</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>KITCHEN</v>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D33" t="str">
-        <v>Tủ lạnh</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E33" t="str">
         <v>NEW</v>
@@ -6603,27 +6603,27 @@
         <v>1</v>
       </c>
       <c r="H33">
-        <v>7500000</v>
+        <v>9500000</v>
       </c>
       <c r="I33">
         <v>24</v>
       </c>
       <c r="J33" t="str">
-        <v>2026-08-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K33" t="str">
-        <v>2028-08-01</v>
+        <v>2028-04-01</v>
       </c>
       <c r="L33">
-        <v>2250000</v>
+        <v>2850000</v>
       </c>
       <c r="M33" t="str">
-        <v/>
+        <v>ĐH PN 1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
+        <v>HD-MTX-26-RENO-WH-FULL</v>
       </c>
       <c r="B34" t="str">
         <v/>
@@ -6632,7 +6632,7 @@
         <v>LIVING_ROOM</v>
       </c>
       <c r="D34" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="E34" t="str">
         <v>NEW</v>
@@ -6644,36 +6644,36 @@
         <v>1</v>
       </c>
       <c r="H34">
-        <v>11000000</v>
+        <v>5500000</v>
       </c>
       <c r="I34">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J34" t="str">
-        <v>2026-09-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K34" t="str">
-        <v>2028-09-01</v>
+        <v>2027-04-01</v>
       </c>
       <c r="L34">
-        <v>3300000</v>
+        <v>1650000</v>
       </c>
       <c r="M34" t="str">
-        <v>ĐH phòng khách</v>
+        <v>Giường PN 1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
+        <v>HD-MTX-26-RENO-WH-FULL</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>KITCHEN</v>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D35" t="str">
-        <v>Tủ lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="E35" t="str">
         <v>NEW</v>
@@ -6685,36 +6685,36 @@
         <v>1</v>
       </c>
       <c r="H35">
-        <v>7500000</v>
+        <v>750000</v>
       </c>
       <c r="I35">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J35" t="str">
-        <v>2026-09-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K35" t="str">
-        <v>2028-09-01</v>
+        <v>2027-04-01</v>
       </c>
       <c r="L35">
-        <v>2250000</v>
+        <v>225000</v>
       </c>
       <c r="M35" t="str">
-        <v/>
+        <v>Quạt PN 1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-26-RENO-WH-FULL</v>
       </c>
       <c r="B36" t="str">
-        <v>101</v>
+        <v/>
       </c>
       <c r="C36" t="str">
-        <v/>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D36" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E36" t="str">
         <v>NEW</v>
@@ -6726,36 +6726,36 @@
         <v>1</v>
       </c>
       <c r="H36">
-        <v>4000000</v>
+        <v>9500000</v>
       </c>
       <c r="I36">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J36" t="str">
-        <v>2026-10-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K36" t="str">
-        <v>2027-10-01</v>
+        <v>2028-04-01</v>
       </c>
       <c r="L36">
-        <v>1200000</v>
+        <v>2850000</v>
       </c>
       <c r="M36" t="str">
-        <v>NT cơ bản phòng 101</v>
+        <v>ĐH PN 2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-26-RENO-WH-FULL</v>
       </c>
       <c r="B37" t="str">
-        <v>101</v>
+        <v/>
       </c>
       <c r="C37" t="str">
-        <v/>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D37" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="E37" t="str">
         <v>NEW</v>
@@ -6767,36 +6767,36 @@
         <v>1</v>
       </c>
       <c r="H37">
-        <v>750000</v>
+        <v>4800000</v>
       </c>
       <c r="I37">
         <v>12</v>
       </c>
       <c r="J37" t="str">
-        <v>2026-10-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K37" t="str">
-        <v>2027-10-01</v>
+        <v>2027-04-01</v>
       </c>
       <c r="L37">
-        <v>225000</v>
+        <v>1440000</v>
       </c>
       <c r="M37" t="str">
-        <v>Quạt phòng 101</v>
+        <v>Giường PN 2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-26-RENO-WH-FULL</v>
       </c>
       <c r="B38" t="str">
-        <v>102</v>
+        <v/>
       </c>
       <c r="C38" t="str">
-        <v/>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D38" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E38" t="str">
         <v>NEW</v>
@@ -6808,33 +6808,33 @@
         <v>1</v>
       </c>
       <c r="H38">
-        <v>4000000</v>
+        <v>750000</v>
       </c>
       <c r="I38">
         <v>12</v>
       </c>
       <c r="J38" t="str">
-        <v>2026-10-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K38" t="str">
-        <v>2027-10-01</v>
+        <v>2027-04-01</v>
       </c>
       <c r="L38">
-        <v>1200000</v>
+        <v>225000</v>
       </c>
       <c r="M38" t="str">
-        <v>NT cơ bản phòng 102</v>
+        <v>Quạt PN 2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-26-RENO-WH-FULL</v>
       </c>
       <c r="B39" t="str">
-        <v>102</v>
+        <v/>
       </c>
       <c r="C39" t="str">
-        <v/>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D39" t="str">
         <v>Điều hòa</v>
@@ -6849,33 +6849,33 @@
         <v>1</v>
       </c>
       <c r="H39">
-        <v>8500000</v>
+        <v>9500000</v>
       </c>
       <c r="I39">
         <v>24</v>
       </c>
       <c r="J39" t="str">
-        <v>2026-10-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K39" t="str">
-        <v>2028-10-01</v>
+        <v>2028-04-01</v>
       </c>
       <c r="L39">
-        <v>2550000</v>
+        <v>2850000</v>
       </c>
       <c r="M39" t="str">
-        <v>ĐH phòng 102</v>
+        <v>ĐH PN 3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-26-RENO-WH-FULL</v>
       </c>
       <c r="B40" t="str">
-        <v>103</v>
+        <v/>
       </c>
       <c r="C40" t="str">
-        <v/>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D40" t="str">
         <v>Giường</v>
@@ -6890,33 +6890,33 @@
         <v>1</v>
       </c>
       <c r="H40">
-        <v>4000000</v>
+        <v>4800000</v>
       </c>
       <c r="I40">
         <v>12</v>
       </c>
       <c r="J40" t="str">
-        <v>2026-10-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K40" t="str">
-        <v>2027-10-01</v>
+        <v>2027-04-01</v>
       </c>
       <c r="L40">
-        <v>1200000</v>
+        <v>1440000</v>
       </c>
       <c r="M40" t="str">
-        <v>NT cơ bản phòng 103</v>
+        <v>Giường PN 3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-26-RENO-WH-FULL</v>
       </c>
       <c r="B41" t="str">
-        <v>103</v>
+        <v/>
       </c>
       <c r="C41" t="str">
-        <v/>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D41" t="str">
         <v>Quạt</v>
@@ -6937,30 +6937,30 @@
         <v>12</v>
       </c>
       <c r="J41" t="str">
-        <v>2026-10-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K41" t="str">
-        <v>2027-10-01</v>
+        <v>2027-04-01</v>
       </c>
       <c r="L41">
         <v>225000</v>
       </c>
       <c r="M41" t="str">
-        <v>Quạt phòng 103</v>
+        <v>Quạt PN 3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-26-RENO-WH-FULL</v>
       </c>
       <c r="B42" t="str">
-        <v>101</v>
+        <v/>
       </c>
       <c r="C42" t="str">
-        <v/>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D42" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E42" t="str">
         <v>NEW</v>
@@ -6972,36 +6972,36 @@
         <v>1</v>
       </c>
       <c r="H42">
-        <v>4000000</v>
+        <v>1200000</v>
       </c>
       <c r="I42">
         <v>12</v>
       </c>
       <c r="J42" t="str">
-        <v>2026-03-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K42" t="str">
-        <v>2027-03-01</v>
+        <v>2027-04-01</v>
       </c>
       <c r="L42">
-        <v>1200000</v>
+        <v>360000</v>
       </c>
       <c r="M42" t="str">
-        <v>NT cơ bản phòng 101</v>
+        <v>Quạt trần PK</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-26-RENO-WH-FULL</v>
       </c>
       <c r="B43" t="str">
-        <v>101</v>
+        <v/>
       </c>
       <c r="C43" t="str">
-        <v/>
+        <v>KITCHEN</v>
       </c>
       <c r="D43" t="str">
-        <v>Quạt</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="E43" t="str">
         <v>NEW</v>
@@ -7013,36 +7013,36 @@
         <v>1</v>
       </c>
       <c r="H43">
-        <v>750000</v>
+        <v>8500000</v>
       </c>
       <c r="I43">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J43" t="str">
-        <v>2026-03-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K43" t="str">
-        <v>2027-03-01</v>
+        <v>2028-04-01</v>
       </c>
       <c r="L43">
-        <v>225000</v>
+        <v>2550000</v>
       </c>
       <c r="M43" t="str">
-        <v>Quạt phòng 101</v>
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-26-RENO-WH-FULL</v>
       </c>
       <c r="B44" t="str">
-        <v>102</v>
+        <v/>
       </c>
       <c r="C44" t="str">
-        <v/>
+        <v>KITCHEN</v>
       </c>
       <c r="D44" t="str">
-        <v>Giường</v>
+        <v>Máy giặt</v>
       </c>
       <c r="E44" t="str">
         <v>NEW</v>
@@ -7054,36 +7054,36 @@
         <v>1</v>
       </c>
       <c r="H44">
-        <v>4000000</v>
+        <v>9500000</v>
       </c>
       <c r="I44">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J44" t="str">
-        <v>2026-03-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K44" t="str">
-        <v>2027-03-01</v>
+        <v>2028-04-01</v>
       </c>
       <c r="L44">
-        <v>1200000</v>
+        <v>2850000</v>
       </c>
       <c r="M44" t="str">
-        <v>NT cơ bản phòng 102</v>
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-26-RENO-WH-FULL</v>
       </c>
       <c r="B45" t="str">
-        <v>102</v>
+        <v/>
       </c>
       <c r="C45" t="str">
-        <v/>
+        <v>BATHROOM</v>
       </c>
       <c r="D45" t="str">
-        <v>Điều hòa</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E45" t="str">
         <v>NEW</v>
@@ -7095,36 +7095,36 @@
         <v>1</v>
       </c>
       <c r="H45">
-        <v>8500000</v>
+        <v>3200000</v>
       </c>
       <c r="I45">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J45" t="str">
-        <v>2026-03-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K45" t="str">
-        <v>2028-03-01</v>
+        <v>2027-04-01</v>
       </c>
       <c r="L45">
-        <v>2550000</v>
+        <v>960000</v>
       </c>
       <c r="M45" t="str">
-        <v>ĐH phòng 102</v>
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-26-RENO-WH-FULL</v>
       </c>
       <c r="B46" t="str">
-        <v>103</v>
+        <v/>
       </c>
       <c r="C46" t="str">
-        <v/>
+        <v>BALCONY</v>
       </c>
       <c r="D46" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E46" t="str">
         <v>NEW</v>
@@ -7136,36 +7136,36 @@
         <v>1</v>
       </c>
       <c r="H46">
-        <v>4000000</v>
+        <v>650000</v>
       </c>
       <c r="I46">
         <v>12</v>
       </c>
       <c r="J46" t="str">
-        <v>2026-03-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K46" t="str">
-        <v>2027-03-01</v>
+        <v>2027-04-01</v>
       </c>
       <c r="L46">
-        <v>1200000</v>
+        <v>195000</v>
       </c>
       <c r="M46" t="str">
-        <v>NT cơ bản phòng 103</v>
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-27-RENO-WH-FULL</v>
       </c>
       <c r="B47" t="str">
-        <v>103</v>
+        <v/>
       </c>
       <c r="C47" t="str">
-        <v/>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D47" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E47" t="str">
         <v>NEW</v>
@@ -7177,36 +7177,36 @@
         <v>1</v>
       </c>
       <c r="H47">
-        <v>750000</v>
+        <v>14000000</v>
       </c>
       <c r="I47">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="J47" t="str">
-        <v>2026-03-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="K47" t="str">
-        <v>2027-03-01</v>
+        <v>2029-05-01</v>
       </c>
       <c r="L47">
-        <v>225000</v>
+        <v>4200000</v>
       </c>
       <c r="M47" t="str">
-        <v>Quạt phòng 103</v>
+        <v>ĐH phòng khách</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-27-RENO-WH-FULL</v>
       </c>
       <c r="B48" t="str">
-        <v>104</v>
+        <v/>
       </c>
       <c r="C48" t="str">
-        <v/>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D48" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E48" t="str">
         <v>NEW</v>
@@ -7218,36 +7218,36 @@
         <v>1</v>
       </c>
       <c r="H48">
-        <v>4000000</v>
+        <v>9500000</v>
       </c>
       <c r="I48">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J48" t="str">
-        <v>2026-03-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="K48" t="str">
-        <v>2027-03-01</v>
+        <v>2028-05-01</v>
       </c>
       <c r="L48">
-        <v>1200000</v>
+        <v>2850000</v>
       </c>
       <c r="M48" t="str">
-        <v>NT cơ bản phòng 104</v>
+        <v>ĐH PN 1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-27-RENO-WH-FULL</v>
       </c>
       <c r="B49" t="str">
-        <v>104</v>
+        <v/>
       </c>
       <c r="C49" t="str">
-        <v/>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D49" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="E49" t="str">
         <v>NEW</v>
@@ -7259,36 +7259,36 @@
         <v>1</v>
       </c>
       <c r="H49">
-        <v>8500000</v>
+        <v>5500000</v>
       </c>
       <c r="I49">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J49" t="str">
-        <v>2026-03-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="K49" t="str">
-        <v>2028-03-01</v>
+        <v>2027-05-01</v>
       </c>
       <c r="L49">
-        <v>2550000</v>
+        <v>1650000</v>
       </c>
       <c r="M49" t="str">
-        <v>ĐH phòng 104</v>
+        <v>Giường PN 1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-27-RENO-WH-FULL</v>
       </c>
       <c r="B50" t="str">
-        <v>101</v>
+        <v/>
       </c>
       <c r="C50" t="str">
-        <v/>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D50" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E50" t="str">
         <v>NEW</v>
@@ -7300,33 +7300,33 @@
         <v>1</v>
       </c>
       <c r="H50">
-        <v>4000000</v>
+        <v>750000</v>
       </c>
       <c r="I50">
         <v>12</v>
       </c>
       <c r="J50" t="str">
-        <v>2026-04-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="K50" t="str">
-        <v>2027-04-01</v>
+        <v>2027-05-01</v>
       </c>
       <c r="L50">
-        <v>1200000</v>
+        <v>225000</v>
       </c>
       <c r="M50" t="str">
-        <v>NT cơ bản phòng 101</v>
+        <v>Quạt PN 1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-27-RENO-WH-FULL</v>
       </c>
       <c r="B51" t="str">
-        <v>101</v>
+        <v/>
       </c>
       <c r="C51" t="str">
-        <v/>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D51" t="str">
         <v>Quạt</v>
@@ -7341,36 +7341,36 @@
         <v>1</v>
       </c>
       <c r="H51">
-        <v>750000</v>
+        <v>1200000</v>
       </c>
       <c r="I51">
         <v>12</v>
       </c>
       <c r="J51" t="str">
-        <v>2026-04-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="K51" t="str">
-        <v>2027-04-01</v>
+        <v>2027-05-01</v>
       </c>
       <c r="L51">
-        <v>225000</v>
+        <v>360000</v>
       </c>
       <c r="M51" t="str">
-        <v>Quạt phòng 101</v>
+        <v>Quạt trần PK</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-27-RENO-WH-FULL</v>
       </c>
       <c r="B52" t="str">
-        <v>102</v>
+        <v/>
       </c>
       <c r="C52" t="str">
-        <v/>
+        <v>KITCHEN</v>
       </c>
       <c r="D52" t="str">
-        <v>Giường</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="E52" t="str">
         <v>NEW</v>
@@ -7382,36 +7382,36 @@
         <v>1</v>
       </c>
       <c r="H52">
-        <v>4000000</v>
+        <v>8500000</v>
       </c>
       <c r="I52">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J52" t="str">
-        <v>2026-04-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="K52" t="str">
-        <v>2027-04-01</v>
+        <v>2028-05-01</v>
       </c>
       <c r="L52">
-        <v>1200000</v>
+        <v>2550000</v>
       </c>
       <c r="M52" t="str">
-        <v>NT cơ bản phòng 102</v>
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-27-RENO-WH-FULL</v>
       </c>
       <c r="B53" t="str">
-        <v>102</v>
+        <v/>
       </c>
       <c r="C53" t="str">
-        <v/>
+        <v>KITCHEN</v>
       </c>
       <c r="D53" t="str">
-        <v>Điều hòa</v>
+        <v>Máy giặt</v>
       </c>
       <c r="E53" t="str">
         <v>NEW</v>
@@ -7423,36 +7423,36 @@
         <v>1</v>
       </c>
       <c r="H53">
-        <v>8500000</v>
+        <v>9500000</v>
       </c>
       <c r="I53">
         <v>24</v>
       </c>
       <c r="J53" t="str">
-        <v>2026-04-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="K53" t="str">
-        <v>2028-04-01</v>
+        <v>2028-05-01</v>
       </c>
       <c r="L53">
-        <v>2550000</v>
+        <v>2850000</v>
       </c>
       <c r="M53" t="str">
-        <v>ĐH phòng 102</v>
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-27-RENO-WH-FULL</v>
       </c>
       <c r="B54" t="str">
-        <v>103</v>
+        <v/>
       </c>
       <c r="C54" t="str">
-        <v/>
+        <v>BATHROOM</v>
       </c>
       <c r="D54" t="str">
-        <v>Giường</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E54" t="str">
         <v>NEW</v>
@@ -7464,33 +7464,33 @@
         <v>1</v>
       </c>
       <c r="H54">
-        <v>4000000</v>
+        <v>3200000</v>
       </c>
       <c r="I54">
         <v>12</v>
       </c>
       <c r="J54" t="str">
-        <v>2026-04-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="K54" t="str">
-        <v>2027-04-01</v>
+        <v>2027-05-01</v>
       </c>
       <c r="L54">
-        <v>1200000</v>
+        <v>960000</v>
       </c>
       <c r="M54" t="str">
-        <v>NT cơ bản phòng 103</v>
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-27-RENO-WH-FULL</v>
       </c>
       <c r="B55" t="str">
-        <v>103</v>
+        <v/>
       </c>
       <c r="C55" t="str">
-        <v/>
+        <v>BALCONY</v>
       </c>
       <c r="D55" t="str">
         <v>Quạt</v>
@@ -7505,36 +7505,36 @@
         <v>1</v>
       </c>
       <c r="H55">
-        <v>750000</v>
+        <v>650000</v>
       </c>
       <c r="I55">
         <v>12</v>
       </c>
       <c r="J55" t="str">
-        <v>2026-04-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="K55" t="str">
-        <v>2027-04-01</v>
+        <v>2027-05-01</v>
       </c>
       <c r="L55">
-        <v>225000</v>
+        <v>195000</v>
       </c>
       <c r="M55" t="str">
-        <v>Quạt phòng 103</v>
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
       </c>
       <c r="B56" t="str">
-        <v>101</v>
+        <v/>
       </c>
       <c r="C56" t="str">
-        <v/>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D56" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E56" t="str">
         <v>NEW</v>
@@ -7546,33 +7546,33 @@
         <v>1</v>
       </c>
       <c r="H56">
-        <v>4000000</v>
+        <v>11000000</v>
       </c>
       <c r="I56">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J56" t="str">
-        <v>2026-05-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K56" t="str">
-        <v>2027-05-01</v>
+        <v>2028-08-01</v>
       </c>
       <c r="L56">
-        <v>1200000</v>
+        <v>3300000</v>
       </c>
       <c r="M56" t="str">
-        <v>NT cơ bản phòng 101</v>
+        <v>ĐH phòng khách</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
       </c>
       <c r="B57" t="str">
-        <v>101</v>
+        <v/>
       </c>
       <c r="C57" t="str">
-        <v/>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D57" t="str">
         <v>Quạt</v>
@@ -7587,33 +7587,33 @@
         <v>1</v>
       </c>
       <c r="H57">
-        <v>750000</v>
+        <v>900000</v>
       </c>
       <c r="I57">
         <v>12</v>
       </c>
       <c r="J57" t="str">
-        <v>2026-05-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K57" t="str">
-        <v>2027-05-01</v>
+        <v>2027-08-01</v>
       </c>
       <c r="L57">
-        <v>225000</v>
+        <v>270000</v>
       </c>
       <c r="M57" t="str">
-        <v>Quạt phòng 101</v>
+        <v>Quạt trần PK</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
       </c>
       <c r="B58" t="str">
-        <v>102</v>
+        <v/>
       </c>
       <c r="C58" t="str">
-        <v/>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D58" t="str">
         <v>Giường</v>
@@ -7628,36 +7628,36 @@
         <v>1</v>
       </c>
       <c r="H58">
-        <v>4000000</v>
+        <v>5000000</v>
       </c>
       <c r="I58">
         <v>12</v>
       </c>
       <c r="J58" t="str">
-        <v>2026-05-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K58" t="str">
-        <v>2027-05-01</v>
+        <v>2027-08-01</v>
       </c>
       <c r="L58">
-        <v>1200000</v>
+        <v>1500000</v>
       </c>
       <c r="M58" t="str">
-        <v>NT cơ bản phòng 102</v>
+        <v>Giường PN 1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
       </c>
       <c r="B59" t="str">
-        <v>102</v>
+        <v/>
       </c>
       <c r="C59" t="str">
-        <v/>
+        <v>KITCHEN</v>
       </c>
       <c r="D59" t="str">
-        <v>Điều hòa</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="E59" t="str">
         <v>NEW</v>
@@ -7669,36 +7669,36 @@
         <v>1</v>
       </c>
       <c r="H59">
-        <v>8500000</v>
+        <v>7500000</v>
       </c>
       <c r="I59">
         <v>24</v>
       </c>
       <c r="J59" t="str">
-        <v>2026-05-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K59" t="str">
-        <v>2028-05-01</v>
+        <v>2028-08-01</v>
       </c>
       <c r="L59">
-        <v>2550000</v>
+        <v>2250000</v>
       </c>
       <c r="M59" t="str">
-        <v>ĐH phòng 102</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
       </c>
       <c r="B60" t="str">
-        <v>103</v>
+        <v/>
       </c>
       <c r="C60" t="str">
-        <v/>
+        <v>BATHROOM</v>
       </c>
       <c r="D60" t="str">
-        <v>Giường</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E60" t="str">
         <v>NEW</v>
@@ -7710,36 +7710,36 @@
         <v>1</v>
       </c>
       <c r="H60">
-        <v>4000000</v>
+        <v>2800000</v>
       </c>
       <c r="I60">
         <v>12</v>
       </c>
       <c r="J60" t="str">
-        <v>2026-05-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K60" t="str">
-        <v>2027-05-01</v>
+        <v>2027-08-01</v>
       </c>
       <c r="L60">
-        <v>1200000</v>
+        <v>840000</v>
       </c>
       <c r="M60" t="str">
-        <v>NT cơ bản phòng 103</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
       </c>
       <c r="B61" t="str">
-        <v>103</v>
+        <v/>
       </c>
       <c r="C61" t="str">
-        <v/>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D61" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E61" t="str">
         <v>NEW</v>
@@ -7751,36 +7751,36 @@
         <v>1</v>
       </c>
       <c r="H61">
-        <v>750000</v>
+        <v>11000000</v>
       </c>
       <c r="I61">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J61" t="str">
-        <v>2026-05-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="K61" t="str">
-        <v>2027-05-01</v>
+        <v>2028-09-01</v>
       </c>
       <c r="L61">
-        <v>225000</v>
+        <v>3300000</v>
       </c>
       <c r="M61" t="str">
-        <v>Quạt phòng 103</v>
+        <v>ĐH phòng khách</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
       </c>
       <c r="B62" t="str">
-        <v>104</v>
+        <v/>
       </c>
       <c r="C62" t="str">
-        <v/>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D62" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E62" t="str">
         <v>NEW</v>
@@ -7792,36 +7792,36 @@
         <v>1</v>
       </c>
       <c r="H62">
-        <v>4000000</v>
+        <v>900000</v>
       </c>
       <c r="I62">
         <v>12</v>
       </c>
       <c r="J62" t="str">
-        <v>2026-05-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="K62" t="str">
-        <v>2027-05-01</v>
+        <v>2027-09-01</v>
       </c>
       <c r="L62">
-        <v>1200000</v>
+        <v>270000</v>
       </c>
       <c r="M62" t="str">
-        <v>NT cơ bản phòng 104</v>
+        <v>Quạt trần PK</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
       </c>
       <c r="B63" t="str">
-        <v>104</v>
+        <v/>
       </c>
       <c r="C63" t="str">
-        <v/>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D63" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="E63" t="str">
         <v>NEW</v>
@@ -7833,33 +7833,33 @@
         <v>1</v>
       </c>
       <c r="H63">
-        <v>8500000</v>
+        <v>5000000</v>
       </c>
       <c r="I63">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J63" t="str">
-        <v>2026-05-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="K63" t="str">
-        <v>2028-05-01</v>
+        <v>2027-09-01</v>
       </c>
       <c r="L63">
-        <v>2550000</v>
+        <v>1500000</v>
       </c>
       <c r="M63" t="str">
-        <v>ĐH phòng 104</v>
+        <v>Giường PN 1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
+        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
       </c>
       <c r="B64" t="str">
-        <v>101</v>
+        <v/>
       </c>
       <c r="C64" t="str">
-        <v/>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D64" t="str">
         <v>Giường</v>
@@ -7874,36 +7874,36 @@
         <v>1</v>
       </c>
       <c r="H64">
-        <v>4500000</v>
+        <v>4200000</v>
       </c>
       <c r="I64">
         <v>12</v>
       </c>
       <c r="J64" t="str">
-        <v>2026-06-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="K64" t="str">
-        <v>2027-06-01</v>
+        <v>2027-09-01</v>
       </c>
       <c r="L64">
-        <v>1350000</v>
+        <v>1260000</v>
       </c>
       <c r="M64" t="str">
-        <v>Giường phòng 101</v>
+        <v>Giường PN 2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
+        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
       </c>
       <c r="B65" t="str">
-        <v>101</v>
+        <v/>
       </c>
       <c r="C65" t="str">
-        <v/>
+        <v>KITCHEN</v>
       </c>
       <c r="D65" t="str">
-        <v>Quạt</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="E65" t="str">
         <v>NEW</v>
@@ -7915,36 +7915,36 @@
         <v>1</v>
       </c>
       <c r="H65">
-        <v>800000</v>
+        <v>7500000</v>
       </c>
       <c r="I65">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J65" t="str">
-        <v>2026-06-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="K65" t="str">
-        <v>2027-06-01</v>
+        <v>2028-09-01</v>
       </c>
       <c r="L65">
-        <v>240000</v>
+        <v>2250000</v>
       </c>
       <c r="M65" t="str">
-        <v>Quạt phòng 101</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
+        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
       </c>
       <c r="B66" t="str">
-        <v>101</v>
+        <v/>
       </c>
       <c r="C66" t="str">
-        <v/>
+        <v>BATHROOM</v>
       </c>
       <c r="D66" t="str">
-        <v>Điều hòa</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E66" t="str">
         <v>NEW</v>
@@ -7956,27 +7956,27 @@
         <v>1</v>
       </c>
       <c r="H66">
-        <v>9200000</v>
+        <v>2800000</v>
       </c>
       <c r="I66">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J66" t="str">
-        <v>2026-06-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="K66" t="str">
-        <v>2028-06-01</v>
+        <v>2027-09-01</v>
       </c>
       <c r="L66">
-        <v>2760000</v>
+        <v>840000</v>
       </c>
       <c r="M66" t="str">
-        <v>ĐH phòng 101</v>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
+        <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B67" t="str">
         <v>101</v>
@@ -7985,7 +7985,7 @@
         <v/>
       </c>
       <c r="D67" t="str">
-        <v>Nóng lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="E67" t="str">
         <v>NEW</v>
@@ -7997,36 +7997,36 @@
         <v>1</v>
       </c>
       <c r="H67">
-        <v>2600000</v>
+        <v>4000000</v>
       </c>
       <c r="I67">
         <v>12</v>
       </c>
       <c r="J67" t="str">
-        <v>2026-06-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="K67" t="str">
-        <v>2027-06-01</v>
+        <v>2027-10-01</v>
       </c>
       <c r="L67">
-        <v>780000</v>
+        <v>1200000</v>
       </c>
       <c r="M67" t="str">
-        <v>NL phòng 101</v>
+        <v>NT cơ bản phòng 101</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
+        <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B68" t="str">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C68" t="str">
         <v/>
       </c>
       <c r="D68" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E68" t="str">
         <v>NEW</v>
@@ -8038,36 +8038,36 @@
         <v>1</v>
       </c>
       <c r="H68">
-        <v>4500000</v>
+        <v>750000</v>
       </c>
       <c r="I68">
         <v>12</v>
       </c>
       <c r="J68" t="str">
-        <v>2026-06-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="K68" t="str">
-        <v>2027-06-01</v>
+        <v>2027-10-01</v>
       </c>
       <c r="L68">
-        <v>1350000</v>
+        <v>225000</v>
       </c>
       <c r="M68" t="str">
-        <v>Giường phòng 102</v>
+        <v>Quạt phòng 101</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
+        <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B69" t="str">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C69" t="str">
         <v/>
       </c>
       <c r="D69" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E69" t="str">
         <v>NEW</v>
@@ -8079,27 +8079,27 @@
         <v>1</v>
       </c>
       <c r="H69">
-        <v>800000</v>
+        <v>8500000</v>
       </c>
       <c r="I69">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J69" t="str">
-        <v>2026-06-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="K69" t="str">
-        <v>2027-06-01</v>
+        <v>2028-10-01</v>
       </c>
       <c r="L69">
-        <v>240000</v>
+        <v>2550000</v>
       </c>
       <c r="M69" t="str">
-        <v>Quạt phòng 102</v>
+        <v>ĐH phòng 101</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
+        <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B70" t="str">
         <v>102</v>
@@ -8108,7 +8108,7 @@
         <v/>
       </c>
       <c r="D70" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="E70" t="str">
         <v>NEW</v>
@@ -8120,27 +8120,27 @@
         <v>1</v>
       </c>
       <c r="H70">
-        <v>9200000</v>
+        <v>4000000</v>
       </c>
       <c r="I70">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J70" t="str">
-        <v>2026-06-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="K70" t="str">
-        <v>2028-06-01</v>
+        <v>2027-10-01</v>
       </c>
       <c r="L70">
-        <v>2760000</v>
+        <v>1200000</v>
       </c>
       <c r="M70" t="str">
-        <v>ĐH phòng 102</v>
+        <v>NT cơ bản phòng 102</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
+        <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B71" t="str">
         <v>102</v>
@@ -8149,7 +8149,7 @@
         <v/>
       </c>
       <c r="D71" t="str">
-        <v>Nóng lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="E71" t="str">
         <v>NEW</v>
@@ -8161,27 +8161,27 @@
         <v>1</v>
       </c>
       <c r="H71">
-        <v>2600000</v>
+        <v>750000</v>
       </c>
       <c r="I71">
         <v>12</v>
       </c>
       <c r="J71" t="str">
-        <v>2026-06-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="K71" t="str">
-        <v>2027-06-01</v>
+        <v>2027-10-01</v>
       </c>
       <c r="L71">
-        <v>780000</v>
+        <v>225000</v>
       </c>
       <c r="M71" t="str">
-        <v>NL phòng 102</v>
+        <v>Quạt phòng 102</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
+        <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B72" t="str">
         <v>103</v>
@@ -8202,27 +8202,27 @@
         <v>1</v>
       </c>
       <c r="H72">
-        <v>4500000</v>
+        <v>4000000</v>
       </c>
       <c r="I72">
         <v>12</v>
       </c>
       <c r="J72" t="str">
-        <v>2026-06-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="K72" t="str">
-        <v>2027-06-01</v>
+        <v>2027-10-01</v>
       </c>
       <c r="L72">
-        <v>1350000</v>
+        <v>1200000</v>
       </c>
       <c r="M72" t="str">
-        <v>Giường phòng 103</v>
+        <v>NT cơ bản phòng 103</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
+        <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B73" t="str">
         <v>103</v>
@@ -8243,19 +8243,19 @@
         <v>1</v>
       </c>
       <c r="H73">
-        <v>800000</v>
+        <v>750000</v>
       </c>
       <c r="I73">
         <v>12</v>
       </c>
       <c r="J73" t="str">
-        <v>2026-06-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="K73" t="str">
-        <v>2027-06-01</v>
+        <v>2027-10-01</v>
       </c>
       <c r="L73">
-        <v>240000</v>
+        <v>225000</v>
       </c>
       <c r="M73" t="str">
         <v>Quạt phòng 103</v>
@@ -8263,7 +8263,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
+        <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B74" t="str">
         <v>103</v>
@@ -8284,19 +8284,19 @@
         <v>1</v>
       </c>
       <c r="H74">
-        <v>9200000</v>
+        <v>8500000</v>
       </c>
       <c r="I74">
         <v>24</v>
       </c>
       <c r="J74" t="str">
-        <v>2026-06-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="K74" t="str">
-        <v>2028-06-01</v>
+        <v>2028-10-01</v>
       </c>
       <c r="L74">
-        <v>2760000</v>
+        <v>2550000</v>
       </c>
       <c r="M74" t="str">
         <v>ĐH phòng 103</v>
@@ -8304,16 +8304,16 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
+        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B75" t="str">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C75" t="str">
         <v/>
       </c>
       <c r="D75" t="str">
-        <v>Nóng lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="E75" t="str">
         <v>NEW</v>
@@ -8325,36 +8325,36 @@
         <v>1</v>
       </c>
       <c r="H75">
-        <v>2600000</v>
+        <v>4000000</v>
       </c>
       <c r="I75">
         <v>12</v>
       </c>
       <c r="J75" t="str">
-        <v>2026-06-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="K75" t="str">
-        <v>2027-06-01</v>
+        <v>2027-03-01</v>
       </c>
       <c r="L75">
-        <v>780000</v>
+        <v>1200000</v>
       </c>
       <c r="M75" t="str">
-        <v>NL phòng 103</v>
+        <v>NT cơ bản phòng 101</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
+        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B76" t="str">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C76" t="str">
         <v/>
       </c>
       <c r="D76" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E76" t="str">
         <v>NEW</v>
@@ -8366,36 +8366,36 @@
         <v>1</v>
       </c>
       <c r="H76">
-        <v>4500000</v>
+        <v>750000</v>
       </c>
       <c r="I76">
         <v>12</v>
       </c>
       <c r="J76" t="str">
-        <v>2026-06-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="K76" t="str">
-        <v>2027-06-01</v>
+        <v>2027-03-01</v>
       </c>
       <c r="L76">
-        <v>1350000</v>
+        <v>225000</v>
       </c>
       <c r="M76" t="str">
-        <v>Giường phòng 104</v>
+        <v>Quạt phòng 101</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
+        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B77" t="str">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C77" t="str">
         <v/>
       </c>
       <c r="D77" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E77" t="str">
         <v>NEW</v>
@@ -8407,36 +8407,36 @@
         <v>1</v>
       </c>
       <c r="H77">
-        <v>800000</v>
+        <v>8500000</v>
       </c>
       <c r="I77">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J77" t="str">
-        <v>2026-06-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="K77" t="str">
-        <v>2027-06-01</v>
+        <v>2028-03-01</v>
       </c>
       <c r="L77">
-        <v>240000</v>
+        <v>2550000</v>
       </c>
       <c r="M77" t="str">
-        <v>Quạt phòng 104</v>
+        <v>ĐH phòng 101</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
+        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B78" t="str">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C78" t="str">
         <v/>
       </c>
       <c r="D78" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="E78" t="str">
         <v>NEW</v>
@@ -8448,36 +8448,36 @@
         <v>1</v>
       </c>
       <c r="H78">
-        <v>9200000</v>
+        <v>4000000</v>
       </c>
       <c r="I78">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J78" t="str">
-        <v>2026-06-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="K78" t="str">
-        <v>2028-06-01</v>
+        <v>2027-03-01</v>
       </c>
       <c r="L78">
-        <v>2760000</v>
+        <v>1200000</v>
       </c>
       <c r="M78" t="str">
-        <v>ĐH phòng 104</v>
+        <v>NT cơ bản phòng 102</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
+        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B79" t="str">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C79" t="str">
         <v/>
       </c>
       <c r="D79" t="str">
-        <v>Nóng lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="E79" t="str">
         <v>NEW</v>
@@ -8489,30 +8489,30 @@
         <v>1</v>
       </c>
       <c r="H79">
-        <v>2600000</v>
+        <v>750000</v>
       </c>
       <c r="I79">
         <v>12</v>
       </c>
       <c r="J79" t="str">
-        <v>2026-06-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="K79" t="str">
-        <v>2027-06-01</v>
+        <v>2027-03-01</v>
       </c>
       <c r="L79">
-        <v>780000</v>
+        <v>225000</v>
       </c>
       <c r="M79" t="str">
-        <v>NL phòng 104</v>
+        <v>Quạt phòng 102</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B80" t="str">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C80" t="str">
         <v/>
@@ -8530,30 +8530,30 @@
         <v>1</v>
       </c>
       <c r="H80">
-        <v>4500000</v>
+        <v>4000000</v>
       </c>
       <c r="I80">
         <v>12</v>
       </c>
       <c r="J80" t="str">
-        <v>2026-07-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="K80" t="str">
-        <v>2027-07-01</v>
+        <v>2027-03-01</v>
       </c>
       <c r="L80">
-        <v>1350000</v>
+        <v>1200000</v>
       </c>
       <c r="M80" t="str">
-        <v>Giường phòng 101</v>
+        <v>NT cơ bản phòng 103</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B81" t="str">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C81" t="str">
         <v/>
@@ -8571,30 +8571,30 @@
         <v>1</v>
       </c>
       <c r="H81">
-        <v>800000</v>
+        <v>750000</v>
       </c>
       <c r="I81">
         <v>12</v>
       </c>
       <c r="J81" t="str">
-        <v>2026-07-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="K81" t="str">
-        <v>2027-07-01</v>
+        <v>2027-03-01</v>
       </c>
       <c r="L81">
-        <v>240000</v>
+        <v>225000</v>
       </c>
       <c r="M81" t="str">
-        <v>Quạt phòng 101</v>
+        <v>Quạt phòng 103</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B82" t="str">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C82" t="str">
         <v/>
@@ -8612,36 +8612,36 @@
         <v>1</v>
       </c>
       <c r="H82">
-        <v>9200000</v>
+        <v>8500000</v>
       </c>
       <c r="I82">
         <v>24</v>
       </c>
       <c r="J82" t="str">
-        <v>2026-07-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="K82" t="str">
-        <v>2028-07-01</v>
+        <v>2028-03-01</v>
       </c>
       <c r="L82">
-        <v>2760000</v>
+        <v>2550000</v>
       </c>
       <c r="M82" t="str">
-        <v>ĐH phòng 101</v>
+        <v>ĐH phòng 103</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B83" t="str">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C83" t="str">
         <v/>
       </c>
       <c r="D83" t="str">
-        <v>Nóng lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="E83" t="str">
         <v>NEW</v>
@@ -8653,36 +8653,36 @@
         <v>1</v>
       </c>
       <c r="H83">
-        <v>2600000</v>
+        <v>4000000</v>
       </c>
       <c r="I83">
         <v>12</v>
       </c>
       <c r="J83" t="str">
-        <v>2026-07-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="K83" t="str">
-        <v>2027-07-01</v>
+        <v>2027-03-01</v>
       </c>
       <c r="L83">
-        <v>780000</v>
+        <v>1200000</v>
       </c>
       <c r="M83" t="str">
-        <v>NL phòng 101</v>
+        <v>NT cơ bản phòng 104</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B84" t="str">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C84" t="str">
         <v/>
       </c>
       <c r="D84" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E84" t="str">
         <v>NEW</v>
@@ -8694,36 +8694,36 @@
         <v>1</v>
       </c>
       <c r="H84">
-        <v>4500000</v>
+        <v>750000</v>
       </c>
       <c r="I84">
         <v>12</v>
       </c>
       <c r="J84" t="str">
-        <v>2026-07-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="K84" t="str">
-        <v>2027-07-01</v>
+        <v>2027-03-01</v>
       </c>
       <c r="L84">
-        <v>1350000</v>
+        <v>225000</v>
       </c>
       <c r="M84" t="str">
-        <v>Giường phòng 102</v>
+        <v>Quạt phòng 104</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B85" t="str">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C85" t="str">
         <v/>
       </c>
       <c r="D85" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="E85" t="str">
         <v>NEW</v>
@@ -8735,36 +8735,36 @@
         <v>1</v>
       </c>
       <c r="H85">
-        <v>800000</v>
+        <v>4000000</v>
       </c>
       <c r="I85">
         <v>12</v>
       </c>
       <c r="J85" t="str">
-        <v>2026-07-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K85" t="str">
-        <v>2027-07-01</v>
+        <v>2027-04-01</v>
       </c>
       <c r="L85">
-        <v>240000</v>
+        <v>1200000</v>
       </c>
       <c r="M85" t="str">
-        <v>Quạt phòng 102</v>
+        <v>NT cơ bản phòng 101</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B86" t="str">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C86" t="str">
         <v/>
       </c>
       <c r="D86" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="E86" t="str">
         <v>NEW</v>
@@ -8776,36 +8776,36 @@
         <v>1</v>
       </c>
       <c r="H86">
-        <v>9200000</v>
+        <v>750000</v>
       </c>
       <c r="I86">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J86" t="str">
-        <v>2026-07-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K86" t="str">
-        <v>2028-07-01</v>
+        <v>2027-04-01</v>
       </c>
       <c r="L86">
-        <v>2760000</v>
+        <v>225000</v>
       </c>
       <c r="M86" t="str">
-        <v>ĐH phòng 102</v>
+        <v>Quạt phòng 101</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B87" t="str">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C87" t="str">
         <v/>
       </c>
       <c r="D87" t="str">
-        <v>Nóng lạnh</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E87" t="str">
         <v>NEW</v>
@@ -8817,30 +8817,30 @@
         <v>1</v>
       </c>
       <c r="H87">
-        <v>2600000</v>
+        <v>8500000</v>
       </c>
       <c r="I87">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J87" t="str">
-        <v>2026-07-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K87" t="str">
-        <v>2027-07-01</v>
+        <v>2028-04-01</v>
       </c>
       <c r="L87">
-        <v>780000</v>
+        <v>2550000</v>
       </c>
       <c r="M87" t="str">
-        <v>NL phòng 102</v>
+        <v>ĐH phòng 101</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B88" t="str">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C88" t="str">
         <v/>
@@ -8858,30 +8858,30 @@
         <v>1</v>
       </c>
       <c r="H88">
-        <v>4500000</v>
+        <v>4000000</v>
       </c>
       <c r="I88">
         <v>12</v>
       </c>
       <c r="J88" t="str">
-        <v>2026-07-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K88" t="str">
-        <v>2027-07-01</v>
+        <v>2027-04-01</v>
       </c>
       <c r="L88">
-        <v>1350000</v>
+        <v>1200000</v>
       </c>
       <c r="M88" t="str">
-        <v>Giường phòng 103</v>
+        <v>NT cơ bản phòng 102</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B89" t="str">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C89" t="str">
         <v/>
@@ -8899,27 +8899,27 @@
         <v>1</v>
       </c>
       <c r="H89">
-        <v>800000</v>
+        <v>750000</v>
       </c>
       <c r="I89">
         <v>12</v>
       </c>
       <c r="J89" t="str">
-        <v>2026-07-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K89" t="str">
-        <v>2027-07-01</v>
+        <v>2027-04-01</v>
       </c>
       <c r="L89">
-        <v>240000</v>
+        <v>225000</v>
       </c>
       <c r="M89" t="str">
-        <v>Quạt phòng 103</v>
+        <v>Quạt phòng 102</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B90" t="str">
         <v>103</v>
@@ -8928,7 +8928,7 @@
         <v/>
       </c>
       <c r="D90" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="E90" t="str">
         <v>NEW</v>
@@ -8940,27 +8940,27 @@
         <v>1</v>
       </c>
       <c r="H90">
-        <v>9200000</v>
+        <v>4000000</v>
       </c>
       <c r="I90">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J90" t="str">
-        <v>2026-07-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K90" t="str">
-        <v>2028-07-01</v>
+        <v>2027-04-01</v>
       </c>
       <c r="L90">
-        <v>2760000</v>
+        <v>1200000</v>
       </c>
       <c r="M90" t="str">
-        <v>ĐH phòng 103</v>
+        <v>NT cơ bản phòng 103</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B91" t="str">
         <v>103</v>
@@ -8969,7 +8969,7 @@
         <v/>
       </c>
       <c r="D91" t="str">
-        <v>Nóng lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="E91" t="str">
         <v>NEW</v>
@@ -8981,36 +8981,36 @@
         <v>1</v>
       </c>
       <c r="H91">
-        <v>2600000</v>
+        <v>750000</v>
       </c>
       <c r="I91">
         <v>12</v>
       </c>
       <c r="J91" t="str">
-        <v>2026-07-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K91" t="str">
-        <v>2027-07-01</v>
+        <v>2027-04-01</v>
       </c>
       <c r="L91">
-        <v>780000</v>
+        <v>225000</v>
       </c>
       <c r="M91" t="str">
-        <v>NL phòng 103</v>
+        <v>Quạt phòng 103</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B92" t="str">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C92" t="str">
         <v/>
       </c>
       <c r="D92" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E92" t="str">
         <v>NEW</v>
@@ -9022,36 +9022,36 @@
         <v>1</v>
       </c>
       <c r="H92">
-        <v>4500000</v>
+        <v>8500000</v>
       </c>
       <c r="I92">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J92" t="str">
-        <v>2026-07-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K92" t="str">
-        <v>2027-07-01</v>
+        <v>2028-04-01</v>
       </c>
       <c r="L92">
-        <v>1350000</v>
+        <v>2550000</v>
       </c>
       <c r="M92" t="str">
-        <v>Giường phòng 104</v>
+        <v>ĐH phòng 103</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B93" t="str">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C93" t="str">
         <v/>
       </c>
       <c r="D93" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="E93" t="str">
         <v>NEW</v>
@@ -9063,36 +9063,36 @@
         <v>1</v>
       </c>
       <c r="H93">
-        <v>800000</v>
+        <v>4000000</v>
       </c>
       <c r="I93">
         <v>12</v>
       </c>
       <c r="J93" t="str">
-        <v>2026-07-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="K93" t="str">
-        <v>2027-07-01</v>
+        <v>2027-05-01</v>
       </c>
       <c r="L93">
-        <v>240000</v>
+        <v>1200000</v>
       </c>
       <c r="M93" t="str">
-        <v>Quạt phòng 104</v>
+        <v>NT cơ bản phòng 101</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B94" t="str">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C94" t="str">
         <v/>
       </c>
       <c r="D94" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="E94" t="str">
         <v>NEW</v>
@@ -9104,36 +9104,36 @@
         <v>1</v>
       </c>
       <c r="H94">
-        <v>9200000</v>
+        <v>750000</v>
       </c>
       <c r="I94">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J94" t="str">
-        <v>2026-07-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="K94" t="str">
-        <v>2028-07-01</v>
+        <v>2027-05-01</v>
       </c>
       <c r="L94">
-        <v>2760000</v>
+        <v>225000</v>
       </c>
       <c r="M94" t="str">
-        <v>ĐH phòng 104</v>
+        <v>Quạt phòng 101</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B95" t="str">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C95" t="str">
         <v/>
       </c>
       <c r="D95" t="str">
-        <v>Nóng lạnh</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E95" t="str">
         <v>NEW</v>
@@ -9145,30 +9145,30 @@
         <v>1</v>
       </c>
       <c r="H95">
-        <v>2600000</v>
+        <v>8500000</v>
       </c>
       <c r="I95">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J95" t="str">
-        <v>2026-07-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="K95" t="str">
-        <v>2027-07-01</v>
+        <v>2028-05-01</v>
       </c>
       <c r="L95">
-        <v>780000</v>
+        <v>2550000</v>
       </c>
       <c r="M95" t="str">
-        <v>NL phòng 104</v>
+        <v>ĐH phòng 101</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B96" t="str">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C96" t="str">
         <v/>
@@ -9186,30 +9186,30 @@
         <v>1</v>
       </c>
       <c r="H96">
-        <v>4500000</v>
+        <v>4000000</v>
       </c>
       <c r="I96">
         <v>12</v>
       </c>
       <c r="J96" t="str">
-        <v>2026-08-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="K96" t="str">
-        <v>2027-08-01</v>
+        <v>2027-05-01</v>
       </c>
       <c r="L96">
-        <v>1350000</v>
+        <v>1200000</v>
       </c>
       <c r="M96" t="str">
-        <v>Giường phòng 101</v>
+        <v>NT cơ bản phòng 102</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B97" t="str">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C97" t="str">
         <v/>
@@ -9227,36 +9227,36 @@
         <v>1</v>
       </c>
       <c r="H97">
-        <v>800000</v>
+        <v>750000</v>
       </c>
       <c r="I97">
         <v>12</v>
       </c>
       <c r="J97" t="str">
-        <v>2026-08-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="K97" t="str">
-        <v>2027-08-01</v>
+        <v>2027-05-01</v>
       </c>
       <c r="L97">
-        <v>240000</v>
+        <v>225000</v>
       </c>
       <c r="M97" t="str">
-        <v>Quạt phòng 101</v>
+        <v>Quạt phòng 102</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B98" t="str">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C98" t="str">
         <v/>
       </c>
       <c r="D98" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="E98" t="str">
         <v>NEW</v>
@@ -9268,36 +9268,36 @@
         <v>1</v>
       </c>
       <c r="H98">
-        <v>9200000</v>
+        <v>4000000</v>
       </c>
       <c r="I98">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J98" t="str">
-        <v>2026-08-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="K98" t="str">
-        <v>2028-08-01</v>
+        <v>2027-05-01</v>
       </c>
       <c r="L98">
-        <v>2760000</v>
+        <v>1200000</v>
       </c>
       <c r="M98" t="str">
-        <v>ĐH phòng 101</v>
+        <v>NT cơ bản phòng 103</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B99" t="str">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C99" t="str">
         <v/>
       </c>
       <c r="D99" t="str">
-        <v>Nóng lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="E99" t="str">
         <v>NEW</v>
@@ -9309,36 +9309,36 @@
         <v>1</v>
       </c>
       <c r="H99">
-        <v>2600000</v>
+        <v>750000</v>
       </c>
       <c r="I99">
         <v>12</v>
       </c>
       <c r="J99" t="str">
-        <v>2026-08-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="K99" t="str">
-        <v>2027-08-01</v>
+        <v>2027-05-01</v>
       </c>
       <c r="L99">
-        <v>780000</v>
+        <v>225000</v>
       </c>
       <c r="M99" t="str">
-        <v>NL phòng 101</v>
+        <v>Quạt phòng 103</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B100" t="str">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C100" t="str">
         <v/>
       </c>
       <c r="D100" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E100" t="str">
         <v>NEW</v>
@@ -9350,36 +9350,36 @@
         <v>1</v>
       </c>
       <c r="H100">
-        <v>4500000</v>
+        <v>8500000</v>
       </c>
       <c r="I100">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J100" t="str">
-        <v>2026-08-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="K100" t="str">
-        <v>2027-08-01</v>
+        <v>2028-05-01</v>
       </c>
       <c r="L100">
-        <v>1350000</v>
+        <v>2550000</v>
       </c>
       <c r="M100" t="str">
-        <v>Giường phòng 102</v>
+        <v>ĐH phòng 103</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B101" t="str">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C101" t="str">
         <v/>
       </c>
       <c r="D101" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="E101" t="str">
         <v>NEW</v>
@@ -9391,36 +9391,36 @@
         <v>1</v>
       </c>
       <c r="H101">
-        <v>800000</v>
+        <v>4000000</v>
       </c>
       <c r="I101">
         <v>12</v>
       </c>
       <c r="J101" t="str">
-        <v>2026-08-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="K101" t="str">
-        <v>2027-08-01</v>
+        <v>2027-05-01</v>
       </c>
       <c r="L101">
-        <v>240000</v>
+        <v>1200000</v>
       </c>
       <c r="M101" t="str">
-        <v>Quạt phòng 102</v>
+        <v>NT cơ bản phòng 104</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B102" t="str">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C102" t="str">
         <v/>
       </c>
       <c r="D102" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="E102" t="str">
         <v>NEW</v>
@@ -9432,36 +9432,36 @@
         <v>1</v>
       </c>
       <c r="H102">
-        <v>9200000</v>
+        <v>750000</v>
       </c>
       <c r="I102">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J102" t="str">
-        <v>2026-08-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="K102" t="str">
-        <v>2028-08-01</v>
+        <v>2027-05-01</v>
       </c>
       <c r="L102">
-        <v>2760000</v>
+        <v>225000</v>
       </c>
       <c r="M102" t="str">
-        <v>ĐH phòng 102</v>
+        <v>Quạt phòng 104</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B103" t="str">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C103" t="str">
         <v/>
       </c>
       <c r="D103" t="str">
-        <v>Nóng lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="E103" t="str">
         <v>NEW</v>
@@ -9473,36 +9473,36 @@
         <v>1</v>
       </c>
       <c r="H103">
-        <v>2600000</v>
+        <v>4500000</v>
       </c>
       <c r="I103">
         <v>12</v>
       </c>
       <c r="J103" t="str">
-        <v>2026-08-01</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K103" t="str">
-        <v>2027-08-01</v>
+        <v>2027-06-01</v>
       </c>
       <c r="L103">
-        <v>780000</v>
+        <v>1350000</v>
       </c>
       <c r="M103" t="str">
-        <v>NL phòng 102</v>
+        <v>Giường phòng 101</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B104" t="str">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C104" t="str">
         <v/>
       </c>
       <c r="D104" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E104" t="str">
         <v>NEW</v>
@@ -9514,36 +9514,36 @@
         <v>1</v>
       </c>
       <c r="H104">
-        <v>4500000</v>
+        <v>800000</v>
       </c>
       <c r="I104">
         <v>12</v>
       </c>
       <c r="J104" t="str">
-        <v>2026-08-01</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K104" t="str">
-        <v>2027-08-01</v>
+        <v>2027-06-01</v>
       </c>
       <c r="L104">
-        <v>1350000</v>
+        <v>240000</v>
       </c>
       <c r="M104" t="str">
-        <v>Giường phòng 103</v>
+        <v>Quạt phòng 101</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B105" t="str">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C105" t="str">
         <v/>
       </c>
       <c r="D105" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E105" t="str">
         <v>NEW</v>
@@ -9555,36 +9555,36 @@
         <v>1</v>
       </c>
       <c r="H105">
-        <v>800000</v>
+        <v>9200000</v>
       </c>
       <c r="I105">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J105" t="str">
-        <v>2026-08-01</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K105" t="str">
-        <v>2027-08-01</v>
+        <v>2028-06-01</v>
       </c>
       <c r="L105">
-        <v>240000</v>
+        <v>2760000</v>
       </c>
       <c r="M105" t="str">
-        <v>Quạt phòng 103</v>
+        <v>ĐH phòng 101</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B106" t="str">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C106" t="str">
         <v/>
       </c>
       <c r="D106" t="str">
-        <v>Điều hòa</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E106" t="str">
         <v>NEW</v>
@@ -9596,36 +9596,36 @@
         <v>1</v>
       </c>
       <c r="H106">
-        <v>9200000</v>
+        <v>2600000</v>
       </c>
       <c r="I106">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J106" t="str">
-        <v>2026-08-01</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K106" t="str">
-        <v>2028-08-01</v>
+        <v>2027-06-01</v>
       </c>
       <c r="L106">
-        <v>2760000</v>
+        <v>780000</v>
       </c>
       <c r="M106" t="str">
-        <v>ĐH phòng 103</v>
+        <v>NL phòng 101</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B107" t="str">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C107" t="str">
         <v/>
       </c>
       <c r="D107" t="str">
-        <v>Nóng lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="E107" t="str">
         <v>NEW</v>
@@ -9637,36 +9637,36 @@
         <v>1</v>
       </c>
       <c r="H107">
-        <v>2600000</v>
+        <v>4500000</v>
       </c>
       <c r="I107">
         <v>12</v>
       </c>
       <c r="J107" t="str">
-        <v>2026-08-01</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K107" t="str">
-        <v>2027-08-01</v>
+        <v>2027-06-01</v>
       </c>
       <c r="L107">
-        <v>780000</v>
+        <v>1350000</v>
       </c>
       <c r="M107" t="str">
-        <v>NL phòng 103</v>
+        <v>Giường phòng 102</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B108" t="str">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C108" t="str">
         <v/>
       </c>
       <c r="D108" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E108" t="str">
         <v>NEW</v>
@@ -9678,36 +9678,36 @@
         <v>1</v>
       </c>
       <c r="H108">
-        <v>4500000</v>
+        <v>800000</v>
       </c>
       <c r="I108">
         <v>12</v>
       </c>
       <c r="J108" t="str">
-        <v>2026-08-01</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K108" t="str">
-        <v>2027-08-01</v>
+        <v>2027-06-01</v>
       </c>
       <c r="L108">
-        <v>1350000</v>
+        <v>240000</v>
       </c>
       <c r="M108" t="str">
-        <v>Giường phòng 104</v>
+        <v>Quạt phòng 102</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B109" t="str">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C109" t="str">
         <v/>
       </c>
       <c r="D109" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E109" t="str">
         <v>NEW</v>
@@ -9719,36 +9719,36 @@
         <v>1</v>
       </c>
       <c r="H109">
-        <v>800000</v>
+        <v>9200000</v>
       </c>
       <c r="I109">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J109" t="str">
-        <v>2026-08-01</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K109" t="str">
-        <v>2027-08-01</v>
+        <v>2028-06-01</v>
       </c>
       <c r="L109">
-        <v>240000</v>
+        <v>2760000</v>
       </c>
       <c r="M109" t="str">
-        <v>Quạt phòng 104</v>
+        <v>ĐH phòng 102</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B110" t="str">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C110" t="str">
         <v/>
       </c>
       <c r="D110" t="str">
-        <v>Điều hòa</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E110" t="str">
         <v>NEW</v>
@@ -9760,36 +9760,36 @@
         <v>1</v>
       </c>
       <c r="H110">
-        <v>9200000</v>
+        <v>2600000</v>
       </c>
       <c r="I110">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J110" t="str">
-        <v>2026-08-01</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K110" t="str">
-        <v>2028-08-01</v>
+        <v>2027-06-01</v>
       </c>
       <c r="L110">
-        <v>2760000</v>
+        <v>780000</v>
       </c>
       <c r="M110" t="str">
-        <v>ĐH phòng 104</v>
+        <v>NL phòng 102</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B111" t="str">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C111" t="str">
         <v/>
       </c>
       <c r="D111" t="str">
-        <v>Nóng lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="E111" t="str">
         <v>NEW</v>
@@ -9801,36 +9801,36 @@
         <v>1</v>
       </c>
       <c r="H111">
-        <v>2600000</v>
+        <v>4500000</v>
       </c>
       <c r="I111">
         <v>12</v>
       </c>
       <c r="J111" t="str">
-        <v>2026-08-01</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K111" t="str">
-        <v>2027-08-01</v>
+        <v>2027-06-01</v>
       </c>
       <c r="L111">
-        <v>780000</v>
+        <v>1350000</v>
       </c>
       <c r="M111" t="str">
-        <v>NL phòng 104</v>
+        <v>Giường phòng 103</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B112" t="str">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C112" t="str">
         <v/>
       </c>
       <c r="D112" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E112" t="str">
         <v>NEW</v>
@@ -9842,36 +9842,36 @@
         <v>1</v>
       </c>
       <c r="H112">
-        <v>4500000</v>
+        <v>800000</v>
       </c>
       <c r="I112">
         <v>12</v>
       </c>
       <c r="J112" t="str">
-        <v>2026-09-01</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K112" t="str">
-        <v>2027-09-01</v>
+        <v>2027-06-01</v>
       </c>
       <c r="L112">
-        <v>1350000</v>
+        <v>240000</v>
       </c>
       <c r="M112" t="str">
-        <v>Giường phòng 101</v>
+        <v>Quạt phòng 103</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B113" t="str">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C113" t="str">
         <v/>
       </c>
       <c r="D113" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E113" t="str">
         <v>NEW</v>
@@ -9883,36 +9883,36 @@
         <v>1</v>
       </c>
       <c r="H113">
-        <v>800000</v>
+        <v>9200000</v>
       </c>
       <c r="I113">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J113" t="str">
-        <v>2026-09-01</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K113" t="str">
-        <v>2027-09-01</v>
+        <v>2028-06-01</v>
       </c>
       <c r="L113">
-        <v>240000</v>
+        <v>2760000</v>
       </c>
       <c r="M113" t="str">
-        <v>Quạt phòng 101</v>
+        <v>ĐH phòng 103</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B114" t="str">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C114" t="str">
         <v/>
       </c>
       <c r="D114" t="str">
-        <v>Điều hòa</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E114" t="str">
         <v>NEW</v>
@@ -9924,36 +9924,36 @@
         <v>1</v>
       </c>
       <c r="H114">
-        <v>9200000</v>
+        <v>2600000</v>
       </c>
       <c r="I114">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J114" t="str">
-        <v>2026-09-01</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K114" t="str">
-        <v>2028-09-01</v>
+        <v>2027-06-01</v>
       </c>
       <c r="L114">
-        <v>2760000</v>
+        <v>780000</v>
       </c>
       <c r="M114" t="str">
-        <v>ĐH phòng 101</v>
+        <v>NL phòng 103</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B115" t="str">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C115" t="str">
         <v/>
       </c>
       <c r="D115" t="str">
-        <v>Nóng lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="E115" t="str">
         <v>NEW</v>
@@ -9965,36 +9965,36 @@
         <v>1</v>
       </c>
       <c r="H115">
-        <v>2600000</v>
+        <v>4500000</v>
       </c>
       <c r="I115">
         <v>12</v>
       </c>
       <c r="J115" t="str">
-        <v>2026-09-01</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K115" t="str">
-        <v>2027-09-01</v>
+        <v>2027-06-01</v>
       </c>
       <c r="L115">
-        <v>780000</v>
+        <v>1350000</v>
       </c>
       <c r="M115" t="str">
-        <v>NL phòng 101</v>
+        <v>Giường phòng 104</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B116" t="str">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C116" t="str">
         <v/>
       </c>
       <c r="D116" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E116" t="str">
         <v>NEW</v>
@@ -10006,36 +10006,36 @@
         <v>1</v>
       </c>
       <c r="H116">
-        <v>4500000</v>
+        <v>800000</v>
       </c>
       <c r="I116">
         <v>12</v>
       </c>
       <c r="J116" t="str">
-        <v>2026-09-01</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K116" t="str">
-        <v>2027-09-01</v>
+        <v>2027-06-01</v>
       </c>
       <c r="L116">
-        <v>1350000</v>
+        <v>240000</v>
       </c>
       <c r="M116" t="str">
-        <v>Giường phòng 102</v>
+        <v>Quạt phòng 104</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B117" t="str">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C117" t="str">
         <v/>
       </c>
       <c r="D117" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E117" t="str">
         <v>NEW</v>
@@ -10047,36 +10047,36 @@
         <v>1</v>
       </c>
       <c r="H117">
-        <v>800000</v>
+        <v>9200000</v>
       </c>
       <c r="I117">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J117" t="str">
-        <v>2026-09-01</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K117" t="str">
-        <v>2027-09-01</v>
+        <v>2028-06-01</v>
       </c>
       <c r="L117">
-        <v>240000</v>
+        <v>2760000</v>
       </c>
       <c r="M117" t="str">
-        <v>Quạt phòng 102</v>
+        <v>ĐH phòng 104</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B118" t="str">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C118" t="str">
         <v/>
       </c>
       <c r="D118" t="str">
-        <v>Điều hòa</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E118" t="str">
         <v>NEW</v>
@@ -10088,36 +10088,36 @@
         <v>1</v>
       </c>
       <c r="H118">
-        <v>9200000</v>
+        <v>2600000</v>
       </c>
       <c r="I118">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J118" t="str">
-        <v>2026-09-01</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K118" t="str">
-        <v>2028-09-01</v>
+        <v>2027-06-01</v>
       </c>
       <c r="L118">
-        <v>2760000</v>
+        <v>780000</v>
       </c>
       <c r="M118" t="str">
-        <v>ĐH phòng 102</v>
+        <v>NL phòng 104</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B119" t="str">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C119" t="str">
         <v/>
       </c>
       <c r="D119" t="str">
-        <v>Nóng lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="E119" t="str">
         <v>NEW</v>
@@ -10129,36 +10129,36 @@
         <v>1</v>
       </c>
       <c r="H119">
-        <v>2600000</v>
+        <v>4500000</v>
       </c>
       <c r="I119">
         <v>12</v>
       </c>
       <c r="J119" t="str">
-        <v>2026-09-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="K119" t="str">
-        <v>2027-09-01</v>
+        <v>2027-07-01</v>
       </c>
       <c r="L119">
-        <v>780000</v>
+        <v>1350000</v>
       </c>
       <c r="M119" t="str">
-        <v>NL phòng 102</v>
+        <v>Giường phòng 101</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B120" t="str">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C120" t="str">
         <v/>
       </c>
       <c r="D120" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E120" t="str">
         <v>NEW</v>
@@ -10170,36 +10170,36 @@
         <v>1</v>
       </c>
       <c r="H120">
-        <v>4500000</v>
+        <v>800000</v>
       </c>
       <c r="I120">
         <v>12</v>
       </c>
       <c r="J120" t="str">
-        <v>2026-09-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="K120" t="str">
-        <v>2027-09-01</v>
+        <v>2027-07-01</v>
       </c>
       <c r="L120">
-        <v>1350000</v>
+        <v>240000</v>
       </c>
       <c r="M120" t="str">
-        <v>Giường phòng 103</v>
+        <v>Quạt phòng 101</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B121" t="str">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C121" t="str">
         <v/>
       </c>
       <c r="D121" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E121" t="str">
         <v>NEW</v>
@@ -10211,36 +10211,36 @@
         <v>1</v>
       </c>
       <c r="H121">
-        <v>800000</v>
+        <v>9200000</v>
       </c>
       <c r="I121">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J121" t="str">
-        <v>2026-09-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="K121" t="str">
-        <v>2027-09-01</v>
+        <v>2028-07-01</v>
       </c>
       <c r="L121">
-        <v>240000</v>
+        <v>2760000</v>
       </c>
       <c r="M121" t="str">
-        <v>Quạt phòng 103</v>
+        <v>ĐH phòng 101</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B122" t="str">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C122" t="str">
         <v/>
       </c>
       <c r="D122" t="str">
-        <v>Điều hòa</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E122" t="str">
         <v>NEW</v>
@@ -10252,36 +10252,36 @@
         <v>1</v>
       </c>
       <c r="H122">
-        <v>9200000</v>
+        <v>2600000</v>
       </c>
       <c r="I122">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J122" t="str">
-        <v>2026-09-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="K122" t="str">
-        <v>2028-09-01</v>
+        <v>2027-07-01</v>
       </c>
       <c r="L122">
-        <v>2760000</v>
+        <v>780000</v>
       </c>
       <c r="M122" t="str">
-        <v>ĐH phòng 103</v>
+        <v>NL phòng 101</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B123" t="str">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C123" t="str">
         <v/>
       </c>
       <c r="D123" t="str">
-        <v>Nóng lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="E123" t="str">
         <v>NEW</v>
@@ -10293,36 +10293,36 @@
         <v>1</v>
       </c>
       <c r="H123">
-        <v>2600000</v>
+        <v>4500000</v>
       </c>
       <c r="I123">
         <v>12</v>
       </c>
       <c r="J123" t="str">
-        <v>2026-09-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="K123" t="str">
-        <v>2027-09-01</v>
+        <v>2027-07-01</v>
       </c>
       <c r="L123">
-        <v>780000</v>
+        <v>1350000</v>
       </c>
       <c r="M123" t="str">
-        <v>NL phòng 103</v>
+        <v>Giường phòng 102</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B124" t="str">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C124" t="str">
         <v/>
       </c>
       <c r="D124" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E124" t="str">
         <v>NEW</v>
@@ -10334,36 +10334,36 @@
         <v>1</v>
       </c>
       <c r="H124">
-        <v>4500000</v>
+        <v>800000</v>
       </c>
       <c r="I124">
         <v>12</v>
       </c>
       <c r="J124" t="str">
-        <v>2026-09-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="K124" t="str">
-        <v>2027-09-01</v>
+        <v>2027-07-01</v>
       </c>
       <c r="L124">
-        <v>1350000</v>
+        <v>240000</v>
       </c>
       <c r="M124" t="str">
-        <v>Giường phòng 104</v>
+        <v>Quạt phòng 102</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B125" t="str">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C125" t="str">
         <v/>
       </c>
       <c r="D125" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E125" t="str">
         <v>NEW</v>
@@ -10375,36 +10375,36 @@
         <v>1</v>
       </c>
       <c r="H125">
-        <v>800000</v>
+        <v>9200000</v>
       </c>
       <c r="I125">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J125" t="str">
-        <v>2026-09-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="K125" t="str">
-        <v>2027-09-01</v>
+        <v>2028-07-01</v>
       </c>
       <c r="L125">
-        <v>240000</v>
+        <v>2760000</v>
       </c>
       <c r="M125" t="str">
-        <v>Quạt phòng 104</v>
+        <v>ĐH phòng 102</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B126" t="str">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C126" t="str">
         <v/>
       </c>
       <c r="D126" t="str">
-        <v>Điều hòa</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E126" t="str">
         <v>NEW</v>
@@ -10416,36 +10416,36 @@
         <v>1</v>
       </c>
       <c r="H126">
-        <v>9200000</v>
+        <v>2600000</v>
       </c>
       <c r="I126">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J126" t="str">
-        <v>2026-09-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="K126" t="str">
-        <v>2028-09-01</v>
+        <v>2027-07-01</v>
       </c>
       <c r="L126">
-        <v>2760000</v>
+        <v>780000</v>
       </c>
       <c r="M126" t="str">
-        <v>ĐH phòng 104</v>
+        <v>NL phòng 102</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B127" t="str">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C127" t="str">
         <v/>
       </c>
       <c r="D127" t="str">
-        <v>Nóng lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="E127" t="str">
         <v>NEW</v>
@@ -10457,36 +10457,36 @@
         <v>1</v>
       </c>
       <c r="H127">
-        <v>2600000</v>
+        <v>4500000</v>
       </c>
       <c r="I127">
         <v>12</v>
       </c>
       <c r="J127" t="str">
-        <v>2026-09-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="K127" t="str">
-        <v>2027-09-01</v>
+        <v>2027-07-01</v>
       </c>
       <c r="L127">
-        <v>780000</v>
+        <v>1350000</v>
       </c>
       <c r="M127" t="str">
-        <v>NL phòng 104</v>
+        <v>Giường phòng 103</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B128" t="str">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C128" t="str">
         <v/>
       </c>
       <c r="D128" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E128" t="str">
         <v>NEW</v>
@@ -10498,36 +10498,36 @@
         <v>1</v>
       </c>
       <c r="H128">
-        <v>4000000</v>
+        <v>800000</v>
       </c>
       <c r="I128">
         <v>12</v>
       </c>
       <c r="J128" t="str">
-        <v>2026-10-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="K128" t="str">
-        <v>2027-10-01</v>
+        <v>2027-07-01</v>
       </c>
       <c r="L128">
-        <v>1200000</v>
+        <v>240000</v>
       </c>
       <c r="M128" t="str">
-        <v>NT cơ bản phòng 101</v>
+        <v>Quạt phòng 103</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B129" t="str">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C129" t="str">
         <v/>
       </c>
       <c r="D129" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E129" t="str">
         <v>NEW</v>
@@ -10539,36 +10539,36 @@
         <v>1</v>
       </c>
       <c r="H129">
-        <v>750000</v>
+        <v>9200000</v>
       </c>
       <c r="I129">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J129" t="str">
-        <v>2026-10-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="K129" t="str">
-        <v>2027-10-01</v>
+        <v>2028-07-01</v>
       </c>
       <c r="L129">
-        <v>225000</v>
+        <v>2760000</v>
       </c>
       <c r="M129" t="str">
-        <v>Quạt phòng 101</v>
+        <v>ĐH phòng 103</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B130" t="str">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C130" t="str">
         <v/>
       </c>
       <c r="D130" t="str">
-        <v>Giường</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E130" t="str">
         <v>NEW</v>
@@ -10580,36 +10580,36 @@
         <v>1</v>
       </c>
       <c r="H130">
-        <v>4000000</v>
+        <v>2600000</v>
       </c>
       <c r="I130">
         <v>12</v>
       </c>
       <c r="J130" t="str">
-        <v>2026-10-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="K130" t="str">
-        <v>2027-10-01</v>
+        <v>2027-07-01</v>
       </c>
       <c r="L130">
-        <v>1200000</v>
+        <v>780000</v>
       </c>
       <c r="M130" t="str">
-        <v>NT cơ bản phòng 102</v>
+        <v>NL phòng 103</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B131" t="str">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C131" t="str">
         <v/>
       </c>
       <c r="D131" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="E131" t="str">
         <v>NEW</v>
@@ -10621,36 +10621,36 @@
         <v>1</v>
       </c>
       <c r="H131">
-        <v>8500000</v>
+        <v>4500000</v>
       </c>
       <c r="I131">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J131" t="str">
-        <v>2026-10-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="K131" t="str">
-        <v>2028-10-01</v>
+        <v>2027-07-01</v>
       </c>
       <c r="L131">
-        <v>2550000</v>
+        <v>1350000</v>
       </c>
       <c r="M131" t="str">
-        <v>ĐH phòng 102</v>
+        <v>Giường phòng 104</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B132" t="str">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C132" t="str">
         <v/>
       </c>
       <c r="D132" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E132" t="str">
         <v>NEW</v>
@@ -10662,36 +10662,36 @@
         <v>1</v>
       </c>
       <c r="H132">
-        <v>4000000</v>
+        <v>800000</v>
       </c>
       <c r="I132">
         <v>12</v>
       </c>
       <c r="J132" t="str">
-        <v>2026-10-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="K132" t="str">
-        <v>2027-10-01</v>
+        <v>2027-07-01</v>
       </c>
       <c r="L132">
-        <v>1200000</v>
+        <v>240000</v>
       </c>
       <c r="M132" t="str">
-        <v>NT cơ bản phòng 103</v>
+        <v>Quạt phòng 104</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B133" t="str">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C133" t="str">
         <v/>
       </c>
       <c r="D133" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E133" t="str">
         <v>NEW</v>
@@ -10703,36 +10703,36 @@
         <v>1</v>
       </c>
       <c r="H133">
-        <v>750000</v>
+        <v>9200000</v>
       </c>
       <c r="I133">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J133" t="str">
-        <v>2026-10-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="K133" t="str">
-        <v>2027-10-01</v>
+        <v>2028-07-01</v>
       </c>
       <c r="L133">
-        <v>225000</v>
+        <v>2760000</v>
       </c>
       <c r="M133" t="str">
-        <v>Quạt phòng 103</v>
+        <v>ĐH phòng 104</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B134" t="str">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C134" t="str">
         <v/>
       </c>
       <c r="D134" t="str">
-        <v>Giường</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E134" t="str">
         <v>NEW</v>
@@ -10744,27 +10744,27 @@
         <v>1</v>
       </c>
       <c r="H134">
-        <v>4000000</v>
+        <v>2600000</v>
       </c>
       <c r="I134">
         <v>12</v>
       </c>
       <c r="J134" t="str">
-        <v>2026-03-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="K134" t="str">
-        <v>2027-03-01</v>
+        <v>2027-07-01</v>
       </c>
       <c r="L134">
-        <v>1200000</v>
+        <v>780000</v>
       </c>
       <c r="M134" t="str">
-        <v>NT cơ bản phòng 101</v>
+        <v>NL phòng 104</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B135" t="str">
         <v>101</v>
@@ -10773,7 +10773,7 @@
         <v/>
       </c>
       <c r="D135" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="E135" t="str">
         <v>NEW</v>
@@ -10785,36 +10785,36 @@
         <v>1</v>
       </c>
       <c r="H135">
-        <v>750000</v>
+        <v>4500000</v>
       </c>
       <c r="I135">
         <v>12</v>
       </c>
       <c r="J135" t="str">
-        <v>2026-03-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K135" t="str">
-        <v>2027-03-01</v>
+        <v>2027-08-01</v>
       </c>
       <c r="L135">
-        <v>225000</v>
+        <v>1350000</v>
       </c>
       <c r="M135" t="str">
-        <v>Quạt phòng 101</v>
+        <v>Giường phòng 101</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B136" t="str">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C136" t="str">
         <v/>
       </c>
       <c r="D136" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E136" t="str">
         <v>NEW</v>
@@ -10826,30 +10826,30 @@
         <v>1</v>
       </c>
       <c r="H136">
-        <v>4000000</v>
+        <v>800000</v>
       </c>
       <c r="I136">
         <v>12</v>
       </c>
       <c r="J136" t="str">
-        <v>2026-03-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K136" t="str">
-        <v>2027-03-01</v>
+        <v>2027-08-01</v>
       </c>
       <c r="L136">
-        <v>1200000</v>
+        <v>240000</v>
       </c>
       <c r="M136" t="str">
-        <v>NT cơ bản phòng 102</v>
+        <v>Quạt phòng 101</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B137" t="str">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C137" t="str">
         <v/>
@@ -10867,36 +10867,36 @@
         <v>1</v>
       </c>
       <c r="H137">
-        <v>8500000</v>
+        <v>9200000</v>
       </c>
       <c r="I137">
         <v>24</v>
       </c>
       <c r="J137" t="str">
-        <v>2026-03-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K137" t="str">
-        <v>2028-03-01</v>
+        <v>2028-08-01</v>
       </c>
       <c r="L137">
-        <v>2550000</v>
+        <v>2760000</v>
       </c>
       <c r="M137" t="str">
-        <v>ĐH phòng 102</v>
+        <v>ĐH phòng 101</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B138" t="str">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C138" t="str">
         <v/>
       </c>
       <c r="D138" t="str">
-        <v>Giường</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E138" t="str">
         <v>NEW</v>
@@ -10908,36 +10908,36 @@
         <v>1</v>
       </c>
       <c r="H138">
-        <v>4000000</v>
+        <v>2600000</v>
       </c>
       <c r="I138">
         <v>12</v>
       </c>
       <c r="J138" t="str">
-        <v>2026-03-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K138" t="str">
-        <v>2027-03-01</v>
+        <v>2027-08-01</v>
       </c>
       <c r="L138">
-        <v>1200000</v>
+        <v>780000</v>
       </c>
       <c r="M138" t="str">
-        <v>NT cơ bản phòng 103</v>
+        <v>NL phòng 101</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B139" t="str">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C139" t="str">
         <v/>
       </c>
       <c r="D139" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="E139" t="str">
         <v>NEW</v>
@@ -10949,36 +10949,36 @@
         <v>1</v>
       </c>
       <c r="H139">
-        <v>750000</v>
+        <v>4500000</v>
       </c>
       <c r="I139">
         <v>12</v>
       </c>
       <c r="J139" t="str">
-        <v>2026-03-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K139" t="str">
-        <v>2027-03-01</v>
+        <v>2027-08-01</v>
       </c>
       <c r="L139">
-        <v>225000</v>
+        <v>1350000</v>
       </c>
       <c r="M139" t="str">
-        <v>Quạt phòng 103</v>
+        <v>Giường phòng 102</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B140" t="str">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C140" t="str">
         <v/>
       </c>
       <c r="D140" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E140" t="str">
         <v>NEW</v>
@@ -10990,36 +10990,36 @@
         <v>1</v>
       </c>
       <c r="H140">
-        <v>4000000</v>
+        <v>800000</v>
       </c>
       <c r="I140">
         <v>12</v>
       </c>
       <c r="J140" t="str">
-        <v>2026-04-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K140" t="str">
-        <v>2027-04-01</v>
+        <v>2027-08-01</v>
       </c>
       <c r="L140">
-        <v>1200000</v>
+        <v>240000</v>
       </c>
       <c r="M140" t="str">
-        <v>NT cơ bản phòng 101</v>
+        <v>Quạt phòng 102</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B141" t="str">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C141" t="str">
         <v/>
       </c>
       <c r="D141" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E141" t="str">
         <v>NEW</v>
@@ -11031,27 +11031,27 @@
         <v>1</v>
       </c>
       <c r="H141">
-        <v>750000</v>
+        <v>9200000</v>
       </c>
       <c r="I141">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J141" t="str">
-        <v>2026-04-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K141" t="str">
-        <v>2027-04-01</v>
+        <v>2028-08-01</v>
       </c>
       <c r="L141">
-        <v>225000</v>
+        <v>2760000</v>
       </c>
       <c r="M141" t="str">
-        <v>Quạt phòng 101</v>
+        <v>ĐH phòng 102</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B142" t="str">
         <v>102</v>
@@ -11060,7 +11060,7 @@
         <v/>
       </c>
       <c r="D142" t="str">
-        <v>Giường</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E142" t="str">
         <v>NEW</v>
@@ -11072,36 +11072,36 @@
         <v>1</v>
       </c>
       <c r="H142">
-        <v>4000000</v>
+        <v>2600000</v>
       </c>
       <c r="I142">
         <v>12</v>
       </c>
       <c r="J142" t="str">
-        <v>2026-04-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K142" t="str">
-        <v>2027-04-01</v>
+        <v>2027-08-01</v>
       </c>
       <c r="L142">
-        <v>1200000</v>
+        <v>780000</v>
       </c>
       <c r="M142" t="str">
-        <v>NT cơ bản phòng 102</v>
+        <v>NL phòng 102</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B143" t="str">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C143" t="str">
         <v/>
       </c>
       <c r="D143" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="E143" t="str">
         <v>NEW</v>
@@ -11113,27 +11113,27 @@
         <v>1</v>
       </c>
       <c r="H143">
-        <v>8500000</v>
+        <v>4500000</v>
       </c>
       <c r="I143">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J143" t="str">
-        <v>2026-04-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K143" t="str">
-        <v>2028-04-01</v>
+        <v>2027-08-01</v>
       </c>
       <c r="L143">
-        <v>2550000</v>
+        <v>1350000</v>
       </c>
       <c r="M143" t="str">
-        <v>ĐH phòng 102</v>
+        <v>Giường phòng 103</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B144" t="str">
         <v>103</v>
@@ -11142,7 +11142,7 @@
         <v/>
       </c>
       <c r="D144" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E144" t="str">
         <v>NEW</v>
@@ -11154,27 +11154,27 @@
         <v>1</v>
       </c>
       <c r="H144">
-        <v>4000000</v>
+        <v>800000</v>
       </c>
       <c r="I144">
         <v>12</v>
       </c>
       <c r="J144" t="str">
-        <v>2026-04-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K144" t="str">
-        <v>2027-04-01</v>
+        <v>2027-08-01</v>
       </c>
       <c r="L144">
-        <v>1200000</v>
+        <v>240000</v>
       </c>
       <c r="M144" t="str">
-        <v>NT cơ bản phòng 103</v>
+        <v>Quạt phòng 103</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B145" t="str">
         <v>103</v>
@@ -11183,39 +11183,1884 @@
         <v/>
       </c>
       <c r="D145" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="E145" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F145" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G145">
+        <v>1</v>
+      </c>
+      <c r="H145">
+        <v>9200000</v>
+      </c>
+      <c r="I145">
+        <v>24</v>
+      </c>
+      <c r="J145" t="str">
+        <v>2026-08-01</v>
+      </c>
+      <c r="K145" t="str">
+        <v>2028-08-01</v>
+      </c>
+      <c r="L145">
+        <v>2760000</v>
+      </c>
+      <c r="M145" t="str">
+        <v>ĐH phòng 103</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>HD-MTX-46-RENO-RM-FULL</v>
+      </c>
+      <c r="B146" t="str">
+        <v>103</v>
+      </c>
+      <c r="C146" t="str">
+        <v/>
+      </c>
+      <c r="D146" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="E146" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F146" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G146">
+        <v>1</v>
+      </c>
+      <c r="H146">
+        <v>2600000</v>
+      </c>
+      <c r="I146">
+        <v>12</v>
+      </c>
+      <c r="J146" t="str">
+        <v>2026-08-01</v>
+      </c>
+      <c r="K146" t="str">
+        <v>2027-08-01</v>
+      </c>
+      <c r="L146">
+        <v>780000</v>
+      </c>
+      <c r="M146" t="str">
+        <v>NL phòng 103</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>HD-MTX-46-RENO-RM-FULL</v>
+      </c>
+      <c r="B147" t="str">
+        <v>104</v>
+      </c>
+      <c r="C147" t="str">
+        <v/>
+      </c>
+      <c r="D147" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E147" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F147" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G147">
+        <v>1</v>
+      </c>
+      <c r="H147">
+        <v>4500000</v>
+      </c>
+      <c r="I147">
+        <v>12</v>
+      </c>
+      <c r="J147" t="str">
+        <v>2026-08-01</v>
+      </c>
+      <c r="K147" t="str">
+        <v>2027-08-01</v>
+      </c>
+      <c r="L147">
+        <v>1350000</v>
+      </c>
+      <c r="M147" t="str">
+        <v>Giường phòng 104</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>HD-MTX-46-RENO-RM-FULL</v>
+      </c>
+      <c r="B148" t="str">
+        <v>104</v>
+      </c>
+      <c r="C148" t="str">
+        <v/>
+      </c>
+      <c r="D148" t="str">
         <v>Quạt</v>
       </c>
-      <c r="E145" t="str">
-        <v>NEW</v>
-      </c>
-      <c r="F145" t="str">
-        <v>THEM_MOI</v>
-      </c>
-      <c r="G145">
-        <v>1</v>
-      </c>
-      <c r="H145">
+      <c r="E148" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F148" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G148">
+        <v>1</v>
+      </c>
+      <c r="H148">
+        <v>800000</v>
+      </c>
+      <c r="I148">
+        <v>12</v>
+      </c>
+      <c r="J148" t="str">
+        <v>2026-08-01</v>
+      </c>
+      <c r="K148" t="str">
+        <v>2027-08-01</v>
+      </c>
+      <c r="L148">
+        <v>240000</v>
+      </c>
+      <c r="M148" t="str">
+        <v>Quạt phòng 104</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>HD-MTX-46-RENO-RM-FULL</v>
+      </c>
+      <c r="B149" t="str">
+        <v>104</v>
+      </c>
+      <c r="C149" t="str">
+        <v/>
+      </c>
+      <c r="D149" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="E149" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F149" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G149">
+        <v>1</v>
+      </c>
+      <c r="H149">
+        <v>9200000</v>
+      </c>
+      <c r="I149">
+        <v>24</v>
+      </c>
+      <c r="J149" t="str">
+        <v>2026-08-01</v>
+      </c>
+      <c r="K149" t="str">
+        <v>2028-08-01</v>
+      </c>
+      <c r="L149">
+        <v>2760000</v>
+      </c>
+      <c r="M149" t="str">
+        <v>ĐH phòng 104</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>HD-MTX-46-RENO-RM-FULL</v>
+      </c>
+      <c r="B150" t="str">
+        <v>104</v>
+      </c>
+      <c r="C150" t="str">
+        <v/>
+      </c>
+      <c r="D150" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="E150" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F150" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G150">
+        <v>1</v>
+      </c>
+      <c r="H150">
+        <v>2600000</v>
+      </c>
+      <c r="I150">
+        <v>12</v>
+      </c>
+      <c r="J150" t="str">
+        <v>2026-08-01</v>
+      </c>
+      <c r="K150" t="str">
+        <v>2027-08-01</v>
+      </c>
+      <c r="L150">
+        <v>780000</v>
+      </c>
+      <c r="M150" t="str">
+        <v>NL phòng 104</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B151" t="str">
+        <v>101</v>
+      </c>
+      <c r="C151" t="str">
+        <v/>
+      </c>
+      <c r="D151" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E151" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F151" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G151">
+        <v>1</v>
+      </c>
+      <c r="H151">
+        <v>4500000</v>
+      </c>
+      <c r="I151">
+        <v>12</v>
+      </c>
+      <c r="J151" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="K151" t="str">
+        <v>2027-09-01</v>
+      </c>
+      <c r="L151">
+        <v>1350000</v>
+      </c>
+      <c r="M151" t="str">
+        <v>Giường phòng 101</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B152" t="str">
+        <v>101</v>
+      </c>
+      <c r="C152" t="str">
+        <v/>
+      </c>
+      <c r="D152" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E152" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F152" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G152">
+        <v>1</v>
+      </c>
+      <c r="H152">
+        <v>800000</v>
+      </c>
+      <c r="I152">
+        <v>12</v>
+      </c>
+      <c r="J152" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="K152" t="str">
+        <v>2027-09-01</v>
+      </c>
+      <c r="L152">
+        <v>240000</v>
+      </c>
+      <c r="M152" t="str">
+        <v>Quạt phòng 101</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B153" t="str">
+        <v>101</v>
+      </c>
+      <c r="C153" t="str">
+        <v/>
+      </c>
+      <c r="D153" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="E153" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F153" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G153">
+        <v>1</v>
+      </c>
+      <c r="H153">
+        <v>9200000</v>
+      </c>
+      <c r="I153">
+        <v>24</v>
+      </c>
+      <c r="J153" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="K153" t="str">
+        <v>2028-09-01</v>
+      </c>
+      <c r="L153">
+        <v>2760000</v>
+      </c>
+      <c r="M153" t="str">
+        <v>ĐH phòng 101</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B154" t="str">
+        <v>101</v>
+      </c>
+      <c r="C154" t="str">
+        <v/>
+      </c>
+      <c r="D154" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="E154" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F154" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G154">
+        <v>1</v>
+      </c>
+      <c r="H154">
+        <v>2600000</v>
+      </c>
+      <c r="I154">
+        <v>12</v>
+      </c>
+      <c r="J154" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="K154" t="str">
+        <v>2027-09-01</v>
+      </c>
+      <c r="L154">
+        <v>780000</v>
+      </c>
+      <c r="M154" t="str">
+        <v>NL phòng 101</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B155" t="str">
+        <v>102</v>
+      </c>
+      <c r="C155" t="str">
+        <v/>
+      </c>
+      <c r="D155" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E155" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F155" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G155">
+        <v>1</v>
+      </c>
+      <c r="H155">
+        <v>4500000</v>
+      </c>
+      <c r="I155">
+        <v>12</v>
+      </c>
+      <c r="J155" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="K155" t="str">
+        <v>2027-09-01</v>
+      </c>
+      <c r="L155">
+        <v>1350000</v>
+      </c>
+      <c r="M155" t="str">
+        <v>Giường phòng 102</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B156" t="str">
+        <v>102</v>
+      </c>
+      <c r="C156" t="str">
+        <v/>
+      </c>
+      <c r="D156" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E156" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F156" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G156">
+        <v>1</v>
+      </c>
+      <c r="H156">
+        <v>800000</v>
+      </c>
+      <c r="I156">
+        <v>12</v>
+      </c>
+      <c r="J156" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="K156" t="str">
+        <v>2027-09-01</v>
+      </c>
+      <c r="L156">
+        <v>240000</v>
+      </c>
+      <c r="M156" t="str">
+        <v>Quạt phòng 102</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B157" t="str">
+        <v>102</v>
+      </c>
+      <c r="C157" t="str">
+        <v/>
+      </c>
+      <c r="D157" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="E157" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F157" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G157">
+        <v>1</v>
+      </c>
+      <c r="H157">
+        <v>9200000</v>
+      </c>
+      <c r="I157">
+        <v>24</v>
+      </c>
+      <c r="J157" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="K157" t="str">
+        <v>2028-09-01</v>
+      </c>
+      <c r="L157">
+        <v>2760000</v>
+      </c>
+      <c r="M157" t="str">
+        <v>ĐH phòng 102</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B158" t="str">
+        <v>102</v>
+      </c>
+      <c r="C158" t="str">
+        <v/>
+      </c>
+      <c r="D158" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="E158" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F158" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G158">
+        <v>1</v>
+      </c>
+      <c r="H158">
+        <v>2600000</v>
+      </c>
+      <c r="I158">
+        <v>12</v>
+      </c>
+      <c r="J158" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="K158" t="str">
+        <v>2027-09-01</v>
+      </c>
+      <c r="L158">
+        <v>780000</v>
+      </c>
+      <c r="M158" t="str">
+        <v>NL phòng 102</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B159" t="str">
+        <v>103</v>
+      </c>
+      <c r="C159" t="str">
+        <v/>
+      </c>
+      <c r="D159" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E159" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F159" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G159">
+        <v>1</v>
+      </c>
+      <c r="H159">
+        <v>4500000</v>
+      </c>
+      <c r="I159">
+        <v>12</v>
+      </c>
+      <c r="J159" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="K159" t="str">
+        <v>2027-09-01</v>
+      </c>
+      <c r="L159">
+        <v>1350000</v>
+      </c>
+      <c r="M159" t="str">
+        <v>Giường phòng 103</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B160" t="str">
+        <v>103</v>
+      </c>
+      <c r="C160" t="str">
+        <v/>
+      </c>
+      <c r="D160" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E160" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F160" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G160">
+        <v>1</v>
+      </c>
+      <c r="H160">
+        <v>800000</v>
+      </c>
+      <c r="I160">
+        <v>12</v>
+      </c>
+      <c r="J160" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="K160" t="str">
+        <v>2027-09-01</v>
+      </c>
+      <c r="L160">
+        <v>240000</v>
+      </c>
+      <c r="M160" t="str">
+        <v>Quạt phòng 103</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B161" t="str">
+        <v>103</v>
+      </c>
+      <c r="C161" t="str">
+        <v/>
+      </c>
+      <c r="D161" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="E161" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F161" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G161">
+        <v>1</v>
+      </c>
+      <c r="H161">
+        <v>9200000</v>
+      </c>
+      <c r="I161">
+        <v>24</v>
+      </c>
+      <c r="J161" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="K161" t="str">
+        <v>2028-09-01</v>
+      </c>
+      <c r="L161">
+        <v>2760000</v>
+      </c>
+      <c r="M161" t="str">
+        <v>ĐH phòng 103</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B162" t="str">
+        <v>103</v>
+      </c>
+      <c r="C162" t="str">
+        <v/>
+      </c>
+      <c r="D162" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="E162" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F162" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G162">
+        <v>1</v>
+      </c>
+      <c r="H162">
+        <v>2600000</v>
+      </c>
+      <c r="I162">
+        <v>12</v>
+      </c>
+      <c r="J162" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="K162" t="str">
+        <v>2027-09-01</v>
+      </c>
+      <c r="L162">
+        <v>780000</v>
+      </c>
+      <c r="M162" t="str">
+        <v>NL phòng 103</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B163" t="str">
+        <v>104</v>
+      </c>
+      <c r="C163" t="str">
+        <v/>
+      </c>
+      <c r="D163" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E163" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F163" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G163">
+        <v>1</v>
+      </c>
+      <c r="H163">
+        <v>4500000</v>
+      </c>
+      <c r="I163">
+        <v>12</v>
+      </c>
+      <c r="J163" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="K163" t="str">
+        <v>2027-09-01</v>
+      </c>
+      <c r="L163">
+        <v>1350000</v>
+      </c>
+      <c r="M163" t="str">
+        <v>Giường phòng 104</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B164" t="str">
+        <v>104</v>
+      </c>
+      <c r="C164" t="str">
+        <v/>
+      </c>
+      <c r="D164" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E164" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F164" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G164">
+        <v>1</v>
+      </c>
+      <c r="H164">
+        <v>800000</v>
+      </c>
+      <c r="I164">
+        <v>12</v>
+      </c>
+      <c r="J164" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="K164" t="str">
+        <v>2027-09-01</v>
+      </c>
+      <c r="L164">
+        <v>240000</v>
+      </c>
+      <c r="M164" t="str">
+        <v>Quạt phòng 104</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B165" t="str">
+        <v>104</v>
+      </c>
+      <c r="C165" t="str">
+        <v/>
+      </c>
+      <c r="D165" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="E165" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F165" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G165">
+        <v>1</v>
+      </c>
+      <c r="H165">
+        <v>9200000</v>
+      </c>
+      <c r="I165">
+        <v>24</v>
+      </c>
+      <c r="J165" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="K165" t="str">
+        <v>2028-09-01</v>
+      </c>
+      <c r="L165">
+        <v>2760000</v>
+      </c>
+      <c r="M165" t="str">
+        <v>ĐH phòng 104</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B166" t="str">
+        <v>104</v>
+      </c>
+      <c r="C166" t="str">
+        <v/>
+      </c>
+      <c r="D166" t="str">
+        <v>Nóng lạnh</v>
+      </c>
+      <c r="E166" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F166" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G166">
+        <v>1</v>
+      </c>
+      <c r="H166">
+        <v>2600000</v>
+      </c>
+      <c r="I166">
+        <v>12</v>
+      </c>
+      <c r="J166" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="K166" t="str">
+        <v>2027-09-01</v>
+      </c>
+      <c r="L166">
+        <v>780000</v>
+      </c>
+      <c r="M166" t="str">
+        <v>NL phòng 104</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B167" t="str">
+        <v>101</v>
+      </c>
+      <c r="C167" t="str">
+        <v/>
+      </c>
+      <c r="D167" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E167" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F167" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G167">
+        <v>1</v>
+      </c>
+      <c r="H167">
+        <v>4000000</v>
+      </c>
+      <c r="I167">
+        <v>12</v>
+      </c>
+      <c r="J167" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="K167" t="str">
+        <v>2027-10-01</v>
+      </c>
+      <c r="L167">
+        <v>1200000</v>
+      </c>
+      <c r="M167" t="str">
+        <v>NT cơ bản phòng 101</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B168" t="str">
+        <v>101</v>
+      </c>
+      <c r="C168" t="str">
+        <v/>
+      </c>
+      <c r="D168" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E168" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F168" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G168">
+        <v>1</v>
+      </c>
+      <c r="H168">
         <v>750000</v>
       </c>
-      <c r="I145">
-        <v>12</v>
-      </c>
-      <c r="J145" t="str">
+      <c r="I168">
+        <v>12</v>
+      </c>
+      <c r="J168" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="K168" t="str">
+        <v>2027-10-01</v>
+      </c>
+      <c r="L168">
+        <v>225000</v>
+      </c>
+      <c r="M168" t="str">
+        <v>Quạt phòng 101</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B169" t="str">
+        <v>101</v>
+      </c>
+      <c r="C169" t="str">
+        <v/>
+      </c>
+      <c r="D169" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="E169" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F169" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G169">
+        <v>1</v>
+      </c>
+      <c r="H169">
+        <v>8500000</v>
+      </c>
+      <c r="I169">
+        <v>24</v>
+      </c>
+      <c r="J169" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="K169" t="str">
+        <v>2028-10-01</v>
+      </c>
+      <c r="L169">
+        <v>2550000</v>
+      </c>
+      <c r="M169" t="str">
+        <v>ĐH phòng 101</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B170" t="str">
+        <v>102</v>
+      </c>
+      <c r="C170" t="str">
+        <v/>
+      </c>
+      <c r="D170" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E170" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F170" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G170">
+        <v>1</v>
+      </c>
+      <c r="H170">
+        <v>4000000</v>
+      </c>
+      <c r="I170">
+        <v>12</v>
+      </c>
+      <c r="J170" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="K170" t="str">
+        <v>2027-10-01</v>
+      </c>
+      <c r="L170">
+        <v>1200000</v>
+      </c>
+      <c r="M170" t="str">
+        <v>NT cơ bản phòng 102</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B171" t="str">
+        <v>102</v>
+      </c>
+      <c r="C171" t="str">
+        <v/>
+      </c>
+      <c r="D171" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E171" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F171" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G171">
+        <v>1</v>
+      </c>
+      <c r="H171">
+        <v>750000</v>
+      </c>
+      <c r="I171">
+        <v>12</v>
+      </c>
+      <c r="J171" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="K171" t="str">
+        <v>2027-10-01</v>
+      </c>
+      <c r="L171">
+        <v>225000</v>
+      </c>
+      <c r="M171" t="str">
+        <v>Quạt phòng 102</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B172" t="str">
+        <v>103</v>
+      </c>
+      <c r="C172" t="str">
+        <v/>
+      </c>
+      <c r="D172" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E172" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F172" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G172">
+        <v>1</v>
+      </c>
+      <c r="H172">
+        <v>4000000</v>
+      </c>
+      <c r="I172">
+        <v>12</v>
+      </c>
+      <c r="J172" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="K172" t="str">
+        <v>2027-10-01</v>
+      </c>
+      <c r="L172">
+        <v>1200000</v>
+      </c>
+      <c r="M172" t="str">
+        <v>NT cơ bản phòng 103</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B173" t="str">
+        <v>103</v>
+      </c>
+      <c r="C173" t="str">
+        <v/>
+      </c>
+      <c r="D173" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E173" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F173" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G173">
+        <v>1</v>
+      </c>
+      <c r="H173">
+        <v>750000</v>
+      </c>
+      <c r="I173">
+        <v>12</v>
+      </c>
+      <c r="J173" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="K173" t="str">
+        <v>2027-10-01</v>
+      </c>
+      <c r="L173">
+        <v>225000</v>
+      </c>
+      <c r="M173" t="str">
+        <v>Quạt phòng 103</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B174" t="str">
+        <v>103</v>
+      </c>
+      <c r="C174" t="str">
+        <v/>
+      </c>
+      <c r="D174" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="E174" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F174" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G174">
+        <v>1</v>
+      </c>
+      <c r="H174">
+        <v>8500000</v>
+      </c>
+      <c r="I174">
+        <v>24</v>
+      </c>
+      <c r="J174" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="K174" t="str">
+        <v>2028-10-01</v>
+      </c>
+      <c r="L174">
+        <v>2550000</v>
+      </c>
+      <c r="M174" t="str">
+        <v>ĐH phòng 103</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B175" t="str">
+        <v>101</v>
+      </c>
+      <c r="C175" t="str">
+        <v/>
+      </c>
+      <c r="D175" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E175" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F175" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G175">
+        <v>1</v>
+      </c>
+      <c r="H175">
+        <v>4000000</v>
+      </c>
+      <c r="I175">
+        <v>12</v>
+      </c>
+      <c r="J175" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="K175" t="str">
+        <v>2027-03-01</v>
+      </c>
+      <c r="L175">
+        <v>1200000</v>
+      </c>
+      <c r="M175" t="str">
+        <v>NT cơ bản phòng 101</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B176" t="str">
+        <v>101</v>
+      </c>
+      <c r="C176" t="str">
+        <v/>
+      </c>
+      <c r="D176" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E176" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F176" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G176">
+        <v>1</v>
+      </c>
+      <c r="H176">
+        <v>750000</v>
+      </c>
+      <c r="I176">
+        <v>12</v>
+      </c>
+      <c r="J176" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="K176" t="str">
+        <v>2027-03-01</v>
+      </c>
+      <c r="L176">
+        <v>225000</v>
+      </c>
+      <c r="M176" t="str">
+        <v>Quạt phòng 101</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B177" t="str">
+        <v>101</v>
+      </c>
+      <c r="C177" t="str">
+        <v/>
+      </c>
+      <c r="D177" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="E177" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F177" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G177">
+        <v>1</v>
+      </c>
+      <c r="H177">
+        <v>8500000</v>
+      </c>
+      <c r="I177">
+        <v>24</v>
+      </c>
+      <c r="J177" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="K177" t="str">
+        <v>2028-03-01</v>
+      </c>
+      <c r="L177">
+        <v>2550000</v>
+      </c>
+      <c r="M177" t="str">
+        <v>ĐH phòng 101</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B178" t="str">
+        <v>102</v>
+      </c>
+      <c r="C178" t="str">
+        <v/>
+      </c>
+      <c r="D178" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E178" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F178" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G178">
+        <v>1</v>
+      </c>
+      <c r="H178">
+        <v>4000000</v>
+      </c>
+      <c r="I178">
+        <v>12</v>
+      </c>
+      <c r="J178" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="K178" t="str">
+        <v>2027-03-01</v>
+      </c>
+      <c r="L178">
+        <v>1200000</v>
+      </c>
+      <c r="M178" t="str">
+        <v>NT cơ bản phòng 102</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B179" t="str">
+        <v>102</v>
+      </c>
+      <c r="C179" t="str">
+        <v/>
+      </c>
+      <c r="D179" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E179" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F179" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G179">
+        <v>1</v>
+      </c>
+      <c r="H179">
+        <v>750000</v>
+      </c>
+      <c r="I179">
+        <v>12</v>
+      </c>
+      <c r="J179" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="K179" t="str">
+        <v>2027-03-01</v>
+      </c>
+      <c r="L179">
+        <v>225000</v>
+      </c>
+      <c r="M179" t="str">
+        <v>Quạt phòng 102</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B180" t="str">
+        <v>103</v>
+      </c>
+      <c r="C180" t="str">
+        <v/>
+      </c>
+      <c r="D180" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E180" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F180" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G180">
+        <v>1</v>
+      </c>
+      <c r="H180">
+        <v>4000000</v>
+      </c>
+      <c r="I180">
+        <v>12</v>
+      </c>
+      <c r="J180" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="K180" t="str">
+        <v>2027-03-01</v>
+      </c>
+      <c r="L180">
+        <v>1200000</v>
+      </c>
+      <c r="M180" t="str">
+        <v>NT cơ bản phòng 103</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B181" t="str">
+        <v>103</v>
+      </c>
+      <c r="C181" t="str">
+        <v/>
+      </c>
+      <c r="D181" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E181" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F181" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G181">
+        <v>1</v>
+      </c>
+      <c r="H181">
+        <v>750000</v>
+      </c>
+      <c r="I181">
+        <v>12</v>
+      </c>
+      <c r="J181" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="K181" t="str">
+        <v>2027-03-01</v>
+      </c>
+      <c r="L181">
+        <v>225000</v>
+      </c>
+      <c r="M181" t="str">
+        <v>Quạt phòng 103</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B182" t="str">
+        <v>103</v>
+      </c>
+      <c r="C182" t="str">
+        <v/>
+      </c>
+      <c r="D182" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="E182" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F182" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G182">
+        <v>1</v>
+      </c>
+      <c r="H182">
+        <v>8500000</v>
+      </c>
+      <c r="I182">
+        <v>24</v>
+      </c>
+      <c r="J182" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="K182" t="str">
+        <v>2028-03-01</v>
+      </c>
+      <c r="L182">
+        <v>2550000</v>
+      </c>
+      <c r="M182" t="str">
+        <v>ĐH phòng 103</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B183" t="str">
+        <v>101</v>
+      </c>
+      <c r="C183" t="str">
+        <v/>
+      </c>
+      <c r="D183" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E183" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F183" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G183">
+        <v>1</v>
+      </c>
+      <c r="H183">
+        <v>4000000</v>
+      </c>
+      <c r="I183">
+        <v>12</v>
+      </c>
+      <c r="J183" t="str">
         <v>2026-04-01</v>
       </c>
-      <c r="K145" t="str">
+      <c r="K183" t="str">
         <v>2027-04-01</v>
       </c>
-      <c r="L145">
+      <c r="L183">
+        <v>1200000</v>
+      </c>
+      <c r="M183" t="str">
+        <v>NT cơ bản phòng 101</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B184" t="str">
+        <v>101</v>
+      </c>
+      <c r="C184" t="str">
+        <v/>
+      </c>
+      <c r="D184" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E184" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F184" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G184">
+        <v>1</v>
+      </c>
+      <c r="H184">
+        <v>750000</v>
+      </c>
+      <c r="I184">
+        <v>12</v>
+      </c>
+      <c r="J184" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="K184" t="str">
+        <v>2027-04-01</v>
+      </c>
+      <c r="L184">
         <v>225000</v>
       </c>
-      <c r="M145" t="str">
+      <c r="M184" t="str">
+        <v>Quạt phòng 101</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B185" t="str">
+        <v>101</v>
+      </c>
+      <c r="C185" t="str">
+        <v/>
+      </c>
+      <c r="D185" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="E185" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F185" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G185">
+        <v>1</v>
+      </c>
+      <c r="H185">
+        <v>8500000</v>
+      </c>
+      <c r="I185">
+        <v>24</v>
+      </c>
+      <c r="J185" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="K185" t="str">
+        <v>2028-04-01</v>
+      </c>
+      <c r="L185">
+        <v>2550000</v>
+      </c>
+      <c r="M185" t="str">
+        <v>ĐH phòng 101</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B186" t="str">
+        <v>102</v>
+      </c>
+      <c r="C186" t="str">
+        <v/>
+      </c>
+      <c r="D186" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E186" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F186" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G186">
+        <v>1</v>
+      </c>
+      <c r="H186">
+        <v>4000000</v>
+      </c>
+      <c r="I186">
+        <v>12</v>
+      </c>
+      <c r="J186" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="K186" t="str">
+        <v>2027-04-01</v>
+      </c>
+      <c r="L186">
+        <v>1200000</v>
+      </c>
+      <c r="M186" t="str">
+        <v>NT cơ bản phòng 102</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B187" t="str">
+        <v>102</v>
+      </c>
+      <c r="C187" t="str">
+        <v/>
+      </c>
+      <c r="D187" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E187" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F187" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G187">
+        <v>1</v>
+      </c>
+      <c r="H187">
+        <v>750000</v>
+      </c>
+      <c r="I187">
+        <v>12</v>
+      </c>
+      <c r="J187" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="K187" t="str">
+        <v>2027-04-01</v>
+      </c>
+      <c r="L187">
+        <v>225000</v>
+      </c>
+      <c r="M187" t="str">
+        <v>Quạt phòng 102</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B188" t="str">
+        <v>103</v>
+      </c>
+      <c r="C188" t="str">
+        <v/>
+      </c>
+      <c r="D188" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E188" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F188" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G188">
+        <v>1</v>
+      </c>
+      <c r="H188">
+        <v>4000000</v>
+      </c>
+      <c r="I188">
+        <v>12</v>
+      </c>
+      <c r="J188" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="K188" t="str">
+        <v>2027-04-01</v>
+      </c>
+      <c r="L188">
+        <v>1200000</v>
+      </c>
+      <c r="M188" t="str">
+        <v>NT cơ bản phòng 103</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B189" t="str">
+        <v>103</v>
+      </c>
+      <c r="C189" t="str">
+        <v/>
+      </c>
+      <c r="D189" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E189" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F189" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G189">
+        <v>1</v>
+      </c>
+      <c r="H189">
+        <v>750000</v>
+      </c>
+      <c r="I189">
+        <v>12</v>
+      </c>
+      <c r="J189" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="K189" t="str">
+        <v>2027-04-01</v>
+      </c>
+      <c r="L189">
+        <v>225000</v>
+      </c>
+      <c r="M189" t="str">
         <v>Quạt phòng 103</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B190" t="str">
+        <v>103</v>
+      </c>
+      <c r="C190" t="str">
+        <v/>
+      </c>
+      <c r="D190" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="E190" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F190" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G190">
+        <v>1</v>
+      </c>
+      <c r="H190">
+        <v>8500000</v>
+      </c>
+      <c r="I190">
+        <v>24</v>
+      </c>
+      <c r="J190" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="K190" t="str">
+        <v>2028-04-01</v>
+      </c>
+      <c r="L190">
+        <v>2550000</v>
+      </c>
+      <c r="M190" t="str">
+        <v>ĐH phòng 103</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M145"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M190"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/SLMS2026_import_matrix_dot2.xlsx
+++ b/docs/SLMS2026_import_matrix_dot2.xlsx
@@ -4077,7 +4077,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E87"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -4241,19 +4241,19 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>HD-MTX-23-RENO-WH-BASIC-BUY</v>
+        <v>HD-MTX-22-RENO-WH-BASIC-BUY</v>
       </c>
       <c r="B10" t="str">
-        <v>PAINTING</v>
+        <v>EQUIPMENT</v>
       </c>
       <c r="C10" t="str">
-        <v>Sơn sửa</v>
+        <v>Thiết bị mua thêm</v>
       </c>
       <c r="D10">
         <v>11500000</v>
       </c>
       <c r="E10" t="str">
-        <v>Sơn lại toàn bộ</v>
+        <v>Mua &amp; lắp TB mới đợt 2</v>
       </c>
     </row>
     <row r="11">
@@ -4261,55 +4261,55 @@
         <v>HD-MTX-23-RENO-WH-BASIC-BUY</v>
       </c>
       <c r="B11" t="str">
-        <v>PLUMBING</v>
+        <v>PAINTING</v>
       </c>
       <c r="C11" t="str">
-        <v>Điện nước</v>
+        <v>Sơn sửa</v>
       </c>
       <c r="D11">
-        <v>13500000</v>
+        <v>11500000</v>
       </c>
       <c r="E11" t="str">
-        <v>Hoàn thiện điện nước</v>
+        <v>Sơn lại toàn bộ</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>HD-MTX-24-RENO-WH-BASIC-BUY</v>
+        <v>HD-MTX-23-RENO-WH-BASIC-BUY</v>
       </c>
       <c r="B12" t="str">
-        <v>PAINTING</v>
+        <v>PLUMBING</v>
       </c>
       <c r="C12" t="str">
-        <v>Sơn sửa</v>
+        <v>Điện nước</v>
       </c>
       <c r="D12">
-        <v>13000000</v>
+        <v>13500000</v>
       </c>
       <c r="E12" t="str">
-        <v>Sơn lại toàn bộ</v>
+        <v>Hoàn thiện điện nước</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>HD-MTX-24-RENO-WH-BASIC-BUY</v>
+        <v>HD-MTX-23-RENO-WH-BASIC-BUY</v>
       </c>
       <c r="B13" t="str">
-        <v>PLUMBING</v>
+        <v>EQUIPMENT</v>
       </c>
       <c r="C13" t="str">
-        <v>Điện nước</v>
+        <v>Thiết bị mua thêm</v>
       </c>
       <c r="D13">
-        <v>15000000</v>
+        <v>13000000</v>
       </c>
       <c r="E13" t="str">
-        <v>Hoàn thiện điện nước</v>
+        <v>Mua &amp; lắp TB mới đợt 2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-24-RENO-WH-BASIC-BUY</v>
       </c>
       <c r="B14" t="str">
         <v>PAINTING</v>
@@ -4318,7 +4318,7 @@
         <v>Sơn sửa</v>
       </c>
       <c r="D14">
-        <v>7000000</v>
+        <v>13000000</v>
       </c>
       <c r="E14" t="str">
         <v>Sơn lại toàn bộ</v>
@@ -4326,7 +4326,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-24-RENO-WH-BASIC-BUY</v>
       </c>
       <c r="B15" t="str">
         <v>PLUMBING</v>
@@ -4335,7 +4335,7 @@
         <v>Điện nước</v>
       </c>
       <c r="D15">
-        <v>9000000</v>
+        <v>15000000</v>
       </c>
       <c r="E15" t="str">
         <v>Hoàn thiện điện nước</v>
@@ -4343,24 +4343,24 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>HD-MTX-25-RENO-WH-FULL</v>
+        <v>HD-MTX-24-RENO-WH-BASIC-BUY</v>
       </c>
       <c r="B16" t="str">
-        <v>FURNITURE</v>
+        <v>EQUIPMENT</v>
       </c>
       <c r="C16" t="str">
-        <v>Nội thất</v>
+        <v>Thiết bị mua thêm</v>
       </c>
       <c r="D16">
-        <v>10000000</v>
+        <v>14500000</v>
       </c>
       <c r="E16" t="str">
-        <v>Lắp đặt nội thất</v>
+        <v>Mua &amp; lắp TB mới đợt 2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B17" t="str">
         <v>PAINTING</v>
@@ -4369,7 +4369,7 @@
         <v>Sơn sửa</v>
       </c>
       <c r="D17">
-        <v>8500000</v>
+        <v>7000000</v>
       </c>
       <c r="E17" t="str">
         <v>Sơn lại toàn bộ</v>
@@ -4377,7 +4377,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B18" t="str">
         <v>PLUMBING</v>
@@ -4386,7 +4386,7 @@
         <v>Điện nước</v>
       </c>
       <c r="D18">
-        <v>10500000</v>
+        <v>9000000</v>
       </c>
       <c r="E18" t="str">
         <v>Hoàn thiện điện nước</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B19" t="str">
         <v>FURNITURE</v>
@@ -4403,7 +4403,7 @@
         <v>Nội thất</v>
       </c>
       <c r="D19">
-        <v>11500000</v>
+        <v>10000000</v>
       </c>
       <c r="E19" t="str">
         <v>Lắp đặt nội thất</v>
@@ -4411,92 +4411,92 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B20" t="str">
-        <v>PAINTING</v>
+        <v>EQUIPMENT</v>
       </c>
       <c r="C20" t="str">
-        <v>Sơn sửa</v>
+        <v>Thiết bị mua thêm</v>
       </c>
       <c r="D20">
-        <v>10000000</v>
+        <v>8500000</v>
       </c>
       <c r="E20" t="str">
-        <v>Sơn lại toàn bộ</v>
+        <v>Mua &amp; lắp TB mới đợt 2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
+        <v>HD-MTX-26-RENO-WH-FULL</v>
       </c>
       <c r="B21" t="str">
-        <v>PLUMBING</v>
+        <v>PAINTING</v>
       </c>
       <c r="C21" t="str">
-        <v>Điện nước</v>
+        <v>Sơn sửa</v>
       </c>
       <c r="D21">
-        <v>12000000</v>
+        <v>8500000</v>
       </c>
       <c r="E21" t="str">
-        <v>Hoàn thiện điện nước</v>
+        <v>Sơn lại toàn bộ</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
+        <v>HD-MTX-26-RENO-WH-FULL</v>
       </c>
       <c r="B22" t="str">
-        <v>FURNITURE</v>
+        <v>PLUMBING</v>
       </c>
       <c r="C22" t="str">
-        <v>Nội thất</v>
+        <v>Điện nước</v>
       </c>
       <c r="D22">
-        <v>13000000</v>
+        <v>10500000</v>
       </c>
       <c r="E22" t="str">
-        <v>Lắp đặt nội thất</v>
+        <v>Hoàn thiện điện nước</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>HD-MTX-28-RENO-WH-HO-NOBUY</v>
+        <v>HD-MTX-26-RENO-WH-FULL</v>
       </c>
       <c r="B23" t="str">
-        <v>PAINTING</v>
+        <v>FURNITURE</v>
       </c>
       <c r="C23" t="str">
-        <v>Sơn sửa</v>
+        <v>Nội thất</v>
       </c>
       <c r="D23">
         <v>11500000</v>
       </c>
       <c r="E23" t="str">
-        <v>Sơn lại toàn bộ</v>
+        <v>Lắp đặt nội thất</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>HD-MTX-29-RENO-WH-HO-NOBUY</v>
+        <v>HD-MTX-26-RENO-WH-FULL</v>
       </c>
       <c r="B24" t="str">
-        <v>PAINTING</v>
+        <v>EQUIPMENT</v>
       </c>
       <c r="C24" t="str">
-        <v>Sơn sửa</v>
+        <v>Thiết bị mua thêm</v>
       </c>
       <c r="D24">
-        <v>13000000</v>
+        <v>10000000</v>
       </c>
       <c r="E24" t="str">
-        <v>Sơn lại toàn bộ</v>
+        <v>Mua &amp; lắp TB mới đợt 2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
+        <v>HD-MTX-27-RENO-WH-FULL</v>
       </c>
       <c r="B25" t="str">
         <v>PAINTING</v>
@@ -4505,7 +4505,7 @@
         <v>Sơn sửa</v>
       </c>
       <c r="D25">
-        <v>7000000</v>
+        <v>10000000</v>
       </c>
       <c r="E25" t="str">
         <v>Sơn lại toàn bộ</v>
@@ -4513,7 +4513,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
+        <v>HD-MTX-27-RENO-WH-FULL</v>
       </c>
       <c r="B26" t="str">
         <v>PLUMBING</v>
@@ -4522,7 +4522,7 @@
         <v>Điện nước</v>
       </c>
       <c r="D26">
-        <v>9000000</v>
+        <v>12000000</v>
       </c>
       <c r="E26" t="str">
         <v>Hoàn thiện điện nước</v>
@@ -4530,41 +4530,41 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
+        <v>HD-MTX-27-RENO-WH-FULL</v>
       </c>
       <c r="B27" t="str">
-        <v>PAINTING</v>
+        <v>FURNITURE</v>
       </c>
       <c r="C27" t="str">
-        <v>Sơn sửa</v>
+        <v>Nội thất</v>
       </c>
       <c r="D27">
-        <v>8500000</v>
+        <v>13000000</v>
       </c>
       <c r="E27" t="str">
-        <v>Sơn lại toàn bộ</v>
+        <v>Lắp đặt nội thất</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
+        <v>HD-MTX-27-RENO-WH-FULL</v>
       </c>
       <c r="B28" t="str">
-        <v>PLUMBING</v>
+        <v>EQUIPMENT</v>
       </c>
       <c r="C28" t="str">
-        <v>Điện nước</v>
+        <v>Thiết bị mua thêm</v>
       </c>
       <c r="D28">
-        <v>10500000</v>
+        <v>11500000</v>
       </c>
       <c r="E28" t="str">
-        <v>Hoàn thiện điện nước</v>
+        <v>Mua &amp; lắp TB mới đợt 2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>HD-MTX-32-RENO-RM-NONE</v>
+        <v>HD-MTX-28-RENO-WH-HO-NOBUY</v>
       </c>
       <c r="B29" t="str">
         <v>PAINTING</v>
@@ -4573,15 +4573,15 @@
         <v>Sơn sửa</v>
       </c>
       <c r="D29">
-        <v>10000000</v>
+        <v>11500000</v>
       </c>
       <c r="E29" t="str">
-        <v>Sơn 3 phòng</v>
+        <v>Sơn lại toàn bộ</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>HD-MTX-33-RENO-RM-NONE</v>
+        <v>HD-MTX-29-RENO-WH-HO-NOBUY</v>
       </c>
       <c r="B30" t="str">
         <v>PAINTING</v>
@@ -4590,66 +4590,66 @@
         <v>Sơn sửa</v>
       </c>
       <c r="D30">
-        <v>11500000</v>
+        <v>13000000</v>
       </c>
       <c r="E30" t="str">
-        <v>Sơn 3 phòng</v>
+        <v>Sơn lại toàn bộ</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>HD-MTX-33-RENO-RM-NONE</v>
+        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
       </c>
       <c r="B31" t="str">
-        <v>FLOORING</v>
+        <v>PAINTING</v>
       </c>
       <c r="C31" t="str">
-        <v>Sàn nhà</v>
+        <v>Sơn sửa</v>
       </c>
       <c r="D31">
-        <v>12500000</v>
+        <v>7000000</v>
       </c>
       <c r="E31" t="str">
-        <v>Lát gạch từng phòng</v>
+        <v>Sơn lại toàn bộ</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>HD-MTX-34-RENO-RM-NONE</v>
+        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
       </c>
       <c r="B32" t="str">
-        <v>PAINTING</v>
+        <v>PLUMBING</v>
       </c>
       <c r="C32" t="str">
-        <v>Sơn sửa</v>
+        <v>Điện nước</v>
       </c>
       <c r="D32">
-        <v>13000000</v>
+        <v>9000000</v>
       </c>
       <c r="E32" t="str">
-        <v>Sơn 3 phòng</v>
+        <v>Hoàn thiện điện nước</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>HD-MTX-35-RENO-RM-NONE</v>
+        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
       </c>
       <c r="B33" t="str">
-        <v>PAINTING</v>
+        <v>EQUIPMENT</v>
       </c>
       <c r="C33" t="str">
-        <v>Sơn sửa</v>
+        <v>Thiết bị mua thêm</v>
       </c>
       <c r="D33">
-        <v>7000000</v>
+        <v>8500000</v>
       </c>
       <c r="E33" t="str">
-        <v>Sơn 3 phòng</v>
+        <v>Mua &amp; lắp TB mới đợt 2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>HD-MTX-36-RENO-RM-BASIC-HO</v>
+        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
       </c>
       <c r="B34" t="str">
         <v>PAINTING</v>
@@ -4661,46 +4661,46 @@
         <v>8500000</v>
       </c>
       <c r="E34" t="str">
-        <v>Sơn 3 phòng</v>
+        <v>Sơn lại toàn bộ</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>HD-MTX-36-RENO-RM-BASIC-HO</v>
+        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
       </c>
       <c r="B35" t="str">
-        <v>FLOORING</v>
+        <v>PLUMBING</v>
       </c>
       <c r="C35" t="str">
-        <v>Sàn nhà</v>
+        <v>Điện nước</v>
       </c>
       <c r="D35">
-        <v>9500000</v>
+        <v>10500000</v>
       </c>
       <c r="E35" t="str">
-        <v>Lát gạch từng phòng</v>
+        <v>Hoàn thiện điện nước</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>HD-MTX-37-RENO-RM-BASIC-HO</v>
+        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
       </c>
       <c r="B36" t="str">
-        <v>PAINTING</v>
+        <v>EQUIPMENT</v>
       </c>
       <c r="C36" t="str">
-        <v>Sơn sửa</v>
+        <v>Thiết bị mua thêm</v>
       </c>
       <c r="D36">
         <v>10000000</v>
       </c>
       <c r="E36" t="str">
-        <v>Sơn 3 phòng</v>
+        <v>Mua &amp; lắp TB mới đợt 2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>HD-MTX-38-RENO-RM-BASIC-HO</v>
+        <v>HD-MTX-32-RENO-RM-NONE</v>
       </c>
       <c r="B37" t="str">
         <v>PAINTING</v>
@@ -4709,7 +4709,7 @@
         <v>Sơn sửa</v>
       </c>
       <c r="D37">
-        <v>11500000</v>
+        <v>10000000</v>
       </c>
       <c r="E37" t="str">
         <v>Sơn 3 phòng</v>
@@ -4717,7 +4717,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>HD-MTX-39-RENO-RM-BASIC-HO</v>
+        <v>HD-MTX-33-RENO-RM-NONE</v>
       </c>
       <c r="B38" t="str">
         <v>PAINTING</v>
@@ -4726,7 +4726,7 @@
         <v>Sơn sửa</v>
       </c>
       <c r="D38">
-        <v>13000000</v>
+        <v>11500000</v>
       </c>
       <c r="E38" t="str">
         <v>Sơn 3 phòng</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>HD-MTX-39-RENO-RM-BASIC-HO</v>
+        <v>HD-MTX-33-RENO-RM-NONE</v>
       </c>
       <c r="B39" t="str">
         <v>FLOORING</v>
@@ -4743,7 +4743,7 @@
         <v>Sàn nhà</v>
       </c>
       <c r="D39">
-        <v>14000000</v>
+        <v>12500000</v>
       </c>
       <c r="E39" t="str">
         <v>Lát gạch từng phòng</v>
@@ -4751,7 +4751,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-34-RENO-RM-NONE</v>
       </c>
       <c r="B40" t="str">
         <v>PAINTING</v>
@@ -4760,7 +4760,7 @@
         <v>Sơn sửa</v>
       </c>
       <c r="D40">
-        <v>7000000</v>
+        <v>13000000</v>
       </c>
       <c r="E40" t="str">
         <v>Sơn 3 phòng</v>
@@ -4768,24 +4768,24 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-35-RENO-RM-NONE</v>
       </c>
       <c r="B41" t="str">
-        <v>PLUMBING</v>
+        <v>PAINTING</v>
       </c>
       <c r="C41" t="str">
-        <v>Điện nước</v>
+        <v>Sơn sửa</v>
       </c>
       <c r="D41">
-        <v>9000000</v>
+        <v>7000000</v>
       </c>
       <c r="E41" t="str">
-        <v>Hoàn thiện điện nước</v>
+        <v>Sơn 3 phòng</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-36-RENO-RM-BASIC-HO</v>
       </c>
       <c r="B42" t="str">
         <v>PAINTING</v>
@@ -4797,29 +4797,29 @@
         <v>8500000</v>
       </c>
       <c r="E42" t="str">
-        <v>Sơn 4 phòng</v>
+        <v>Sơn 3 phòng</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-36-RENO-RM-BASIC-HO</v>
       </c>
       <c r="B43" t="str">
-        <v>PLUMBING</v>
+        <v>FLOORING</v>
       </c>
       <c r="C43" t="str">
-        <v>Điện nước</v>
+        <v>Sàn nhà</v>
       </c>
       <c r="D43">
-        <v>10500000</v>
+        <v>9500000</v>
       </c>
       <c r="E43" t="str">
-        <v>Hoàn thiện điện nước</v>
+        <v>Lát gạch từng phòng</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-37-RENO-RM-BASIC-HO</v>
       </c>
       <c r="B44" t="str">
         <v>PAINTING</v>
@@ -4836,347 +4836,347 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-38-RENO-RM-BASIC-HO</v>
       </c>
       <c r="B45" t="str">
-        <v>PLUMBING</v>
+        <v>PAINTING</v>
       </c>
       <c r="C45" t="str">
-        <v>Điện nước</v>
+        <v>Sơn sửa</v>
       </c>
       <c r="D45">
-        <v>12000000</v>
+        <v>11500000</v>
       </c>
       <c r="E45" t="str">
-        <v>Hoàn thiện điện nước</v>
+        <v>Sơn 3 phòng</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-39-RENO-RM-BASIC-HO</v>
       </c>
       <c r="B46" t="str">
-        <v>FLOORING</v>
+        <v>PAINTING</v>
       </c>
       <c r="C46" t="str">
-        <v>Sàn nhà</v>
+        <v>Sơn sửa</v>
       </c>
       <c r="D46">
-        <v>11000000</v>
+        <v>13000000</v>
       </c>
       <c r="E46" t="str">
-        <v>Lát gạch từng phòng</v>
+        <v>Sơn 3 phòng</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-39-RENO-RM-BASIC-HO</v>
       </c>
       <c r="B47" t="str">
-        <v>PAINTING</v>
+        <v>FLOORING</v>
       </c>
       <c r="C47" t="str">
-        <v>Sơn sửa</v>
+        <v>Sàn nhà</v>
       </c>
       <c r="D47">
-        <v>11500000</v>
+        <v>14000000</v>
       </c>
       <c r="E47" t="str">
-        <v>Sơn 4 phòng</v>
+        <v>Lát gạch từng phòng</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B48" t="str">
-        <v>PLUMBING</v>
+        <v>PAINTING</v>
       </c>
       <c r="C48" t="str">
-        <v>Điện nước</v>
+        <v>Sơn sửa</v>
       </c>
       <c r="D48">
-        <v>13500000</v>
+        <v>7000000</v>
       </c>
       <c r="E48" t="str">
-        <v>Hoàn thiện điện nước</v>
+        <v>Sơn 3 phòng</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
+        <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B49" t="str">
-        <v>PAINTING</v>
+        <v>PLUMBING</v>
       </c>
       <c r="C49" t="str">
-        <v>Sơn sửa</v>
+        <v>Điện nước</v>
       </c>
       <c r="D49">
-        <v>13000000</v>
+        <v>9000000</v>
       </c>
       <c r="E49" t="str">
-        <v>Sơn 4 phòng</v>
+        <v>Hoàn thiện điện nước</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
+        <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B50" t="str">
-        <v>PLUMBING</v>
+        <v>EQUIPMENT</v>
       </c>
       <c r="C50" t="str">
-        <v>Điện nước</v>
+        <v>Thiết bị mua thêm</v>
       </c>
       <c r="D50">
-        <v>15000000</v>
+        <v>8500000</v>
       </c>
       <c r="E50" t="str">
-        <v>Hoàn thiện điện nước</v>
+        <v>Mua &amp; lắp TB mới đợt 2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
+        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B51" t="str">
-        <v>FURNITURE</v>
+        <v>PAINTING</v>
       </c>
       <c r="C51" t="str">
-        <v>Nội thất</v>
+        <v>Sơn sửa</v>
       </c>
       <c r="D51">
-        <v>16000000</v>
+        <v>8500000</v>
       </c>
       <c r="E51" t="str">
-        <v>Lắp đặt nội thất</v>
+        <v>Sơn 4 phòng</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B52" t="str">
-        <v>PAINTING</v>
+        <v>PLUMBING</v>
       </c>
       <c r="C52" t="str">
-        <v>Sơn sửa</v>
+        <v>Điện nước</v>
       </c>
       <c r="D52">
-        <v>7000000</v>
+        <v>10500000</v>
       </c>
       <c r="E52" t="str">
-        <v>Sơn 4 phòng</v>
+        <v>Hoàn thiện điện nước</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B53" t="str">
-        <v>PLUMBING</v>
+        <v>EQUIPMENT</v>
       </c>
       <c r="C53" t="str">
-        <v>Điện nước</v>
+        <v>Thiết bị mua thêm</v>
       </c>
       <c r="D53">
-        <v>9000000</v>
+        <v>10000000</v>
       </c>
       <c r="E53" t="str">
-        <v>Hoàn thiện điện nước</v>
+        <v>Mua &amp; lắp TB mới đợt 2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B54" t="str">
-        <v>FURNITURE</v>
+        <v>PAINTING</v>
       </c>
       <c r="C54" t="str">
-        <v>Nội thất</v>
+        <v>Sơn sửa</v>
       </c>
       <c r="D54">
         <v>10000000</v>
       </c>
       <c r="E54" t="str">
-        <v>Lắp đặt nội thất</v>
+        <v>Sơn 3 phòng</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B55" t="str">
-        <v>FLOORING</v>
+        <v>PLUMBING</v>
       </c>
       <c r="C55" t="str">
-        <v>Sàn nhà</v>
+        <v>Điện nước</v>
       </c>
       <c r="D55">
-        <v>8000000</v>
+        <v>12000000</v>
       </c>
       <c r="E55" t="str">
-        <v>Lát gạch từng phòng</v>
+        <v>Hoàn thiện điện nước</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B56" t="str">
-        <v>PAINTING</v>
+        <v>EQUIPMENT</v>
       </c>
       <c r="C56" t="str">
-        <v>Sơn sửa</v>
+        <v>Thiết bị mua thêm</v>
       </c>
       <c r="D56">
-        <v>8500000</v>
+        <v>11500000</v>
       </c>
       <c r="E56" t="str">
-        <v>Sơn 4 phòng</v>
+        <v>Mua &amp; lắp TB mới đợt 2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B57" t="str">
-        <v>PLUMBING</v>
+        <v>FLOORING</v>
       </c>
       <c r="C57" t="str">
-        <v>Điện nước</v>
+        <v>Sàn nhà</v>
       </c>
       <c r="D57">
-        <v>10500000</v>
+        <v>11000000</v>
       </c>
       <c r="E57" t="str">
-        <v>Hoàn thiện điện nước</v>
+        <v>Lát gạch từng phòng</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B58" t="str">
-        <v>FURNITURE</v>
+        <v>PAINTING</v>
       </c>
       <c r="C58" t="str">
-        <v>Nội thất</v>
+        <v>Sơn sửa</v>
       </c>
       <c r="D58">
         <v>11500000</v>
       </c>
       <c r="E58" t="str">
-        <v>Lắp đặt nội thất</v>
+        <v>Sơn 4 phòng</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B59" t="str">
-        <v>PAINTING</v>
+        <v>PLUMBING</v>
       </c>
       <c r="C59" t="str">
-        <v>Sơn sửa</v>
+        <v>Điện nước</v>
       </c>
       <c r="D59">
-        <v>10000000</v>
+        <v>13500000</v>
       </c>
       <c r="E59" t="str">
-        <v>Sơn 4 phòng</v>
+        <v>Hoàn thiện điện nước</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B60" t="str">
-        <v>PLUMBING</v>
+        <v>EQUIPMENT</v>
       </c>
       <c r="C60" t="str">
-        <v>Điện nước</v>
+        <v>Thiết bị mua thêm</v>
       </c>
       <c r="D60">
-        <v>12000000</v>
+        <v>13000000</v>
       </c>
       <c r="E60" t="str">
-        <v>Hoàn thiện điện nước</v>
+        <v>Mua &amp; lắp TB mới đợt 2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B61" t="str">
-        <v>FURNITURE</v>
+        <v>PAINTING</v>
       </c>
       <c r="C61" t="str">
-        <v>Nội thất</v>
+        <v>Sơn sửa</v>
       </c>
       <c r="D61">
         <v>13000000</v>
       </c>
       <c r="E61" t="str">
-        <v>Lắp đặt nội thất</v>
+        <v>Sơn 4 phòng</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B62" t="str">
-        <v>PAINTING</v>
+        <v>PLUMBING</v>
       </c>
       <c r="C62" t="str">
-        <v>Sơn sửa</v>
+        <v>Điện nước</v>
       </c>
       <c r="D62">
-        <v>11500000</v>
+        <v>15000000</v>
       </c>
       <c r="E62" t="str">
-        <v>Sơn 3 phòng</v>
+        <v>Hoàn thiện điện nước</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B63" t="str">
-        <v>PLUMBING</v>
+        <v>FURNITURE</v>
       </c>
       <c r="C63" t="str">
-        <v>Điện nước</v>
+        <v>Nội thất</v>
       </c>
       <c r="D63">
-        <v>13500000</v>
+        <v>16000000</v>
       </c>
       <c r="E63" t="str">
-        <v>Hoàn thiện điện nước</v>
+        <v>Lắp đặt nội thất</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B64" t="str">
-        <v>FLOORING</v>
+        <v>EQUIPMENT</v>
       </c>
       <c r="C64" t="str">
-        <v>Sàn nhà</v>
+        <v>Thiết bị mua thêm</v>
       </c>
       <c r="D64">
-        <v>12500000</v>
+        <v>14500000</v>
       </c>
       <c r="E64" t="str">
-        <v>Lát gạch từng phòng</v>
+        <v>Mua &amp; lắp TB mới đợt 2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B65" t="str">
         <v>PAINTING</v>
@@ -5185,15 +5185,15 @@
         <v>Sơn sửa</v>
       </c>
       <c r="D65">
-        <v>13000000</v>
+        <v>7000000</v>
       </c>
       <c r="E65" t="str">
-        <v>Sơn 3 phòng</v>
+        <v>Sơn 4 phòng</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B66" t="str">
         <v>PLUMBING</v>
@@ -5202,7 +5202,7 @@
         <v>Điện nước</v>
       </c>
       <c r="D66">
-        <v>15000000</v>
+        <v>9000000</v>
       </c>
       <c r="E66" t="str">
         <v>Hoàn thiện điện nước</v>
@@ -5210,48 +5210,371 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B67" t="str">
-        <v>PAINTING</v>
+        <v>FURNITURE</v>
       </c>
       <c r="C67" t="str">
-        <v>Sơn sửa</v>
+        <v>Nội thất</v>
       </c>
       <c r="D67">
-        <v>7000000</v>
+        <v>10000000</v>
       </c>
       <c r="E67" t="str">
-        <v>Sơn 3 phòng</v>
+        <v>Lắp đặt nội thất</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
+        <v>HD-MTX-45-RENO-RM-FULL</v>
+      </c>
+      <c r="B68" t="str">
+        <v>EQUIPMENT</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Thiết bị mua thêm</v>
+      </c>
+      <c r="D68">
+        <v>8500000</v>
+      </c>
+      <c r="E68" t="str">
+        <v>Mua &amp; lắp TB mới đợt 2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>HD-MTX-45-RENO-RM-FULL</v>
+      </c>
+      <c r="B69" t="str">
+        <v>FLOORING</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Sàn nhà</v>
+      </c>
+      <c r="D69">
+        <v>8000000</v>
+      </c>
+      <c r="E69" t="str">
+        <v>Lát gạch từng phòng</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>HD-MTX-46-RENO-RM-FULL</v>
+      </c>
+      <c r="B70" t="str">
+        <v>PAINTING</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Sơn sửa</v>
+      </c>
+      <c r="D70">
+        <v>8500000</v>
+      </c>
+      <c r="E70" t="str">
+        <v>Sơn 4 phòng</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>HD-MTX-46-RENO-RM-FULL</v>
+      </c>
+      <c r="B71" t="str">
+        <v>PLUMBING</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Điện nước</v>
+      </c>
+      <c r="D71">
+        <v>10500000</v>
+      </c>
+      <c r="E71" t="str">
+        <v>Hoàn thiện điện nước</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>HD-MTX-46-RENO-RM-FULL</v>
+      </c>
+      <c r="B72" t="str">
+        <v>FURNITURE</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Nội thất</v>
+      </c>
+      <c r="D72">
+        <v>11500000</v>
+      </c>
+      <c r="E72" t="str">
+        <v>Lắp đặt nội thất</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>HD-MTX-46-RENO-RM-FULL</v>
+      </c>
+      <c r="B73" t="str">
+        <v>EQUIPMENT</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Thiết bị mua thêm</v>
+      </c>
+      <c r="D73">
+        <v>10000000</v>
+      </c>
+      <c r="E73" t="str">
+        <v>Mua &amp; lắp TB mới đợt 2</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B74" t="str">
+        <v>PAINTING</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Sơn sửa</v>
+      </c>
+      <c r="D74">
+        <v>10000000</v>
+      </c>
+      <c r="E74" t="str">
+        <v>Sơn 4 phòng</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B75" t="str">
+        <v>PLUMBING</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Điện nước</v>
+      </c>
+      <c r="D75">
+        <v>12000000</v>
+      </c>
+      <c r="E75" t="str">
+        <v>Hoàn thiện điện nước</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B76" t="str">
+        <v>FURNITURE</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Nội thất</v>
+      </c>
+      <c r="D76">
+        <v>13000000</v>
+      </c>
+      <c r="E76" t="str">
+        <v>Lắp đặt nội thất</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>HD-MTX-47-RENO-RM-FULL</v>
+      </c>
+      <c r="B77" t="str">
+        <v>EQUIPMENT</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Thiết bị mua thêm</v>
+      </c>
+      <c r="D77">
+        <v>11500000</v>
+      </c>
+      <c r="E77" t="str">
+        <v>Mua &amp; lắp TB mới đợt 2</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B78" t="str">
+        <v>PAINTING</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Sơn sửa</v>
+      </c>
+      <c r="D78">
+        <v>11500000</v>
+      </c>
+      <c r="E78" t="str">
+        <v>Sơn 3 phòng</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B79" t="str">
+        <v>PLUMBING</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Điện nước</v>
+      </c>
+      <c r="D79">
+        <v>13500000</v>
+      </c>
+      <c r="E79" t="str">
+        <v>Hoàn thiện điện nước</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B80" t="str">
+        <v>EQUIPMENT</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Thiết bị mua thêm</v>
+      </c>
+      <c r="D80">
+        <v>13000000</v>
+      </c>
+      <c r="E80" t="str">
+        <v>Mua &amp; lắp TB mới đợt 2</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B81" t="str">
+        <v>FLOORING</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Sàn nhà</v>
+      </c>
+      <c r="D81">
+        <v>12500000</v>
+      </c>
+      <c r="E81" t="str">
+        <v>Lát gạch từng phòng</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B82" t="str">
+        <v>PAINTING</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Sơn sửa</v>
+      </c>
+      <c r="D82">
+        <v>13000000</v>
+      </c>
+      <c r="E82" t="str">
+        <v>Sơn 3 phòng</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B83" t="str">
+        <v>PLUMBING</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Điện nước</v>
+      </c>
+      <c r="D83">
+        <v>15000000</v>
+      </c>
+      <c r="E83" t="str">
+        <v>Hoàn thiện điện nước</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B84" t="str">
+        <v>EQUIPMENT</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Thiết bị mua thêm</v>
+      </c>
+      <c r="D84">
+        <v>14500000</v>
+      </c>
+      <c r="E84" t="str">
+        <v>Mua &amp; lắp TB mới đợt 2</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
         <v>HD-MTX-50-RENO-RM-HO-BUY</v>
       </c>
-      <c r="B68" t="str">
+      <c r="B85" t="str">
+        <v>PAINTING</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Sơn sửa</v>
+      </c>
+      <c r="D85">
+        <v>7000000</v>
+      </c>
+      <c r="E85" t="str">
+        <v>Sơn 3 phòng</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B86" t="str">
         <v>PLUMBING</v>
       </c>
-      <c r="C68" t="str">
+      <c r="C86" t="str">
         <v>Điện nước</v>
       </c>
-      <c r="D68">
+      <c r="D86">
         <v>9000000</v>
       </c>
-      <c r="E68" t="str">
+      <c r="E86" t="str">
         <v>Hoàn thiện điện nước</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B87" t="str">
+        <v>EQUIPMENT</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Thiết bị mua thêm</v>
+      </c>
+      <c r="D87">
+        <v>8500000</v>
+      </c>
+      <c r="E87" t="str">
+        <v>Mua &amp; lắp TB mới đợt 2</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E68"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E87"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M190"/>
+  <dimension ref="A1:M207"/>
   <cols>
     <col min="1" max="1" width="17.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -5347,7 +5670,7 @@
         <v>3300000</v>
       </c>
       <c r="M2" t="str">
-        <v>ĐH phòng khách</v>
+        <v>ĐH phòng khách — NT cơ bản</v>
       </c>
     </row>
     <row r="3">
@@ -5511,7 +5834,7 @@
         <v>2250000</v>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>Tủ lạnh — NT cơ bản</v>
       </c>
     </row>
     <row r="7">
@@ -5593,7 +5916,7 @@
         <v>3300000</v>
       </c>
       <c r="M8" t="str">
-        <v>ĐH phòng khách</v>
+        <v>ĐH phòng khách — NT cơ bản</v>
       </c>
     </row>
     <row r="9">
@@ -5798,7 +6121,7 @@
         <v>2250000</v>
       </c>
       <c r="M13" t="str">
-        <v/>
+        <v>Tủ lạnh — NT cơ bản</v>
       </c>
     </row>
     <row r="14">
@@ -5880,7 +6203,7 @@
         <v>3300000</v>
       </c>
       <c r="M15" t="str">
-        <v>ĐH phòng khách</v>
+        <v>ĐH phòng khách — NT cơ bản</v>
       </c>
     </row>
     <row r="16">
@@ -6003,7 +6326,7 @@
         <v>2250000</v>
       </c>
       <c r="M18" t="str">
-        <v/>
+        <v>Tủ lạnh — NT cơ bản</v>
       </c>
     </row>
     <row r="19">
@@ -6099,7 +6422,7 @@
         <v>LIVING_ROOM</v>
       </c>
       <c r="D21" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="E21" t="str">
         <v>NEW</v>
@@ -6111,22 +6434,22 @@
         <v>1</v>
       </c>
       <c r="H21">
-        <v>9500000</v>
+        <v>1200000</v>
       </c>
       <c r="I21">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J21" t="str">
         <v>2026-03-01</v>
       </c>
       <c r="K21" t="str">
-        <v>2028-03-01</v>
+        <v>2027-03-01</v>
       </c>
       <c r="L21">
-        <v>2850000</v>
+        <v>360000</v>
       </c>
       <c r="M21" t="str">
-        <v>ĐH PN 1</v>
+        <v>Quạt trần PK</v>
       </c>
     </row>
     <row r="22">
@@ -6140,7 +6463,7 @@
         <v>LIVING_ROOM</v>
       </c>
       <c r="D22" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E22" t="str">
         <v>NEW</v>
@@ -6152,22 +6475,22 @@
         <v>1</v>
       </c>
       <c r="H22">
-        <v>5500000</v>
+        <v>9500000</v>
       </c>
       <c r="I22">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J22" t="str">
         <v>2026-03-01</v>
       </c>
       <c r="K22" t="str">
-        <v>2027-03-01</v>
+        <v>2028-03-01</v>
       </c>
       <c r="L22">
-        <v>1650000</v>
+        <v>2850000</v>
       </c>
       <c r="M22" t="str">
-        <v>Giường PN 1</v>
+        <v>ĐH PN 1</v>
       </c>
     </row>
     <row r="23">
@@ -6181,7 +6504,7 @@
         <v>LIVING_ROOM</v>
       </c>
       <c r="D23" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="E23" t="str">
         <v>NEW</v>
@@ -6193,7 +6516,7 @@
         <v>1</v>
       </c>
       <c r="H23">
-        <v>750000</v>
+        <v>5500000</v>
       </c>
       <c r="I23">
         <v>12</v>
@@ -6205,10 +6528,10 @@
         <v>2027-03-01</v>
       </c>
       <c r="L23">
-        <v>225000</v>
+        <v>1650000</v>
       </c>
       <c r="M23" t="str">
-        <v>Quạt PN 1</v>
+        <v>Giường PN 1</v>
       </c>
     </row>
     <row r="24">
@@ -6222,7 +6545,7 @@
         <v>LIVING_ROOM</v>
       </c>
       <c r="D24" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="E24" t="str">
         <v>NEW</v>
@@ -6234,22 +6557,22 @@
         <v>1</v>
       </c>
       <c r="H24">
-        <v>9500000</v>
+        <v>750000</v>
       </c>
       <c r="I24">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J24" t="str">
         <v>2026-03-01</v>
       </c>
       <c r="K24" t="str">
-        <v>2028-03-01</v>
+        <v>2027-03-01</v>
       </c>
       <c r="L24">
-        <v>2850000</v>
+        <v>225000</v>
       </c>
       <c r="M24" t="str">
-        <v>ĐH PN 2</v>
+        <v>Quạt PN 1</v>
       </c>
     </row>
     <row r="25">
@@ -6263,7 +6586,7 @@
         <v>LIVING_ROOM</v>
       </c>
       <c r="D25" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E25" t="str">
         <v>NEW</v>
@@ -6275,22 +6598,22 @@
         <v>1</v>
       </c>
       <c r="H25">
-        <v>4800000</v>
+        <v>9600000</v>
       </c>
       <c r="I25">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J25" t="str">
         <v>2026-03-01</v>
       </c>
       <c r="K25" t="str">
-        <v>2027-03-01</v>
+        <v>2028-03-01</v>
       </c>
       <c r="L25">
-        <v>1440000</v>
+        <v>2880000</v>
       </c>
       <c r="M25" t="str">
-        <v>Giường PN 2</v>
+        <v>ĐH PN 2</v>
       </c>
     </row>
     <row r="26">
@@ -6304,7 +6627,7 @@
         <v>LIVING_ROOM</v>
       </c>
       <c r="D26" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="E26" t="str">
         <v>NEW</v>
@@ -6316,7 +6639,7 @@
         <v>1</v>
       </c>
       <c r="H26">
-        <v>750000</v>
+        <v>4800000</v>
       </c>
       <c r="I26">
         <v>12</v>
@@ -6328,10 +6651,10 @@
         <v>2027-03-01</v>
       </c>
       <c r="L26">
-        <v>225000</v>
+        <v>1440000</v>
       </c>
       <c r="M26" t="str">
-        <v>Quạt PN 2</v>
+        <v>Giường PN 2</v>
       </c>
     </row>
     <row r="27">
@@ -6357,7 +6680,7 @@
         <v>1</v>
       </c>
       <c r="H27">
-        <v>1200000</v>
+        <v>750000</v>
       </c>
       <c r="I27">
         <v>12</v>
@@ -6369,10 +6692,10 @@
         <v>2027-03-01</v>
       </c>
       <c r="L27">
-        <v>360000</v>
+        <v>225000</v>
       </c>
       <c r="M27" t="str">
-        <v>Quạt trần PK</v>
+        <v>Quạt PN 2</v>
       </c>
     </row>
     <row r="28">
@@ -6506,10 +6829,10 @@
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>BALCONY</v>
+        <v>BATHROOM</v>
       </c>
       <c r="D31" t="str">
-        <v>Quạt</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E31" t="str">
         <v>NEW</v>
@@ -6521,7 +6844,7 @@
         <v>1</v>
       </c>
       <c r="H31">
-        <v>650000</v>
+        <v>3000000</v>
       </c>
       <c r="I31">
         <v>12</v>
@@ -6533,24 +6856,24 @@
         <v>2027-03-01</v>
       </c>
       <c r="L31">
-        <v>195000</v>
+        <v>900000</v>
       </c>
       <c r="M31" t="str">
-        <v/>
+        <v>NL tầng 2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>HD-MTX-26-RENO-WH-FULL</v>
+        <v>HD-MTX-25-RENO-WH-FULL</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>LIVING_ROOM</v>
+        <v>BALCONY</v>
       </c>
       <c r="D32" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="E32" t="str">
         <v>NEW</v>
@@ -6562,22 +6885,22 @@
         <v>1</v>
       </c>
       <c r="H32">
-        <v>14000000</v>
+        <v>650000</v>
       </c>
       <c r="I32">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="J32" t="str">
-        <v>2026-04-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="K32" t="str">
-        <v>2029-04-01</v>
+        <v>2027-03-01</v>
       </c>
       <c r="L32">
-        <v>4200000</v>
+        <v>195000</v>
       </c>
       <c r="M32" t="str">
-        <v>ĐH phòng khách</v>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -6603,22 +6926,22 @@
         <v>1</v>
       </c>
       <c r="H33">
-        <v>9500000</v>
+        <v>14000000</v>
       </c>
       <c r="I33">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="J33" t="str">
         <v>2026-04-01</v>
       </c>
       <c r="K33" t="str">
-        <v>2028-04-01</v>
+        <v>2029-04-01</v>
       </c>
       <c r="L33">
-        <v>2850000</v>
+        <v>4200000</v>
       </c>
       <c r="M33" t="str">
-        <v>ĐH PN 1</v>
+        <v>ĐH phòng khách</v>
       </c>
     </row>
     <row r="34">
@@ -6632,7 +6955,7 @@
         <v>LIVING_ROOM</v>
       </c>
       <c r="D34" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E34" t="str">
         <v>NEW</v>
@@ -6644,7 +6967,7 @@
         <v>1</v>
       </c>
       <c r="H34">
-        <v>5500000</v>
+        <v>1200000</v>
       </c>
       <c r="I34">
         <v>12</v>
@@ -6656,10 +6979,10 @@
         <v>2027-04-01</v>
       </c>
       <c r="L34">
-        <v>1650000</v>
+        <v>360000</v>
       </c>
       <c r="M34" t="str">
-        <v>Giường PN 1</v>
+        <v>Quạt trần PK</v>
       </c>
     </row>
     <row r="35">
@@ -6673,7 +6996,7 @@
         <v>LIVING_ROOM</v>
       </c>
       <c r="D35" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E35" t="str">
         <v>NEW</v>
@@ -6685,22 +7008,22 @@
         <v>1</v>
       </c>
       <c r="H35">
-        <v>750000</v>
+        <v>9500000</v>
       </c>
       <c r="I35">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J35" t="str">
         <v>2026-04-01</v>
       </c>
       <c r="K35" t="str">
-        <v>2027-04-01</v>
+        <v>2028-04-01</v>
       </c>
       <c r="L35">
-        <v>225000</v>
+        <v>2850000</v>
       </c>
       <c r="M35" t="str">
-        <v>Quạt PN 1</v>
+        <v>ĐH PN 1</v>
       </c>
     </row>
     <row r="36">
@@ -6714,7 +7037,7 @@
         <v>LIVING_ROOM</v>
       </c>
       <c r="D36" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="E36" t="str">
         <v>NEW</v>
@@ -6726,22 +7049,22 @@
         <v>1</v>
       </c>
       <c r="H36">
-        <v>9500000</v>
+        <v>5500000</v>
       </c>
       <c r="I36">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J36" t="str">
         <v>2026-04-01</v>
       </c>
       <c r="K36" t="str">
-        <v>2028-04-01</v>
+        <v>2027-04-01</v>
       </c>
       <c r="L36">
-        <v>2850000</v>
+        <v>1650000</v>
       </c>
       <c r="M36" t="str">
-        <v>ĐH PN 2</v>
+        <v>Giường PN 1</v>
       </c>
     </row>
     <row r="37">
@@ -6755,7 +7078,7 @@
         <v>LIVING_ROOM</v>
       </c>
       <c r="D37" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E37" t="str">
         <v>NEW</v>
@@ -6767,7 +7090,7 @@
         <v>1</v>
       </c>
       <c r="H37">
-        <v>4800000</v>
+        <v>750000</v>
       </c>
       <c r="I37">
         <v>12</v>
@@ -6779,10 +7102,10 @@
         <v>2027-04-01</v>
       </c>
       <c r="L37">
-        <v>1440000</v>
+        <v>225000</v>
       </c>
       <c r="M37" t="str">
-        <v>Giường PN 2</v>
+        <v>Quạt PN 1</v>
       </c>
     </row>
     <row r="38">
@@ -6796,7 +7119,7 @@
         <v>LIVING_ROOM</v>
       </c>
       <c r="D38" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E38" t="str">
         <v>NEW</v>
@@ -6808,22 +7131,22 @@
         <v>1</v>
       </c>
       <c r="H38">
-        <v>750000</v>
+        <v>9600000</v>
       </c>
       <c r="I38">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J38" t="str">
         <v>2026-04-01</v>
       </c>
       <c r="K38" t="str">
-        <v>2027-04-01</v>
+        <v>2028-04-01</v>
       </c>
       <c r="L38">
-        <v>225000</v>
+        <v>2880000</v>
       </c>
       <c r="M38" t="str">
-        <v>Quạt PN 2</v>
+        <v>ĐH PN 2</v>
       </c>
     </row>
     <row r="39">
@@ -6837,7 +7160,7 @@
         <v>LIVING_ROOM</v>
       </c>
       <c r="D39" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="E39" t="str">
         <v>NEW</v>
@@ -6849,22 +7172,22 @@
         <v>1</v>
       </c>
       <c r="H39">
-        <v>9500000</v>
+        <v>4800000</v>
       </c>
       <c r="I39">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J39" t="str">
         <v>2026-04-01</v>
       </c>
       <c r="K39" t="str">
-        <v>2028-04-01</v>
+        <v>2027-04-01</v>
       </c>
       <c r="L39">
-        <v>2850000</v>
+        <v>1440000</v>
       </c>
       <c r="M39" t="str">
-        <v>ĐH PN 3</v>
+        <v>Giường PN 2</v>
       </c>
     </row>
     <row r="40">
@@ -6878,7 +7201,7 @@
         <v>LIVING_ROOM</v>
       </c>
       <c r="D40" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E40" t="str">
         <v>NEW</v>
@@ -6890,7 +7213,7 @@
         <v>1</v>
       </c>
       <c r="H40">
-        <v>4800000</v>
+        <v>750000</v>
       </c>
       <c r="I40">
         <v>12</v>
@@ -6902,10 +7225,10 @@
         <v>2027-04-01</v>
       </c>
       <c r="L40">
-        <v>1440000</v>
+        <v>225000</v>
       </c>
       <c r="M40" t="str">
-        <v>Giường PN 3</v>
+        <v>Quạt PN 2</v>
       </c>
     </row>
     <row r="41">
@@ -6919,7 +7242,7 @@
         <v>LIVING_ROOM</v>
       </c>
       <c r="D41" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E41" t="str">
         <v>NEW</v>
@@ -6931,22 +7254,22 @@
         <v>1</v>
       </c>
       <c r="H41">
-        <v>750000</v>
+        <v>9700000</v>
       </c>
       <c r="I41">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J41" t="str">
         <v>2026-04-01</v>
       </c>
       <c r="K41" t="str">
-        <v>2027-04-01</v>
+        <v>2028-04-01</v>
       </c>
       <c r="L41">
-        <v>225000</v>
+        <v>2910000</v>
       </c>
       <c r="M41" t="str">
-        <v>Quạt PN 3</v>
+        <v>ĐH PN 3</v>
       </c>
     </row>
     <row r="42">
@@ -6960,7 +7283,7 @@
         <v>LIVING_ROOM</v>
       </c>
       <c r="D42" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="E42" t="str">
         <v>NEW</v>
@@ -6972,7 +7295,7 @@
         <v>1</v>
       </c>
       <c r="H42">
-        <v>1200000</v>
+        <v>4800000</v>
       </c>
       <c r="I42">
         <v>12</v>
@@ -6984,10 +7307,10 @@
         <v>2027-04-01</v>
       </c>
       <c r="L42">
-        <v>360000</v>
+        <v>1440000</v>
       </c>
       <c r="M42" t="str">
-        <v>Quạt trần PK</v>
+        <v>Giường PN 3</v>
       </c>
     </row>
     <row r="43">
@@ -6998,10 +7321,10 @@
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>KITCHEN</v>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D43" t="str">
-        <v>Tủ lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="E43" t="str">
         <v>NEW</v>
@@ -7013,22 +7336,22 @@
         <v>1</v>
       </c>
       <c r="H43">
-        <v>8500000</v>
+        <v>750000</v>
       </c>
       <c r="I43">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J43" t="str">
         <v>2026-04-01</v>
       </c>
       <c r="K43" t="str">
-        <v>2028-04-01</v>
+        <v>2027-04-01</v>
       </c>
       <c r="L43">
-        <v>2550000</v>
+        <v>225000</v>
       </c>
       <c r="M43" t="str">
-        <v/>
+        <v>Quạt PN 3</v>
       </c>
     </row>
     <row r="44">
@@ -7042,7 +7365,7 @@
         <v>KITCHEN</v>
       </c>
       <c r="D44" t="str">
-        <v>Máy giặt</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="E44" t="str">
         <v>NEW</v>
@@ -7054,7 +7377,7 @@
         <v>1</v>
       </c>
       <c r="H44">
-        <v>9500000</v>
+        <v>8500000</v>
       </c>
       <c r="I44">
         <v>24</v>
@@ -7066,7 +7389,7 @@
         <v>2028-04-01</v>
       </c>
       <c r="L44">
-        <v>2850000</v>
+        <v>2550000</v>
       </c>
       <c r="M44" t="str">
         <v/>
@@ -7080,10 +7403,10 @@
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>BATHROOM</v>
+        <v>KITCHEN</v>
       </c>
       <c r="D45" t="str">
-        <v>Nóng lạnh</v>
+        <v>Máy giặt</v>
       </c>
       <c r="E45" t="str">
         <v>NEW</v>
@@ -7095,19 +7418,19 @@
         <v>1</v>
       </c>
       <c r="H45">
-        <v>3200000</v>
+        <v>9500000</v>
       </c>
       <c r="I45">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J45" t="str">
         <v>2026-04-01</v>
       </c>
       <c r="K45" t="str">
-        <v>2027-04-01</v>
+        <v>2028-04-01</v>
       </c>
       <c r="L45">
-        <v>960000</v>
+        <v>2850000</v>
       </c>
       <c r="M45" t="str">
         <v/>
@@ -7121,10 +7444,10 @@
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>BALCONY</v>
+        <v>BATHROOM</v>
       </c>
       <c r="D46" t="str">
-        <v>Quạt</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E46" t="str">
         <v>NEW</v>
@@ -7136,7 +7459,7 @@
         <v>1</v>
       </c>
       <c r="H46">
-        <v>650000</v>
+        <v>3200000</v>
       </c>
       <c r="I46">
         <v>12</v>
@@ -7148,7 +7471,7 @@
         <v>2027-04-01</v>
       </c>
       <c r="L46">
-        <v>195000</v>
+        <v>960000</v>
       </c>
       <c r="M46" t="str">
         <v/>
@@ -7156,16 +7479,16 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>HD-MTX-27-RENO-WH-FULL</v>
+        <v>HD-MTX-26-RENO-WH-FULL</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>LIVING_ROOM</v>
+        <v>BALCONY</v>
       </c>
       <c r="D47" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="E47" t="str">
         <v>NEW</v>
@@ -7177,22 +7500,22 @@
         <v>1</v>
       </c>
       <c r="H47">
-        <v>14000000</v>
+        <v>650000</v>
       </c>
       <c r="I47">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="J47" t="str">
-        <v>2026-05-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K47" t="str">
-        <v>2029-05-01</v>
+        <v>2027-04-01</v>
       </c>
       <c r="L47">
-        <v>4200000</v>
+        <v>195000</v>
       </c>
       <c r="M47" t="str">
-        <v>ĐH phòng khách</v>
+        <v/>
       </c>
     </row>
     <row r="48">
@@ -7218,22 +7541,22 @@
         <v>1</v>
       </c>
       <c r="H48">
-        <v>9500000</v>
+        <v>14000000</v>
       </c>
       <c r="I48">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="J48" t="str">
         <v>2026-05-01</v>
       </c>
       <c r="K48" t="str">
-        <v>2028-05-01</v>
+        <v>2029-05-01</v>
       </c>
       <c r="L48">
-        <v>2850000</v>
+        <v>4200000</v>
       </c>
       <c r="M48" t="str">
-        <v>ĐH PN 1</v>
+        <v>ĐH phòng khách</v>
       </c>
     </row>
     <row r="49">
@@ -7247,7 +7570,7 @@
         <v>LIVING_ROOM</v>
       </c>
       <c r="D49" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E49" t="str">
         <v>NEW</v>
@@ -7259,7 +7582,7 @@
         <v>1</v>
       </c>
       <c r="H49">
-        <v>5500000</v>
+        <v>1200000</v>
       </c>
       <c r="I49">
         <v>12</v>
@@ -7271,10 +7594,10 @@
         <v>2027-05-01</v>
       </c>
       <c r="L49">
-        <v>1650000</v>
+        <v>360000</v>
       </c>
       <c r="M49" t="str">
-        <v>Giường PN 1</v>
+        <v>Quạt trần PK</v>
       </c>
     </row>
     <row r="50">
@@ -7288,7 +7611,7 @@
         <v>LIVING_ROOM</v>
       </c>
       <c r="D50" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E50" t="str">
         <v>NEW</v>
@@ -7300,22 +7623,22 @@
         <v>1</v>
       </c>
       <c r="H50">
-        <v>750000</v>
+        <v>9500000</v>
       </c>
       <c r="I50">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J50" t="str">
         <v>2026-05-01</v>
       </c>
       <c r="K50" t="str">
-        <v>2027-05-01</v>
+        <v>2028-05-01</v>
       </c>
       <c r="L50">
-        <v>225000</v>
+        <v>2850000</v>
       </c>
       <c r="M50" t="str">
-        <v>Quạt PN 1</v>
+        <v>ĐH PN 1</v>
       </c>
     </row>
     <row r="51">
@@ -7329,7 +7652,7 @@
         <v>LIVING_ROOM</v>
       </c>
       <c r="D51" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="E51" t="str">
         <v>NEW</v>
@@ -7341,7 +7664,7 @@
         <v>1</v>
       </c>
       <c r="H51">
-        <v>1200000</v>
+        <v>5500000</v>
       </c>
       <c r="I51">
         <v>12</v>
@@ -7353,10 +7676,10 @@
         <v>2027-05-01</v>
       </c>
       <c r="L51">
-        <v>360000</v>
+        <v>1650000</v>
       </c>
       <c r="M51" t="str">
-        <v>Quạt trần PK</v>
+        <v>Giường PN 1</v>
       </c>
     </row>
     <row r="52">
@@ -7367,10 +7690,10 @@
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>KITCHEN</v>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D52" t="str">
-        <v>Tủ lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="E52" t="str">
         <v>NEW</v>
@@ -7382,22 +7705,22 @@
         <v>1</v>
       </c>
       <c r="H52">
-        <v>8500000</v>
+        <v>750000</v>
       </c>
       <c r="I52">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J52" t="str">
         <v>2026-05-01</v>
       </c>
       <c r="K52" t="str">
-        <v>2028-05-01</v>
+        <v>2027-05-01</v>
       </c>
       <c r="L52">
-        <v>2550000</v>
+        <v>225000</v>
       </c>
       <c r="M52" t="str">
-        <v/>
+        <v>Quạt PN 1</v>
       </c>
     </row>
     <row r="53">
@@ -7411,7 +7734,7 @@
         <v>KITCHEN</v>
       </c>
       <c r="D53" t="str">
-        <v>Máy giặt</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="E53" t="str">
         <v>NEW</v>
@@ -7423,7 +7746,7 @@
         <v>1</v>
       </c>
       <c r="H53">
-        <v>9500000</v>
+        <v>8500000</v>
       </c>
       <c r="I53">
         <v>24</v>
@@ -7435,7 +7758,7 @@
         <v>2028-05-01</v>
       </c>
       <c r="L53">
-        <v>2850000</v>
+        <v>2550000</v>
       </c>
       <c r="M53" t="str">
         <v/>
@@ -7449,10 +7772,10 @@
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>BATHROOM</v>
+        <v>KITCHEN</v>
       </c>
       <c r="D54" t="str">
-        <v>Nóng lạnh</v>
+        <v>Máy giặt</v>
       </c>
       <c r="E54" t="str">
         <v>NEW</v>
@@ -7464,19 +7787,19 @@
         <v>1</v>
       </c>
       <c r="H54">
-        <v>3200000</v>
+        <v>9500000</v>
       </c>
       <c r="I54">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J54" t="str">
         <v>2026-05-01</v>
       </c>
       <c r="K54" t="str">
-        <v>2027-05-01</v>
+        <v>2028-05-01</v>
       </c>
       <c r="L54">
-        <v>960000</v>
+        <v>2850000</v>
       </c>
       <c r="M54" t="str">
         <v/>
@@ -7490,10 +7813,10 @@
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>BALCONY</v>
+        <v>BATHROOM</v>
       </c>
       <c r="D55" t="str">
-        <v>Quạt</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E55" t="str">
         <v>NEW</v>
@@ -7505,7 +7828,7 @@
         <v>1</v>
       </c>
       <c r="H55">
-        <v>650000</v>
+        <v>3200000</v>
       </c>
       <c r="I55">
         <v>12</v>
@@ -7517,7 +7840,7 @@
         <v>2027-05-01</v>
       </c>
       <c r="L55">
-        <v>195000</v>
+        <v>960000</v>
       </c>
       <c r="M55" t="str">
         <v/>
@@ -7525,16 +7848,16 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
+        <v>HD-MTX-27-RENO-WH-FULL</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>LIVING_ROOM</v>
+        <v>BATHROOM</v>
       </c>
       <c r="D56" t="str">
-        <v>Điều hòa</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E56" t="str">
         <v>NEW</v>
@@ -7546,33 +7869,33 @@
         <v>1</v>
       </c>
       <c r="H56">
-        <v>11000000</v>
+        <v>3000000</v>
       </c>
       <c r="I56">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J56" t="str">
-        <v>2026-08-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="K56" t="str">
-        <v>2028-08-01</v>
+        <v>2027-05-01</v>
       </c>
       <c r="L56">
-        <v>3300000</v>
+        <v>900000</v>
       </c>
       <c r="M56" t="str">
-        <v>ĐH phòng khách</v>
+        <v>NL tầng 2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
+        <v>HD-MTX-27-RENO-WH-FULL</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>LIVING_ROOM</v>
+        <v>BALCONY</v>
       </c>
       <c r="D57" t="str">
         <v>Quạt</v>
@@ -7587,22 +7910,22 @@
         <v>1</v>
       </c>
       <c r="H57">
-        <v>900000</v>
+        <v>650000</v>
       </c>
       <c r="I57">
         <v>12</v>
       </c>
       <c r="J57" t="str">
-        <v>2026-08-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="K57" t="str">
-        <v>2027-08-01</v>
+        <v>2027-05-01</v>
       </c>
       <c r="L57">
-        <v>270000</v>
+        <v>195000</v>
       </c>
       <c r="M57" t="str">
-        <v>Quạt trần PK</v>
+        <v/>
       </c>
     </row>
     <row r="58">
@@ -7616,7 +7939,7 @@
         <v>LIVING_ROOM</v>
       </c>
       <c r="D58" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E58" t="str">
         <v>NEW</v>
@@ -7628,22 +7951,22 @@
         <v>1</v>
       </c>
       <c r="H58">
-        <v>5000000</v>
+        <v>11000000</v>
       </c>
       <c r="I58">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J58" t="str">
         <v>2026-08-01</v>
       </c>
       <c r="K58" t="str">
-        <v>2027-08-01</v>
+        <v>2028-08-01</v>
       </c>
       <c r="L58">
-        <v>1500000</v>
+        <v>3300000</v>
       </c>
       <c r="M58" t="str">
-        <v>Giường PN 1</v>
+        <v>ĐH phòng khách — NT cơ bản</v>
       </c>
     </row>
     <row r="59">
@@ -7654,10 +7977,10 @@
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>KITCHEN</v>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D59" t="str">
-        <v>Tủ lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="E59" t="str">
         <v>NEW</v>
@@ -7669,22 +7992,22 @@
         <v>1</v>
       </c>
       <c r="H59">
-        <v>7500000</v>
+        <v>900000</v>
       </c>
       <c r="I59">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J59" t="str">
         <v>2026-08-01</v>
       </c>
       <c r="K59" t="str">
-        <v>2028-08-01</v>
+        <v>2027-08-01</v>
       </c>
       <c r="L59">
-        <v>2250000</v>
+        <v>270000</v>
       </c>
       <c r="M59" t="str">
-        <v/>
+        <v>Quạt trần PK</v>
       </c>
     </row>
     <row r="60">
@@ -7695,10 +8018,10 @@
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>BATHROOM</v>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D60" t="str">
-        <v>Nóng lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="E60" t="str">
         <v>NEW</v>
@@ -7710,7 +8033,7 @@
         <v>1</v>
       </c>
       <c r="H60">
-        <v>2800000</v>
+        <v>5000000</v>
       </c>
       <c r="I60">
         <v>12</v>
@@ -7722,24 +8045,24 @@
         <v>2027-08-01</v>
       </c>
       <c r="L60">
-        <v>840000</v>
+        <v>1500000</v>
       </c>
       <c r="M60" t="str">
-        <v/>
+        <v>Giường PN 1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
+        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>LIVING_ROOM</v>
+        <v>KITCHEN</v>
       </c>
       <c r="D61" t="str">
-        <v>Điều hòa</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="E61" t="str">
         <v>NEW</v>
@@ -7751,36 +8074,36 @@
         <v>1</v>
       </c>
       <c r="H61">
-        <v>11000000</v>
+        <v>7500000</v>
       </c>
       <c r="I61">
         <v>24</v>
       </c>
       <c r="J61" t="str">
-        <v>2026-09-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K61" t="str">
-        <v>2028-09-01</v>
+        <v>2028-08-01</v>
       </c>
       <c r="L61">
-        <v>3300000</v>
+        <v>2250000</v>
       </c>
       <c r="M61" t="str">
-        <v>ĐH phòng khách</v>
+        <v>Tủ lạnh — NT cơ bản</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
+        <v>HD-MTX-30-RENO-WH-HO-BUY</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>LIVING_ROOM</v>
+        <v>BATHROOM</v>
       </c>
       <c r="D62" t="str">
-        <v>Quạt</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E62" t="str">
         <v>NEW</v>
@@ -7792,22 +8115,22 @@
         <v>1</v>
       </c>
       <c r="H62">
-        <v>900000</v>
+        <v>2800000</v>
       </c>
       <c r="I62">
         <v>12</v>
       </c>
       <c r="J62" t="str">
-        <v>2026-09-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K62" t="str">
-        <v>2027-09-01</v>
+        <v>2027-08-01</v>
       </c>
       <c r="L62">
-        <v>270000</v>
+        <v>840000</v>
       </c>
       <c r="M62" t="str">
-        <v>Quạt trần PK</v>
+        <v/>
       </c>
     </row>
     <row r="63">
@@ -7821,7 +8144,7 @@
         <v>LIVING_ROOM</v>
       </c>
       <c r="D63" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E63" t="str">
         <v>NEW</v>
@@ -7833,22 +8156,22 @@
         <v>1</v>
       </c>
       <c r="H63">
-        <v>5000000</v>
+        <v>11000000</v>
       </c>
       <c r="I63">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J63" t="str">
         <v>2026-09-01</v>
       </c>
       <c r="K63" t="str">
-        <v>2027-09-01</v>
+        <v>2028-09-01</v>
       </c>
       <c r="L63">
-        <v>1500000</v>
+        <v>3300000</v>
       </c>
       <c r="M63" t="str">
-        <v>Giường PN 1</v>
+        <v>ĐH phòng khách — NT cơ bản</v>
       </c>
     </row>
     <row r="64">
@@ -7862,7 +8185,7 @@
         <v>LIVING_ROOM</v>
       </c>
       <c r="D64" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E64" t="str">
         <v>NEW</v>
@@ -7874,7 +8197,7 @@
         <v>1</v>
       </c>
       <c r="H64">
-        <v>4200000</v>
+        <v>900000</v>
       </c>
       <c r="I64">
         <v>12</v>
@@ -7886,10 +8209,10 @@
         <v>2027-09-01</v>
       </c>
       <c r="L64">
-        <v>1260000</v>
+        <v>270000</v>
       </c>
       <c r="M64" t="str">
-        <v>Giường PN 2</v>
+        <v>Quạt trần PK</v>
       </c>
     </row>
     <row r="65">
@@ -7900,10 +8223,10 @@
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>KITCHEN</v>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D65" t="str">
-        <v>Tủ lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="E65" t="str">
         <v>NEW</v>
@@ -7915,22 +8238,22 @@
         <v>1</v>
       </c>
       <c r="H65">
-        <v>7500000</v>
+        <v>5000000</v>
       </c>
       <c r="I65">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J65" t="str">
         <v>2026-09-01</v>
       </c>
       <c r="K65" t="str">
-        <v>2028-09-01</v>
+        <v>2027-09-01</v>
       </c>
       <c r="L65">
-        <v>2250000</v>
+        <v>1500000</v>
       </c>
       <c r="M65" t="str">
-        <v/>
+        <v>Giường PN 1</v>
       </c>
     </row>
     <row r="66">
@@ -7941,10 +8264,10 @@
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>BATHROOM</v>
+        <v>LIVING_ROOM</v>
       </c>
       <c r="D66" t="str">
-        <v>Nóng lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="E66" t="str">
         <v>NEW</v>
@@ -7956,7 +8279,7 @@
         <v>1</v>
       </c>
       <c r="H66">
-        <v>2800000</v>
+        <v>4200000</v>
       </c>
       <c r="I66">
         <v>12</v>
@@ -7968,24 +8291,24 @@
         <v>2027-09-01</v>
       </c>
       <c r="L66">
-        <v>840000</v>
+        <v>1260000</v>
       </c>
       <c r="M66" t="str">
-        <v/>
+        <v>Giường PN 2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
       </c>
       <c r="B67" t="str">
-        <v>101</v>
+        <v/>
       </c>
       <c r="C67" t="str">
-        <v/>
+        <v>KITCHEN</v>
       </c>
       <c r="D67" t="str">
-        <v>Giường</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="E67" t="str">
         <v>NEW</v>
@@ -7997,36 +8320,36 @@
         <v>1</v>
       </c>
       <c r="H67">
-        <v>4000000</v>
+        <v>7500000</v>
       </c>
       <c r="I67">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J67" t="str">
-        <v>2026-10-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="K67" t="str">
-        <v>2027-10-01</v>
+        <v>2028-09-01</v>
       </c>
       <c r="L67">
-        <v>1200000</v>
+        <v>2250000</v>
       </c>
       <c r="M67" t="str">
-        <v>NT cơ bản phòng 101</v>
+        <v>Tủ lạnh — NT cơ bản</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-31-RENO-WH-HO-BUY</v>
       </c>
       <c r="B68" t="str">
-        <v>101</v>
+        <v/>
       </c>
       <c r="C68" t="str">
-        <v/>
+        <v>BATHROOM</v>
       </c>
       <c r="D68" t="str">
-        <v>Quạt</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E68" t="str">
         <v>NEW</v>
@@ -8038,22 +8361,22 @@
         <v>1</v>
       </c>
       <c r="H68">
-        <v>750000</v>
+        <v>2800000</v>
       </c>
       <c r="I68">
         <v>12</v>
       </c>
       <c r="J68" t="str">
-        <v>2026-10-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="K68" t="str">
-        <v>2027-10-01</v>
+        <v>2027-09-01</v>
       </c>
       <c r="L68">
-        <v>225000</v>
+        <v>840000</v>
       </c>
       <c r="M68" t="str">
-        <v>Quạt phòng 101</v>
+        <v/>
       </c>
     </row>
     <row r="69">
@@ -8067,7 +8390,7 @@
         <v/>
       </c>
       <c r="D69" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="E69" t="str">
         <v>NEW</v>
@@ -8079,22 +8402,22 @@
         <v>1</v>
       </c>
       <c r="H69">
-        <v>8500000</v>
+        <v>4000000</v>
       </c>
       <c r="I69">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J69" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="K69" t="str">
-        <v>2028-10-01</v>
+        <v>2027-10-01</v>
       </c>
       <c r="L69">
-        <v>2550000</v>
+        <v>1200000</v>
       </c>
       <c r="M69" t="str">
-        <v>ĐH phòng 101</v>
+        <v>Giường phòng 101 — NT cơ bản</v>
       </c>
     </row>
     <row r="70">
@@ -8102,13 +8425,13 @@
         <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B70" t="str">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C70" t="str">
         <v/>
       </c>
       <c r="D70" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E70" t="str">
         <v>NEW</v>
@@ -8120,7 +8443,7 @@
         <v>1</v>
       </c>
       <c r="H70">
-        <v>4000000</v>
+        <v>750000</v>
       </c>
       <c r="I70">
         <v>12</v>
@@ -8132,10 +8455,10 @@
         <v>2027-10-01</v>
       </c>
       <c r="L70">
-        <v>1200000</v>
+        <v>225000</v>
       </c>
       <c r="M70" t="str">
-        <v>NT cơ bản phòng 102</v>
+        <v>Quạt phòng 101</v>
       </c>
     </row>
     <row r="71">
@@ -8143,13 +8466,13 @@
         <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B71" t="str">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C71" t="str">
         <v/>
       </c>
       <c r="D71" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E71" t="str">
         <v>NEW</v>
@@ -8161,22 +8484,22 @@
         <v>1</v>
       </c>
       <c r="H71">
-        <v>750000</v>
+        <v>8500000</v>
       </c>
       <c r="I71">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J71" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="K71" t="str">
-        <v>2027-10-01</v>
+        <v>2028-10-01</v>
       </c>
       <c r="L71">
-        <v>225000</v>
+        <v>2550000</v>
       </c>
       <c r="M71" t="str">
-        <v>Quạt phòng 102</v>
+        <v>ĐH phòng 101</v>
       </c>
     </row>
     <row r="72">
@@ -8184,7 +8507,7 @@
         <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B72" t="str">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C72" t="str">
         <v/>
@@ -8217,7 +8540,7 @@
         <v>1200000</v>
       </c>
       <c r="M72" t="str">
-        <v>NT cơ bản phòng 103</v>
+        <v>Giường phòng 102 — NT cơ bản</v>
       </c>
     </row>
     <row r="73">
@@ -8225,7 +8548,7 @@
         <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B73" t="str">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C73" t="str">
         <v/>
@@ -8258,7 +8581,7 @@
         <v>225000</v>
       </c>
       <c r="M73" t="str">
-        <v>Quạt phòng 103</v>
+        <v>Quạt phòng 102</v>
       </c>
     </row>
     <row r="74">
@@ -8272,7 +8595,7 @@
         <v/>
       </c>
       <c r="D74" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="E74" t="str">
         <v>NEW</v>
@@ -8284,36 +8607,36 @@
         <v>1</v>
       </c>
       <c r="H74">
-        <v>8500000</v>
+        <v>4000000</v>
       </c>
       <c r="I74">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J74" t="str">
         <v>2026-10-01</v>
       </c>
       <c r="K74" t="str">
-        <v>2028-10-01</v>
+        <v>2027-10-01</v>
       </c>
       <c r="L74">
-        <v>2550000</v>
+        <v>1200000</v>
       </c>
       <c r="M74" t="str">
-        <v>ĐH phòng 103</v>
+        <v>Giường phòng 103 — NT cơ bản</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B75" t="str">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C75" t="str">
         <v/>
       </c>
       <c r="D75" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E75" t="str">
         <v>NEW</v>
@@ -8325,36 +8648,36 @@
         <v>1</v>
       </c>
       <c r="H75">
-        <v>4000000</v>
+        <v>750000</v>
       </c>
       <c r="I75">
         <v>12</v>
       </c>
       <c r="J75" t="str">
-        <v>2026-03-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="K75" t="str">
-        <v>2027-03-01</v>
+        <v>2027-10-01</v>
       </c>
       <c r="L75">
-        <v>1200000</v>
+        <v>225000</v>
       </c>
       <c r="M75" t="str">
-        <v>NT cơ bản phòng 101</v>
+        <v>Quạt phòng 103</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B76" t="str">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C76" t="str">
         <v/>
       </c>
       <c r="D76" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E76" t="str">
         <v>NEW</v>
@@ -8366,36 +8689,36 @@
         <v>1</v>
       </c>
       <c r="H76">
-        <v>750000</v>
+        <v>8500000</v>
       </c>
       <c r="I76">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J76" t="str">
-        <v>2026-03-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="K76" t="str">
-        <v>2027-03-01</v>
+        <v>2028-10-01</v>
       </c>
       <c r="L76">
-        <v>225000</v>
+        <v>2550000</v>
       </c>
       <c r="M76" t="str">
-        <v>Quạt phòng 101</v>
+        <v>ĐH phòng 103</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-40-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B77" t="str">
-        <v>101</v>
+        <v/>
       </c>
       <c r="C77" t="str">
-        <v/>
+        <v>KITCHEN</v>
       </c>
       <c r="D77" t="str">
-        <v>Điều hòa</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="E77" t="str">
         <v>NEW</v>
@@ -8407,22 +8730,22 @@
         <v>1</v>
       </c>
       <c r="H77">
-        <v>8500000</v>
+        <v>6500000</v>
       </c>
       <c r="I77">
         <v>24</v>
       </c>
       <c r="J77" t="str">
-        <v>2026-03-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="K77" t="str">
-        <v>2028-03-01</v>
+        <v>2028-10-01</v>
       </c>
       <c r="L77">
-        <v>2550000</v>
+        <v>1950000</v>
       </c>
       <c r="M77" t="str">
-        <v>ĐH phòng 101</v>
+        <v>Tủ dùng chung — NT cơ bản</v>
       </c>
     </row>
     <row r="78">
@@ -8430,7 +8753,7 @@
         <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B78" t="str">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C78" t="str">
         <v/>
@@ -8463,7 +8786,7 @@
         <v>1200000</v>
       </c>
       <c r="M78" t="str">
-        <v>NT cơ bản phòng 102</v>
+        <v>Giường phòng 101 — NT cơ bản</v>
       </c>
     </row>
     <row r="79">
@@ -8471,7 +8794,7 @@
         <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B79" t="str">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C79" t="str">
         <v/>
@@ -8504,7 +8827,7 @@
         <v>225000</v>
       </c>
       <c r="M79" t="str">
-        <v>Quạt phòng 102</v>
+        <v>Quạt phòng 101</v>
       </c>
     </row>
     <row r="80">
@@ -8512,13 +8835,13 @@
         <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B80" t="str">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C80" t="str">
         <v/>
       </c>
       <c r="D80" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E80" t="str">
         <v>NEW</v>
@@ -8530,22 +8853,22 @@
         <v>1</v>
       </c>
       <c r="H80">
-        <v>4000000</v>
+        <v>8500000</v>
       </c>
       <c r="I80">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J80" t="str">
         <v>2026-03-01</v>
       </c>
       <c r="K80" t="str">
-        <v>2027-03-01</v>
+        <v>2028-03-01</v>
       </c>
       <c r="L80">
-        <v>1200000</v>
+        <v>2550000</v>
       </c>
       <c r="M80" t="str">
-        <v>NT cơ bản phòng 103</v>
+        <v>ĐH phòng 101</v>
       </c>
     </row>
     <row r="81">
@@ -8553,13 +8876,13 @@
         <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B81" t="str">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C81" t="str">
         <v/>
       </c>
       <c r="D81" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="E81" t="str">
         <v>NEW</v>
@@ -8571,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="H81">
-        <v>750000</v>
+        <v>4000000</v>
       </c>
       <c r="I81">
         <v>12</v>
@@ -8583,10 +8906,10 @@
         <v>2027-03-01</v>
       </c>
       <c r="L81">
-        <v>225000</v>
+        <v>1200000</v>
       </c>
       <c r="M81" t="str">
-        <v>Quạt phòng 103</v>
+        <v>Giường phòng 102 — NT cơ bản</v>
       </c>
     </row>
     <row r="82">
@@ -8594,13 +8917,13 @@
         <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B82" t="str">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C82" t="str">
         <v/>
       </c>
       <c r="D82" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="E82" t="str">
         <v>NEW</v>
@@ -8612,22 +8935,22 @@
         <v>1</v>
       </c>
       <c r="H82">
-        <v>8500000</v>
+        <v>750000</v>
       </c>
       <c r="I82">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J82" t="str">
         <v>2026-03-01</v>
       </c>
       <c r="K82" t="str">
-        <v>2028-03-01</v>
+        <v>2027-03-01</v>
       </c>
       <c r="L82">
-        <v>2550000</v>
+        <v>225000</v>
       </c>
       <c r="M82" t="str">
-        <v>ĐH phòng 103</v>
+        <v>Quạt phòng 102</v>
       </c>
     </row>
     <row r="83">
@@ -8635,7 +8958,7 @@
         <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B83" t="str">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C83" t="str">
         <v/>
@@ -8668,7 +8991,7 @@
         <v>1200000</v>
       </c>
       <c r="M83" t="str">
-        <v>NT cơ bản phòng 104</v>
+        <v>Giường phòng 103 — NT cơ bản</v>
       </c>
     </row>
     <row r="84">
@@ -8676,7 +8999,7 @@
         <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B84" t="str">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C84" t="str">
         <v/>
@@ -8709,21 +9032,21 @@
         <v>225000</v>
       </c>
       <c r="M84" t="str">
-        <v>Quạt phòng 104</v>
+        <v>Quạt phòng 103</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B85" t="str">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C85" t="str">
         <v/>
       </c>
       <c r="D85" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E85" t="str">
         <v>NEW</v>
@@ -8735,36 +9058,36 @@
         <v>1</v>
       </c>
       <c r="H85">
-        <v>4000000</v>
+        <v>8500000</v>
       </c>
       <c r="I85">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J85" t="str">
-        <v>2026-04-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="K85" t="str">
-        <v>2027-04-01</v>
+        <v>2028-03-01</v>
       </c>
       <c r="L85">
-        <v>1200000</v>
+        <v>2550000</v>
       </c>
       <c r="M85" t="str">
-        <v>NT cơ bản phòng 101</v>
+        <v>ĐH phòng 103</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B86" t="str">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C86" t="str">
         <v/>
       </c>
       <c r="D86" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="E86" t="str">
         <v>NEW</v>
@@ -8776,36 +9099,36 @@
         <v>1</v>
       </c>
       <c r="H86">
-        <v>750000</v>
+        <v>4000000</v>
       </c>
       <c r="I86">
         <v>12</v>
       </c>
       <c r="J86" t="str">
-        <v>2026-04-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="K86" t="str">
-        <v>2027-04-01</v>
+        <v>2027-03-01</v>
       </c>
       <c r="L86">
-        <v>225000</v>
+        <v>1200000</v>
       </c>
       <c r="M86" t="str">
-        <v>Quạt phòng 101</v>
+        <v>Giường phòng 104 — NT cơ bản</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B87" t="str">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C87" t="str">
         <v/>
       </c>
       <c r="D87" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="E87" t="str">
         <v>NEW</v>
@@ -8817,36 +9140,36 @@
         <v>1</v>
       </c>
       <c r="H87">
-        <v>8500000</v>
+        <v>750000</v>
       </c>
       <c r="I87">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J87" t="str">
-        <v>2026-04-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="K87" t="str">
-        <v>2028-04-01</v>
+        <v>2027-03-01</v>
       </c>
       <c r="L87">
-        <v>2550000</v>
+        <v>225000</v>
       </c>
       <c r="M87" t="str">
-        <v>ĐH phòng 101</v>
+        <v>Quạt phòng 104</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-41-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B88" t="str">
-        <v>102</v>
+        <v/>
       </c>
       <c r="C88" t="str">
-        <v/>
+        <v>KITCHEN</v>
       </c>
       <c r="D88" t="str">
-        <v>Giường</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="E88" t="str">
         <v>NEW</v>
@@ -8858,22 +9181,22 @@
         <v>1</v>
       </c>
       <c r="H88">
-        <v>4000000</v>
+        <v>6500000</v>
       </c>
       <c r="I88">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J88" t="str">
-        <v>2026-04-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="K88" t="str">
-        <v>2027-04-01</v>
+        <v>2028-03-01</v>
       </c>
       <c r="L88">
-        <v>1200000</v>
+        <v>1950000</v>
       </c>
       <c r="M88" t="str">
-        <v>NT cơ bản phòng 102</v>
+        <v>Tủ dùng chung — NT cơ bản</v>
       </c>
     </row>
     <row r="89">
@@ -8881,13 +9204,13 @@
         <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B89" t="str">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C89" t="str">
         <v/>
       </c>
       <c r="D89" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="E89" t="str">
         <v>NEW</v>
@@ -8899,7 +9222,7 @@
         <v>1</v>
       </c>
       <c r="H89">
-        <v>750000</v>
+        <v>4000000</v>
       </c>
       <c r="I89">
         <v>12</v>
@@ -8911,10 +9234,10 @@
         <v>2027-04-01</v>
       </c>
       <c r="L89">
-        <v>225000</v>
+        <v>1200000</v>
       </c>
       <c r="M89" t="str">
-        <v>Quạt phòng 102</v>
+        <v>Giường phòng 101 — NT cơ bản</v>
       </c>
     </row>
     <row r="90">
@@ -8922,13 +9245,13 @@
         <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B90" t="str">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C90" t="str">
         <v/>
       </c>
       <c r="D90" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E90" t="str">
         <v>NEW</v>
@@ -8940,7 +9263,7 @@
         <v>1</v>
       </c>
       <c r="H90">
-        <v>4000000</v>
+        <v>750000</v>
       </c>
       <c r="I90">
         <v>12</v>
@@ -8952,10 +9275,10 @@
         <v>2027-04-01</v>
       </c>
       <c r="L90">
-        <v>1200000</v>
+        <v>225000</v>
       </c>
       <c r="M90" t="str">
-        <v>NT cơ bản phòng 103</v>
+        <v>Quạt phòng 101</v>
       </c>
     </row>
     <row r="91">
@@ -8963,13 +9286,13 @@
         <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B91" t="str">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C91" t="str">
         <v/>
       </c>
       <c r="D91" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E91" t="str">
         <v>NEW</v>
@@ -8981,22 +9304,22 @@
         <v>1</v>
       </c>
       <c r="H91">
-        <v>750000</v>
+        <v>8500000</v>
       </c>
       <c r="I91">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J91" t="str">
         <v>2026-04-01</v>
       </c>
       <c r="K91" t="str">
-        <v>2027-04-01</v>
+        <v>2028-04-01</v>
       </c>
       <c r="L91">
-        <v>225000</v>
+        <v>2550000</v>
       </c>
       <c r="M91" t="str">
-        <v>Quạt phòng 103</v>
+        <v>ĐH phòng 101</v>
       </c>
     </row>
     <row r="92">
@@ -9004,13 +9327,13 @@
         <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B92" t="str">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C92" t="str">
         <v/>
       </c>
       <c r="D92" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="E92" t="str">
         <v>NEW</v>
@@ -9022,36 +9345,36 @@
         <v>1</v>
       </c>
       <c r="H92">
-        <v>8500000</v>
+        <v>4000000</v>
       </c>
       <c r="I92">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J92" t="str">
         <v>2026-04-01</v>
       </c>
       <c r="K92" t="str">
-        <v>2028-04-01</v>
+        <v>2027-04-01</v>
       </c>
       <c r="L92">
-        <v>2550000</v>
+        <v>1200000</v>
       </c>
       <c r="M92" t="str">
-        <v>ĐH phòng 103</v>
+        <v>Giường phòng 102 — NT cơ bản</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B93" t="str">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C93" t="str">
         <v/>
       </c>
       <c r="D93" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E93" t="str">
         <v>NEW</v>
@@ -9063,36 +9386,36 @@
         <v>1</v>
       </c>
       <c r="H93">
-        <v>4000000</v>
+        <v>750000</v>
       </c>
       <c r="I93">
         <v>12</v>
       </c>
       <c r="J93" t="str">
-        <v>2026-05-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K93" t="str">
-        <v>2027-05-01</v>
+        <v>2027-04-01</v>
       </c>
       <c r="L93">
-        <v>1200000</v>
+        <v>225000</v>
       </c>
       <c r="M93" t="str">
-        <v>NT cơ bản phòng 101</v>
+        <v>Quạt phòng 102</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B94" t="str">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C94" t="str">
         <v/>
       </c>
       <c r="D94" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="E94" t="str">
         <v>NEW</v>
@@ -9104,36 +9427,36 @@
         <v>1</v>
       </c>
       <c r="H94">
-        <v>750000</v>
+        <v>4000000</v>
       </c>
       <c r="I94">
         <v>12</v>
       </c>
       <c r="J94" t="str">
-        <v>2026-05-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K94" t="str">
-        <v>2027-05-01</v>
+        <v>2027-04-01</v>
       </c>
       <c r="L94">
-        <v>225000</v>
+        <v>1200000</v>
       </c>
       <c r="M94" t="str">
-        <v>Quạt phòng 101</v>
+        <v>Giường phòng 103 — NT cơ bản</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B95" t="str">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C95" t="str">
         <v/>
       </c>
       <c r="D95" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="E95" t="str">
         <v>NEW</v>
@@ -9145,36 +9468,36 @@
         <v>1</v>
       </c>
       <c r="H95">
-        <v>8500000</v>
+        <v>750000</v>
       </c>
       <c r="I95">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J95" t="str">
-        <v>2026-05-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K95" t="str">
-        <v>2028-05-01</v>
+        <v>2027-04-01</v>
       </c>
       <c r="L95">
-        <v>2550000</v>
+        <v>225000</v>
       </c>
       <c r="M95" t="str">
-        <v>ĐH phòng 101</v>
+        <v>Quạt phòng 103</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B96" t="str">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C96" t="str">
         <v/>
       </c>
       <c r="D96" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E96" t="str">
         <v>NEW</v>
@@ -9186,36 +9509,36 @@
         <v>1</v>
       </c>
       <c r="H96">
-        <v>4000000</v>
+        <v>8500000</v>
       </c>
       <c r="I96">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J96" t="str">
-        <v>2026-05-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K96" t="str">
-        <v>2027-05-01</v>
+        <v>2028-04-01</v>
       </c>
       <c r="L96">
-        <v>1200000</v>
+        <v>2550000</v>
       </c>
       <c r="M96" t="str">
-        <v>NT cơ bản phòng 102</v>
+        <v>ĐH phòng 103</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
+        <v>HD-MTX-42-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B97" t="str">
-        <v>102</v>
+        <v/>
       </c>
       <c r="C97" t="str">
-        <v/>
+        <v>KITCHEN</v>
       </c>
       <c r="D97" t="str">
-        <v>Quạt</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="E97" t="str">
         <v>NEW</v>
@@ -9227,22 +9550,22 @@
         <v>1</v>
       </c>
       <c r="H97">
-        <v>750000</v>
+        <v>6500000</v>
       </c>
       <c r="I97">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J97" t="str">
-        <v>2026-05-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="K97" t="str">
-        <v>2027-05-01</v>
+        <v>2028-04-01</v>
       </c>
       <c r="L97">
-        <v>225000</v>
+        <v>1950000</v>
       </c>
       <c r="M97" t="str">
-        <v>Quạt phòng 102</v>
+        <v>Tủ dùng chung — NT cơ bản</v>
       </c>
     </row>
     <row r="98">
@@ -9250,7 +9573,7 @@
         <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B98" t="str">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C98" t="str">
         <v/>
@@ -9283,7 +9606,7 @@
         <v>1200000</v>
       </c>
       <c r="M98" t="str">
-        <v>NT cơ bản phòng 103</v>
+        <v>Giường phòng 101 — NT cơ bản</v>
       </c>
     </row>
     <row r="99">
@@ -9291,7 +9614,7 @@
         <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B99" t="str">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C99" t="str">
         <v/>
@@ -9324,7 +9647,7 @@
         <v>225000</v>
       </c>
       <c r="M99" t="str">
-        <v>Quạt phòng 103</v>
+        <v>Quạt phòng 101</v>
       </c>
     </row>
     <row r="100">
@@ -9332,7 +9655,7 @@
         <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B100" t="str">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C100" t="str">
         <v/>
@@ -9365,7 +9688,7 @@
         <v>2550000</v>
       </c>
       <c r="M100" t="str">
-        <v>ĐH phòng 103</v>
+        <v>ĐH phòng 101</v>
       </c>
     </row>
     <row r="101">
@@ -9373,7 +9696,7 @@
         <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B101" t="str">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C101" t="str">
         <v/>
@@ -9406,7 +9729,7 @@
         <v>1200000</v>
       </c>
       <c r="M101" t="str">
-        <v>NT cơ bản phòng 104</v>
+        <v>Giường phòng 102 — NT cơ bản</v>
       </c>
     </row>
     <row r="102">
@@ -9414,7 +9737,7 @@
         <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B102" t="str">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C102" t="str">
         <v/>
@@ -9447,15 +9770,15 @@
         <v>225000</v>
       </c>
       <c r="M102" t="str">
-        <v>Quạt phòng 104</v>
+        <v>Quạt phòng 102</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
+        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B103" t="str">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C103" t="str">
         <v/>
@@ -9473,30 +9796,30 @@
         <v>1</v>
       </c>
       <c r="H103">
-        <v>4500000</v>
+        <v>4000000</v>
       </c>
       <c r="I103">
         <v>12</v>
       </c>
       <c r="J103" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="K103" t="str">
-        <v>2027-06-01</v>
+        <v>2027-05-01</v>
       </c>
       <c r="L103">
-        <v>1350000</v>
+        <v>1200000</v>
       </c>
       <c r="M103" t="str">
-        <v>Giường phòng 101</v>
+        <v>Giường phòng 103 — NT cơ bản</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
+        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B104" t="str">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C104" t="str">
         <v/>
@@ -9514,30 +9837,30 @@
         <v>1</v>
       </c>
       <c r="H104">
-        <v>800000</v>
+        <v>750000</v>
       </c>
       <c r="I104">
         <v>12</v>
       </c>
       <c r="J104" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="K104" t="str">
-        <v>2027-06-01</v>
+        <v>2027-05-01</v>
       </c>
       <c r="L104">
-        <v>240000</v>
+        <v>225000</v>
       </c>
       <c r="M104" t="str">
-        <v>Quạt phòng 101</v>
+        <v>Quạt phòng 103</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
+        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B105" t="str">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C105" t="str">
         <v/>
@@ -9555,36 +9878,36 @@
         <v>1</v>
       </c>
       <c r="H105">
-        <v>9200000</v>
+        <v>8500000</v>
       </c>
       <c r="I105">
         <v>24</v>
       </c>
       <c r="J105" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="K105" t="str">
-        <v>2028-06-01</v>
+        <v>2028-05-01</v>
       </c>
       <c r="L105">
-        <v>2760000</v>
+        <v>2550000</v>
       </c>
       <c r="M105" t="str">
-        <v>ĐH phòng 101</v>
+        <v>ĐH phòng 103</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
+        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B106" t="str">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C106" t="str">
         <v/>
       </c>
       <c r="D106" t="str">
-        <v>Nóng lạnh</v>
+        <v>Giường</v>
       </c>
       <c r="E106" t="str">
         <v>NEW</v>
@@ -9596,36 +9919,36 @@
         <v>1</v>
       </c>
       <c r="H106">
-        <v>2600000</v>
+        <v>4000000</v>
       </c>
       <c r="I106">
         <v>12</v>
       </c>
       <c r="J106" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="K106" t="str">
-        <v>2027-06-01</v>
+        <v>2027-05-01</v>
       </c>
       <c r="L106">
-        <v>780000</v>
+        <v>1200000</v>
       </c>
       <c r="M106" t="str">
-        <v>NL phòng 101</v>
+        <v>Giường phòng 104 — NT cơ bản</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
+        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B107" t="str">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C107" t="str">
         <v/>
       </c>
       <c r="D107" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E107" t="str">
         <v>NEW</v>
@@ -9637,36 +9960,36 @@
         <v>1</v>
       </c>
       <c r="H107">
-        <v>4500000</v>
+        <v>750000</v>
       </c>
       <c r="I107">
         <v>12</v>
       </c>
       <c r="J107" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="K107" t="str">
-        <v>2027-06-01</v>
+        <v>2027-05-01</v>
       </c>
       <c r="L107">
-        <v>1350000</v>
+        <v>225000</v>
       </c>
       <c r="M107" t="str">
-        <v>Giường phòng 102</v>
+        <v>Quạt phòng 104</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>HD-MTX-44-RENO-RM-FULL</v>
+        <v>HD-MTX-43-RENO-RM-BASIC-BUY</v>
       </c>
       <c r="B108" t="str">
-        <v>102</v>
+        <v/>
       </c>
       <c r="C108" t="str">
-        <v/>
+        <v>KITCHEN</v>
       </c>
       <c r="D108" t="str">
-        <v>Quạt</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="E108" t="str">
         <v>NEW</v>
@@ -9678,22 +10001,22 @@
         <v>1</v>
       </c>
       <c r="H108">
-        <v>800000</v>
+        <v>6500000</v>
       </c>
       <c r="I108">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J108" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-01</v>
       </c>
       <c r="K108" t="str">
-        <v>2027-06-01</v>
+        <v>2028-05-01</v>
       </c>
       <c r="L108">
-        <v>240000</v>
+        <v>1950000</v>
       </c>
       <c r="M108" t="str">
-        <v>Quạt phòng 102</v>
+        <v>Tủ dùng chung — NT cơ bản</v>
       </c>
     </row>
     <row r="109">
@@ -9701,13 +10024,13 @@
         <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B109" t="str">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C109" t="str">
         <v/>
       </c>
       <c r="D109" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="E109" t="str">
         <v>NEW</v>
@@ -9719,22 +10042,22 @@
         <v>1</v>
       </c>
       <c r="H109">
-        <v>9200000</v>
+        <v>4500000</v>
       </c>
       <c r="I109">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J109" t="str">
         <v>2026-06-01</v>
       </c>
       <c r="K109" t="str">
-        <v>2028-06-01</v>
+        <v>2027-06-01</v>
       </c>
       <c r="L109">
-        <v>2760000</v>
+        <v>1350000</v>
       </c>
       <c r="M109" t="str">
-        <v>ĐH phòng 102</v>
+        <v>Giường phòng 101</v>
       </c>
     </row>
     <row r="110">
@@ -9742,13 +10065,13 @@
         <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B110" t="str">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C110" t="str">
         <v/>
       </c>
       <c r="D110" t="str">
-        <v>Nóng lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="E110" t="str">
         <v>NEW</v>
@@ -9760,7 +10083,7 @@
         <v>1</v>
       </c>
       <c r="H110">
-        <v>2600000</v>
+        <v>800000</v>
       </c>
       <c r="I110">
         <v>12</v>
@@ -9772,10 +10095,10 @@
         <v>2027-06-01</v>
       </c>
       <c r="L110">
-        <v>780000</v>
+        <v>240000</v>
       </c>
       <c r="M110" t="str">
-        <v>NL phòng 102</v>
+        <v>Quạt phòng 101</v>
       </c>
     </row>
     <row r="111">
@@ -9783,13 +10106,13 @@
         <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B111" t="str">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C111" t="str">
         <v/>
       </c>
       <c r="D111" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E111" t="str">
         <v>NEW</v>
@@ -9801,22 +10124,22 @@
         <v>1</v>
       </c>
       <c r="H111">
-        <v>4500000</v>
+        <v>9200000</v>
       </c>
       <c r="I111">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J111" t="str">
         <v>2026-06-01</v>
       </c>
       <c r="K111" t="str">
-        <v>2027-06-01</v>
+        <v>2028-06-01</v>
       </c>
       <c r="L111">
-        <v>1350000</v>
+        <v>2760000</v>
       </c>
       <c r="M111" t="str">
-        <v>Giường phòng 103</v>
+        <v>ĐH phòng 101</v>
       </c>
     </row>
     <row r="112">
@@ -9824,13 +10147,13 @@
         <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B112" t="str">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C112" t="str">
         <v/>
       </c>
       <c r="D112" t="str">
-        <v>Quạt</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E112" t="str">
         <v>NEW</v>
@@ -9842,7 +10165,7 @@
         <v>1</v>
       </c>
       <c r="H112">
-        <v>800000</v>
+        <v>2600000</v>
       </c>
       <c r="I112">
         <v>12</v>
@@ -9854,10 +10177,10 @@
         <v>2027-06-01</v>
       </c>
       <c r="L112">
-        <v>240000</v>
+        <v>780000</v>
       </c>
       <c r="M112" t="str">
-        <v>Quạt phòng 103</v>
+        <v>NL phòng 101</v>
       </c>
     </row>
     <row r="113">
@@ -9865,13 +10188,13 @@
         <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B113" t="str">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C113" t="str">
         <v/>
       </c>
       <c r="D113" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="E113" t="str">
         <v>NEW</v>
@@ -9883,22 +10206,22 @@
         <v>1</v>
       </c>
       <c r="H113">
-        <v>9200000</v>
+        <v>4500000</v>
       </c>
       <c r="I113">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J113" t="str">
         <v>2026-06-01</v>
       </c>
       <c r="K113" t="str">
-        <v>2028-06-01</v>
+        <v>2027-06-01</v>
       </c>
       <c r="L113">
-        <v>2760000</v>
+        <v>1350000</v>
       </c>
       <c r="M113" t="str">
-        <v>ĐH phòng 103</v>
+        <v>Giường phòng 102</v>
       </c>
     </row>
     <row r="114">
@@ -9906,13 +10229,13 @@
         <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B114" t="str">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C114" t="str">
         <v/>
       </c>
       <c r="D114" t="str">
-        <v>Nóng lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="E114" t="str">
         <v>NEW</v>
@@ -9924,7 +10247,7 @@
         <v>1</v>
       </c>
       <c r="H114">
-        <v>2600000</v>
+        <v>800000</v>
       </c>
       <c r="I114">
         <v>12</v>
@@ -9936,10 +10259,10 @@
         <v>2027-06-01</v>
       </c>
       <c r="L114">
-        <v>780000</v>
+        <v>240000</v>
       </c>
       <c r="M114" t="str">
-        <v>NL phòng 103</v>
+        <v>Quạt phòng 102</v>
       </c>
     </row>
     <row r="115">
@@ -9947,13 +10270,13 @@
         <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B115" t="str">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C115" t="str">
         <v/>
       </c>
       <c r="D115" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E115" t="str">
         <v>NEW</v>
@@ -9965,22 +10288,22 @@
         <v>1</v>
       </c>
       <c r="H115">
-        <v>4500000</v>
+        <v>9200000</v>
       </c>
       <c r="I115">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J115" t="str">
         <v>2026-06-01</v>
       </c>
       <c r="K115" t="str">
-        <v>2027-06-01</v>
+        <v>2028-06-01</v>
       </c>
       <c r="L115">
-        <v>1350000</v>
+        <v>2760000</v>
       </c>
       <c r="M115" t="str">
-        <v>Giường phòng 104</v>
+        <v>ĐH phòng 102</v>
       </c>
     </row>
     <row r="116">
@@ -9988,13 +10311,13 @@
         <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B116" t="str">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C116" t="str">
         <v/>
       </c>
       <c r="D116" t="str">
-        <v>Quạt</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E116" t="str">
         <v>NEW</v>
@@ -10006,7 +10329,7 @@
         <v>1</v>
       </c>
       <c r="H116">
-        <v>800000</v>
+        <v>2600000</v>
       </c>
       <c r="I116">
         <v>12</v>
@@ -10018,10 +10341,10 @@
         <v>2027-06-01</v>
       </c>
       <c r="L116">
-        <v>240000</v>
+        <v>780000</v>
       </c>
       <c r="M116" t="str">
-        <v>Quạt phòng 104</v>
+        <v>NL phòng 102</v>
       </c>
     </row>
     <row r="117">
@@ -10029,13 +10352,13 @@
         <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B117" t="str">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C117" t="str">
         <v/>
       </c>
       <c r="D117" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="E117" t="str">
         <v>NEW</v>
@@ -10047,22 +10370,22 @@
         <v>1</v>
       </c>
       <c r="H117">
-        <v>9200000</v>
+        <v>4500000</v>
       </c>
       <c r="I117">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J117" t="str">
         <v>2026-06-01</v>
       </c>
       <c r="K117" t="str">
-        <v>2028-06-01</v>
+        <v>2027-06-01</v>
       </c>
       <c r="L117">
-        <v>2760000</v>
+        <v>1350000</v>
       </c>
       <c r="M117" t="str">
-        <v>ĐH phòng 104</v>
+        <v>Giường phòng 103</v>
       </c>
     </row>
     <row r="118">
@@ -10070,13 +10393,13 @@
         <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B118" t="str">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C118" t="str">
         <v/>
       </c>
       <c r="D118" t="str">
-        <v>Nóng lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="E118" t="str">
         <v>NEW</v>
@@ -10088,7 +10411,7 @@
         <v>1</v>
       </c>
       <c r="H118">
-        <v>2600000</v>
+        <v>800000</v>
       </c>
       <c r="I118">
         <v>12</v>
@@ -10100,24 +10423,24 @@
         <v>2027-06-01</v>
       </c>
       <c r="L118">
-        <v>780000</v>
+        <v>240000</v>
       </c>
       <c r="M118" t="str">
-        <v>NL phòng 104</v>
+        <v>Quạt phòng 103</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B119" t="str">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C119" t="str">
         <v/>
       </c>
       <c r="D119" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E119" t="str">
         <v>NEW</v>
@@ -10129,36 +10452,36 @@
         <v>1</v>
       </c>
       <c r="H119">
-        <v>4500000</v>
+        <v>9200000</v>
       </c>
       <c r="I119">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J119" t="str">
-        <v>2026-07-01</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K119" t="str">
-        <v>2027-07-01</v>
+        <v>2028-06-01</v>
       </c>
       <c r="L119">
-        <v>1350000</v>
+        <v>2760000</v>
       </c>
       <c r="M119" t="str">
-        <v>Giường phòng 101</v>
+        <v>ĐH phòng 103</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B120" t="str">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C120" t="str">
         <v/>
       </c>
       <c r="D120" t="str">
-        <v>Quạt</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E120" t="str">
         <v>NEW</v>
@@ -10170,36 +10493,36 @@
         <v>1</v>
       </c>
       <c r="H120">
-        <v>800000</v>
+        <v>2600000</v>
       </c>
       <c r="I120">
         <v>12</v>
       </c>
       <c r="J120" t="str">
-        <v>2026-07-01</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K120" t="str">
-        <v>2027-07-01</v>
+        <v>2027-06-01</v>
       </c>
       <c r="L120">
-        <v>240000</v>
+        <v>780000</v>
       </c>
       <c r="M120" t="str">
-        <v>Quạt phòng 101</v>
+        <v>NL phòng 103</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B121" t="str">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C121" t="str">
         <v/>
       </c>
       <c r="D121" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="E121" t="str">
         <v>NEW</v>
@@ -10211,36 +10534,36 @@
         <v>1</v>
       </c>
       <c r="H121">
-        <v>9200000</v>
+        <v>4500000</v>
       </c>
       <c r="I121">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J121" t="str">
-        <v>2026-07-01</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K121" t="str">
-        <v>2028-07-01</v>
+        <v>2027-06-01</v>
       </c>
       <c r="L121">
-        <v>2760000</v>
+        <v>1350000</v>
       </c>
       <c r="M121" t="str">
-        <v>ĐH phòng 101</v>
+        <v>Giường phòng 104</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B122" t="str">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C122" t="str">
         <v/>
       </c>
       <c r="D122" t="str">
-        <v>Nóng lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="E122" t="str">
         <v>NEW</v>
@@ -10252,36 +10575,36 @@
         <v>1</v>
       </c>
       <c r="H122">
-        <v>2600000</v>
+        <v>800000</v>
       </c>
       <c r="I122">
         <v>12</v>
       </c>
       <c r="J122" t="str">
-        <v>2026-07-01</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K122" t="str">
-        <v>2027-07-01</v>
+        <v>2027-06-01</v>
       </c>
       <c r="L122">
-        <v>780000</v>
+        <v>240000</v>
       </c>
       <c r="M122" t="str">
-        <v>NL phòng 101</v>
+        <v>Quạt phòng 104</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B123" t="str">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C123" t="str">
         <v/>
       </c>
       <c r="D123" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E123" t="str">
         <v>NEW</v>
@@ -10293,36 +10616,36 @@
         <v>1</v>
       </c>
       <c r="H123">
-        <v>4500000</v>
+        <v>9200000</v>
       </c>
       <c r="I123">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J123" t="str">
-        <v>2026-07-01</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K123" t="str">
-        <v>2027-07-01</v>
+        <v>2028-06-01</v>
       </c>
       <c r="L123">
-        <v>1350000</v>
+        <v>2760000</v>
       </c>
       <c r="M123" t="str">
-        <v>Giường phòng 102</v>
+        <v>ĐH phòng 104</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B124" t="str">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C124" t="str">
         <v/>
       </c>
       <c r="D124" t="str">
-        <v>Quạt</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E124" t="str">
         <v>NEW</v>
@@ -10334,36 +10657,36 @@
         <v>1</v>
       </c>
       <c r="H124">
-        <v>800000</v>
+        <v>2600000</v>
       </c>
       <c r="I124">
         <v>12</v>
       </c>
       <c r="J124" t="str">
-        <v>2026-07-01</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K124" t="str">
-        <v>2027-07-01</v>
+        <v>2027-06-01</v>
       </c>
       <c r="L124">
-        <v>240000</v>
+        <v>780000</v>
       </c>
       <c r="M124" t="str">
-        <v>Quạt phòng 102</v>
+        <v>NL phòng 104</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B125" t="str">
-        <v>102</v>
+        <v/>
       </c>
       <c r="C125" t="str">
-        <v/>
+        <v>KITCHEN</v>
       </c>
       <c r="D125" t="str">
-        <v>Điều hòa</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="E125" t="str">
         <v>NEW</v>
@@ -10375,36 +10698,36 @@
         <v>1</v>
       </c>
       <c r="H125">
-        <v>9200000</v>
+        <v>8000000</v>
       </c>
       <c r="I125">
         <v>24</v>
       </c>
       <c r="J125" t="str">
-        <v>2026-07-01</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K125" t="str">
-        <v>2028-07-01</v>
+        <v>2028-06-01</v>
       </c>
       <c r="L125">
-        <v>2760000</v>
+        <v>2400000</v>
       </c>
       <c r="M125" t="str">
-        <v>ĐH phòng 102</v>
+        <v>Tủ dùng chung — full NT</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>HD-MTX-45-RENO-RM-FULL</v>
+        <v>HD-MTX-44-RENO-RM-FULL</v>
       </c>
       <c r="B126" t="str">
-        <v>102</v>
+        <v/>
       </c>
       <c r="C126" t="str">
-        <v/>
+        <v>BALCONY</v>
       </c>
       <c r="D126" t="str">
-        <v>Nóng lạnh</v>
+        <v>Máy giặt</v>
       </c>
       <c r="E126" t="str">
         <v>NEW</v>
@@ -10416,22 +10739,22 @@
         <v>1</v>
       </c>
       <c r="H126">
-        <v>2600000</v>
+        <v>9000000</v>
       </c>
       <c r="I126">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J126" t="str">
-        <v>2026-07-01</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K126" t="str">
-        <v>2027-07-01</v>
+        <v>2028-06-01</v>
       </c>
       <c r="L126">
-        <v>780000</v>
+        <v>2700000</v>
       </c>
       <c r="M126" t="str">
-        <v>NL phòng 102</v>
+        <v>Máy giặt dùng chung — full NT</v>
       </c>
     </row>
     <row r="127">
@@ -10439,7 +10762,7 @@
         <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B127" t="str">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C127" t="str">
         <v/>
@@ -10472,7 +10795,7 @@
         <v>1350000</v>
       </c>
       <c r="M127" t="str">
-        <v>Giường phòng 103</v>
+        <v>Giường phòng 101</v>
       </c>
     </row>
     <row r="128">
@@ -10480,7 +10803,7 @@
         <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B128" t="str">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C128" t="str">
         <v/>
@@ -10513,7 +10836,7 @@
         <v>240000</v>
       </c>
       <c r="M128" t="str">
-        <v>Quạt phòng 103</v>
+        <v>Quạt phòng 101</v>
       </c>
     </row>
     <row r="129">
@@ -10521,7 +10844,7 @@
         <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B129" t="str">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C129" t="str">
         <v/>
@@ -10554,7 +10877,7 @@
         <v>2760000</v>
       </c>
       <c r="M129" t="str">
-        <v>ĐH phòng 103</v>
+        <v>ĐH phòng 101</v>
       </c>
     </row>
     <row r="130">
@@ -10562,7 +10885,7 @@
         <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B130" t="str">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C130" t="str">
         <v/>
@@ -10595,7 +10918,7 @@
         <v>780000</v>
       </c>
       <c r="M130" t="str">
-        <v>NL phòng 103</v>
+        <v>NL phòng 101</v>
       </c>
     </row>
     <row r="131">
@@ -10603,7 +10926,7 @@
         <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B131" t="str">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C131" t="str">
         <v/>
@@ -10636,7 +10959,7 @@
         <v>1350000</v>
       </c>
       <c r="M131" t="str">
-        <v>Giường phòng 104</v>
+        <v>Giường phòng 102</v>
       </c>
     </row>
     <row r="132">
@@ -10644,7 +10967,7 @@
         <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B132" t="str">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C132" t="str">
         <v/>
@@ -10677,7 +11000,7 @@
         <v>240000</v>
       </c>
       <c r="M132" t="str">
-        <v>Quạt phòng 104</v>
+        <v>Quạt phòng 102</v>
       </c>
     </row>
     <row r="133">
@@ -10685,7 +11008,7 @@
         <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B133" t="str">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C133" t="str">
         <v/>
@@ -10718,7 +11041,7 @@
         <v>2760000</v>
       </c>
       <c r="M133" t="str">
-        <v>ĐH phòng 104</v>
+        <v>ĐH phòng 102</v>
       </c>
     </row>
     <row r="134">
@@ -10726,7 +11049,7 @@
         <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B134" t="str">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C134" t="str">
         <v/>
@@ -10759,15 +11082,15 @@
         <v>780000</v>
       </c>
       <c r="M134" t="str">
-        <v>NL phòng 104</v>
+        <v>NL phòng 102</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B135" t="str">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C135" t="str">
         <v/>
@@ -10791,24 +11114,24 @@
         <v>12</v>
       </c>
       <c r="J135" t="str">
-        <v>2026-08-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="K135" t="str">
-        <v>2027-08-01</v>
+        <v>2027-07-01</v>
       </c>
       <c r="L135">
         <v>1350000</v>
       </c>
       <c r="M135" t="str">
-        <v>Giường phòng 101</v>
+        <v>Giường phòng 103</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B136" t="str">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C136" t="str">
         <v/>
@@ -10832,24 +11155,24 @@
         <v>12</v>
       </c>
       <c r="J136" t="str">
-        <v>2026-08-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="K136" t="str">
-        <v>2027-08-01</v>
+        <v>2027-07-01</v>
       </c>
       <c r="L136">
         <v>240000</v>
       </c>
       <c r="M136" t="str">
-        <v>Quạt phòng 101</v>
+        <v>Quạt phòng 103</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B137" t="str">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C137" t="str">
         <v/>
@@ -10873,24 +11196,24 @@
         <v>24</v>
       </c>
       <c r="J137" t="str">
-        <v>2026-08-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="K137" t="str">
-        <v>2028-08-01</v>
+        <v>2028-07-01</v>
       </c>
       <c r="L137">
         <v>2760000</v>
       </c>
       <c r="M137" t="str">
-        <v>ĐH phòng 101</v>
+        <v>ĐH phòng 103</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B138" t="str">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C138" t="str">
         <v/>
@@ -10914,24 +11237,24 @@
         <v>12</v>
       </c>
       <c r="J138" t="str">
-        <v>2026-08-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="K138" t="str">
-        <v>2027-08-01</v>
+        <v>2027-07-01</v>
       </c>
       <c r="L138">
         <v>780000</v>
       </c>
       <c r="M138" t="str">
-        <v>NL phòng 101</v>
+        <v>NL phòng 103</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B139" t="str">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C139" t="str">
         <v/>
@@ -10955,24 +11278,24 @@
         <v>12</v>
       </c>
       <c r="J139" t="str">
-        <v>2026-08-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="K139" t="str">
-        <v>2027-08-01</v>
+        <v>2027-07-01</v>
       </c>
       <c r="L139">
         <v>1350000</v>
       </c>
       <c r="M139" t="str">
-        <v>Giường phòng 102</v>
+        <v>Giường phòng 104</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B140" t="str">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C140" t="str">
         <v/>
@@ -10996,24 +11319,24 @@
         <v>12</v>
       </c>
       <c r="J140" t="str">
-        <v>2026-08-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="K140" t="str">
-        <v>2027-08-01</v>
+        <v>2027-07-01</v>
       </c>
       <c r="L140">
         <v>240000</v>
       </c>
       <c r="M140" t="str">
-        <v>Quạt phòng 102</v>
+        <v>Quạt phòng 104</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B141" t="str">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C141" t="str">
         <v/>
@@ -11037,24 +11360,24 @@
         <v>24</v>
       </c>
       <c r="J141" t="str">
-        <v>2026-08-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="K141" t="str">
-        <v>2028-08-01</v>
+        <v>2028-07-01</v>
       </c>
       <c r="L141">
         <v>2760000</v>
       </c>
       <c r="M141" t="str">
-        <v>ĐH phòng 102</v>
+        <v>ĐH phòng 104</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B142" t="str">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C142" t="str">
         <v/>
@@ -11078,30 +11401,30 @@
         <v>12</v>
       </c>
       <c r="J142" t="str">
-        <v>2026-08-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="K142" t="str">
-        <v>2027-08-01</v>
+        <v>2027-07-01</v>
       </c>
       <c r="L142">
         <v>780000</v>
       </c>
       <c r="M142" t="str">
-        <v>NL phòng 102</v>
+        <v>NL phòng 104</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B143" t="str">
-        <v>103</v>
+        <v/>
       </c>
       <c r="C143" t="str">
-        <v/>
+        <v>KITCHEN</v>
       </c>
       <c r="D143" t="str">
-        <v>Giường</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="E143" t="str">
         <v>NEW</v>
@@ -11113,36 +11436,36 @@
         <v>1</v>
       </c>
       <c r="H143">
-        <v>4500000</v>
+        <v>8000000</v>
       </c>
       <c r="I143">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J143" t="str">
-        <v>2026-08-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="K143" t="str">
-        <v>2027-08-01</v>
+        <v>2028-07-01</v>
       </c>
       <c r="L143">
-        <v>1350000</v>
+        <v>2400000</v>
       </c>
       <c r="M143" t="str">
-        <v>Giường phòng 103</v>
+        <v>Tủ dùng chung — full NT</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>HD-MTX-46-RENO-RM-FULL</v>
+        <v>HD-MTX-45-RENO-RM-FULL</v>
       </c>
       <c r="B144" t="str">
-        <v>103</v>
+        <v/>
       </c>
       <c r="C144" t="str">
-        <v/>
+        <v>BALCONY</v>
       </c>
       <c r="D144" t="str">
-        <v>Quạt</v>
+        <v>Máy giặt</v>
       </c>
       <c r="E144" t="str">
         <v>NEW</v>
@@ -11154,22 +11477,22 @@
         <v>1</v>
       </c>
       <c r="H144">
-        <v>800000</v>
+        <v>9000000</v>
       </c>
       <c r="I144">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J144" t="str">
-        <v>2026-08-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="K144" t="str">
-        <v>2027-08-01</v>
+        <v>2028-07-01</v>
       </c>
       <c r="L144">
-        <v>240000</v>
+        <v>2700000</v>
       </c>
       <c r="M144" t="str">
-        <v>Quạt phòng 103</v>
+        <v>Máy giặt dùng chung — full NT</v>
       </c>
     </row>
     <row r="145">
@@ -11177,13 +11500,13 @@
         <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B145" t="str">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C145" t="str">
         <v/>
       </c>
       <c r="D145" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="E145" t="str">
         <v>NEW</v>
@@ -11195,22 +11518,22 @@
         <v>1</v>
       </c>
       <c r="H145">
-        <v>9200000</v>
+        <v>4500000</v>
       </c>
       <c r="I145">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J145" t="str">
         <v>2026-08-01</v>
       </c>
       <c r="K145" t="str">
-        <v>2028-08-01</v>
+        <v>2027-08-01</v>
       </c>
       <c r="L145">
-        <v>2760000</v>
+        <v>1350000</v>
       </c>
       <c r="M145" t="str">
-        <v>ĐH phòng 103</v>
+        <v>Giường phòng 101</v>
       </c>
     </row>
     <row r="146">
@@ -11218,13 +11541,13 @@
         <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B146" t="str">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C146" t="str">
         <v/>
       </c>
       <c r="D146" t="str">
-        <v>Nóng lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="E146" t="str">
         <v>NEW</v>
@@ -11236,7 +11559,7 @@
         <v>1</v>
       </c>
       <c r="H146">
-        <v>2600000</v>
+        <v>800000</v>
       </c>
       <c r="I146">
         <v>12</v>
@@ -11248,10 +11571,10 @@
         <v>2027-08-01</v>
       </c>
       <c r="L146">
-        <v>780000</v>
+        <v>240000</v>
       </c>
       <c r="M146" t="str">
-        <v>NL phòng 103</v>
+        <v>Quạt phòng 101</v>
       </c>
     </row>
     <row r="147">
@@ -11259,13 +11582,13 @@
         <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B147" t="str">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C147" t="str">
         <v/>
       </c>
       <c r="D147" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E147" t="str">
         <v>NEW</v>
@@ -11277,22 +11600,22 @@
         <v>1</v>
       </c>
       <c r="H147">
-        <v>4500000</v>
+        <v>9200000</v>
       </c>
       <c r="I147">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J147" t="str">
         <v>2026-08-01</v>
       </c>
       <c r="K147" t="str">
-        <v>2027-08-01</v>
+        <v>2028-08-01</v>
       </c>
       <c r="L147">
-        <v>1350000</v>
+        <v>2760000</v>
       </c>
       <c r="M147" t="str">
-        <v>Giường phòng 104</v>
+        <v>ĐH phòng 101</v>
       </c>
     </row>
     <row r="148">
@@ -11300,13 +11623,13 @@
         <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B148" t="str">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C148" t="str">
         <v/>
       </c>
       <c r="D148" t="str">
-        <v>Quạt</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E148" t="str">
         <v>NEW</v>
@@ -11318,7 +11641,7 @@
         <v>1</v>
       </c>
       <c r="H148">
-        <v>800000</v>
+        <v>2600000</v>
       </c>
       <c r="I148">
         <v>12</v>
@@ -11330,10 +11653,10 @@
         <v>2027-08-01</v>
       </c>
       <c r="L148">
-        <v>240000</v>
+        <v>780000</v>
       </c>
       <c r="M148" t="str">
-        <v>Quạt phòng 104</v>
+        <v>NL phòng 101</v>
       </c>
     </row>
     <row r="149">
@@ -11341,13 +11664,13 @@
         <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B149" t="str">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C149" t="str">
         <v/>
       </c>
       <c r="D149" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="E149" t="str">
         <v>NEW</v>
@@ -11359,22 +11682,22 @@
         <v>1</v>
       </c>
       <c r="H149">
-        <v>9200000</v>
+        <v>4500000</v>
       </c>
       <c r="I149">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J149" t="str">
         <v>2026-08-01</v>
       </c>
       <c r="K149" t="str">
-        <v>2028-08-01</v>
+        <v>2027-08-01</v>
       </c>
       <c r="L149">
-        <v>2760000</v>
+        <v>1350000</v>
       </c>
       <c r="M149" t="str">
-        <v>ĐH phòng 104</v>
+        <v>Giường phòng 102</v>
       </c>
     </row>
     <row r="150">
@@ -11382,13 +11705,13 @@
         <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B150" t="str">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C150" t="str">
         <v/>
       </c>
       <c r="D150" t="str">
-        <v>Nóng lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="E150" t="str">
         <v>NEW</v>
@@ -11400,7 +11723,7 @@
         <v>1</v>
       </c>
       <c r="H150">
-        <v>2600000</v>
+        <v>800000</v>
       </c>
       <c r="I150">
         <v>12</v>
@@ -11412,24 +11735,24 @@
         <v>2027-08-01</v>
       </c>
       <c r="L150">
-        <v>780000</v>
+        <v>240000</v>
       </c>
       <c r="M150" t="str">
-        <v>NL phòng 104</v>
+        <v>Quạt phòng 102</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B151" t="str">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C151" t="str">
         <v/>
       </c>
       <c r="D151" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E151" t="str">
         <v>NEW</v>
@@ -11441,36 +11764,36 @@
         <v>1</v>
       </c>
       <c r="H151">
-        <v>4500000</v>
+        <v>9200000</v>
       </c>
       <c r="I151">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J151" t="str">
-        <v>2026-09-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K151" t="str">
-        <v>2027-09-01</v>
+        <v>2028-08-01</v>
       </c>
       <c r="L151">
-        <v>1350000</v>
+        <v>2760000</v>
       </c>
       <c r="M151" t="str">
-        <v>Giường phòng 101</v>
+        <v>ĐH phòng 102</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B152" t="str">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C152" t="str">
         <v/>
       </c>
       <c r="D152" t="str">
-        <v>Quạt</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E152" t="str">
         <v>NEW</v>
@@ -11482,36 +11805,36 @@
         <v>1</v>
       </c>
       <c r="H152">
-        <v>800000</v>
+        <v>2600000</v>
       </c>
       <c r="I152">
         <v>12</v>
       </c>
       <c r="J152" t="str">
-        <v>2026-09-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K152" t="str">
-        <v>2027-09-01</v>
+        <v>2027-08-01</v>
       </c>
       <c r="L152">
-        <v>240000</v>
+        <v>780000</v>
       </c>
       <c r="M152" t="str">
-        <v>Quạt phòng 101</v>
+        <v>NL phòng 102</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B153" t="str">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C153" t="str">
         <v/>
       </c>
       <c r="D153" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="E153" t="str">
         <v>NEW</v>
@@ -11523,36 +11846,36 @@
         <v>1</v>
       </c>
       <c r="H153">
-        <v>9200000</v>
+        <v>4500000</v>
       </c>
       <c r="I153">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J153" t="str">
-        <v>2026-09-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K153" t="str">
-        <v>2028-09-01</v>
+        <v>2027-08-01</v>
       </c>
       <c r="L153">
-        <v>2760000</v>
+        <v>1350000</v>
       </c>
       <c r="M153" t="str">
-        <v>ĐH phòng 101</v>
+        <v>Giường phòng 103</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B154" t="str">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C154" t="str">
         <v/>
       </c>
       <c r="D154" t="str">
-        <v>Nóng lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="E154" t="str">
         <v>NEW</v>
@@ -11564,36 +11887,36 @@
         <v>1</v>
       </c>
       <c r="H154">
-        <v>2600000</v>
+        <v>800000</v>
       </c>
       <c r="I154">
         <v>12</v>
       </c>
       <c r="J154" t="str">
-        <v>2026-09-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K154" t="str">
-        <v>2027-09-01</v>
+        <v>2027-08-01</v>
       </c>
       <c r="L154">
-        <v>780000</v>
+        <v>240000</v>
       </c>
       <c r="M154" t="str">
-        <v>NL phòng 101</v>
+        <v>Quạt phòng 103</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B155" t="str">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C155" t="str">
         <v/>
       </c>
       <c r="D155" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E155" t="str">
         <v>NEW</v>
@@ -11605,36 +11928,36 @@
         <v>1</v>
       </c>
       <c r="H155">
-        <v>4500000</v>
+        <v>9200000</v>
       </c>
       <c r="I155">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J155" t="str">
-        <v>2026-09-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K155" t="str">
-        <v>2027-09-01</v>
+        <v>2028-08-01</v>
       </c>
       <c r="L155">
-        <v>1350000</v>
+        <v>2760000</v>
       </c>
       <c r="M155" t="str">
-        <v>Giường phòng 102</v>
+        <v>ĐH phòng 103</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B156" t="str">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C156" t="str">
         <v/>
       </c>
       <c r="D156" t="str">
-        <v>Quạt</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E156" t="str">
         <v>NEW</v>
@@ -11646,36 +11969,36 @@
         <v>1</v>
       </c>
       <c r="H156">
-        <v>800000</v>
+        <v>2600000</v>
       </c>
       <c r="I156">
         <v>12</v>
       </c>
       <c r="J156" t="str">
-        <v>2026-09-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K156" t="str">
-        <v>2027-09-01</v>
+        <v>2027-08-01</v>
       </c>
       <c r="L156">
-        <v>240000</v>
+        <v>780000</v>
       </c>
       <c r="M156" t="str">
-        <v>Quạt phòng 102</v>
+        <v>NL phòng 103</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B157" t="str">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C157" t="str">
         <v/>
       </c>
       <c r="D157" t="str">
-        <v>Điều hòa</v>
+        <v>Giường</v>
       </c>
       <c r="E157" t="str">
         <v>NEW</v>
@@ -11687,36 +12010,36 @@
         <v>1</v>
       </c>
       <c r="H157">
-        <v>9200000</v>
+        <v>4500000</v>
       </c>
       <c r="I157">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J157" t="str">
-        <v>2026-09-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K157" t="str">
-        <v>2028-09-01</v>
+        <v>2027-08-01</v>
       </c>
       <c r="L157">
-        <v>2760000</v>
+        <v>1350000</v>
       </c>
       <c r="M157" t="str">
-        <v>ĐH phòng 102</v>
+        <v>Giường phòng 104</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B158" t="str">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C158" t="str">
         <v/>
       </c>
       <c r="D158" t="str">
-        <v>Nóng lạnh</v>
+        <v>Quạt</v>
       </c>
       <c r="E158" t="str">
         <v>NEW</v>
@@ -11728,36 +12051,36 @@
         <v>1</v>
       </c>
       <c r="H158">
-        <v>2600000</v>
+        <v>800000</v>
       </c>
       <c r="I158">
         <v>12</v>
       </c>
       <c r="J158" t="str">
-        <v>2026-09-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K158" t="str">
-        <v>2027-09-01</v>
+        <v>2027-08-01</v>
       </c>
       <c r="L158">
-        <v>780000</v>
+        <v>240000</v>
       </c>
       <c r="M158" t="str">
-        <v>NL phòng 102</v>
+        <v>Quạt phòng 104</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B159" t="str">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C159" t="str">
         <v/>
       </c>
       <c r="D159" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E159" t="str">
         <v>NEW</v>
@@ -11769,36 +12092,36 @@
         <v>1</v>
       </c>
       <c r="H159">
-        <v>4500000</v>
+        <v>9200000</v>
       </c>
       <c r="I159">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J159" t="str">
-        <v>2026-09-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K159" t="str">
-        <v>2027-09-01</v>
+        <v>2028-08-01</v>
       </c>
       <c r="L159">
-        <v>1350000</v>
+        <v>2760000</v>
       </c>
       <c r="M159" t="str">
-        <v>Giường phòng 103</v>
+        <v>ĐH phòng 104</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B160" t="str">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C160" t="str">
         <v/>
       </c>
       <c r="D160" t="str">
-        <v>Quạt</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E160" t="str">
         <v>NEW</v>
@@ -11810,36 +12133,36 @@
         <v>1</v>
       </c>
       <c r="H160">
-        <v>800000</v>
+        <v>2600000</v>
       </c>
       <c r="I160">
         <v>12</v>
       </c>
       <c r="J160" t="str">
-        <v>2026-09-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K160" t="str">
-        <v>2027-09-01</v>
+        <v>2027-08-01</v>
       </c>
       <c r="L160">
-        <v>240000</v>
+        <v>780000</v>
       </c>
       <c r="M160" t="str">
-        <v>Quạt phòng 103</v>
+        <v>NL phòng 104</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B161" t="str">
-        <v>103</v>
+        <v/>
       </c>
       <c r="C161" t="str">
-        <v/>
+        <v>KITCHEN</v>
       </c>
       <c r="D161" t="str">
-        <v>Điều hòa</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="E161" t="str">
         <v>NEW</v>
@@ -11851,36 +12174,36 @@
         <v>1</v>
       </c>
       <c r="H161">
-        <v>9200000</v>
+        <v>8000000</v>
       </c>
       <c r="I161">
         <v>24</v>
       </c>
       <c r="J161" t="str">
-        <v>2026-09-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K161" t="str">
-        <v>2028-09-01</v>
+        <v>2028-08-01</v>
       </c>
       <c r="L161">
-        <v>2760000</v>
+        <v>2400000</v>
       </c>
       <c r="M161" t="str">
-        <v>ĐH phòng 103</v>
+        <v>Tủ dùng chung — full NT</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>HD-MTX-47-RENO-RM-FULL</v>
+        <v>HD-MTX-46-RENO-RM-FULL</v>
       </c>
       <c r="B162" t="str">
-        <v>103</v>
+        <v/>
       </c>
       <c r="C162" t="str">
-        <v/>
+        <v>BALCONY</v>
       </c>
       <c r="D162" t="str">
-        <v>Nóng lạnh</v>
+        <v>Máy giặt</v>
       </c>
       <c r="E162" t="str">
         <v>NEW</v>
@@ -11892,22 +12215,22 @@
         <v>1</v>
       </c>
       <c r="H162">
-        <v>2600000</v>
+        <v>9000000</v>
       </c>
       <c r="I162">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J162" t="str">
-        <v>2026-09-01</v>
+        <v>2026-08-01</v>
       </c>
       <c r="K162" t="str">
-        <v>2027-09-01</v>
+        <v>2028-08-01</v>
       </c>
       <c r="L162">
-        <v>780000</v>
+        <v>2700000</v>
       </c>
       <c r="M162" t="str">
-        <v>NL phòng 103</v>
+        <v>Máy giặt dùng chung — full NT</v>
       </c>
     </row>
     <row r="163">
@@ -11915,7 +12238,7 @@
         <v>HD-MTX-47-RENO-RM-FULL</v>
       </c>
       <c r="B163" t="str">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C163" t="str">
         <v/>
@@ -11948,7 +12271,7 @@
         <v>1350000</v>
       </c>
       <c r="M163" t="str">
-        <v>Giường phòng 104</v>
+        <v>Giường phòng 101</v>
       </c>
     </row>
     <row r="164">
@@ -11956,7 +12279,7 @@
         <v>HD-MTX-47-RENO-RM-FULL</v>
       </c>
       <c r="B164" t="str">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C164" t="str">
         <v/>
@@ -11989,7 +12312,7 @@
         <v>240000</v>
       </c>
       <c r="M164" t="str">
-        <v>Quạt phòng 104</v>
+        <v>Quạt phòng 101</v>
       </c>
     </row>
     <row r="165">
@@ -11997,7 +12320,7 @@
         <v>HD-MTX-47-RENO-RM-FULL</v>
       </c>
       <c r="B165" t="str">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C165" t="str">
         <v/>
@@ -12030,7 +12353,7 @@
         <v>2760000</v>
       </c>
       <c r="M165" t="str">
-        <v>ĐH phòng 104</v>
+        <v>ĐH phòng 101</v>
       </c>
     </row>
     <row r="166">
@@ -12038,7 +12361,7 @@
         <v>HD-MTX-47-RENO-RM-FULL</v>
       </c>
       <c r="B166" t="str">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C166" t="str">
         <v/>
@@ -12071,15 +12394,15 @@
         <v>780000</v>
       </c>
       <c r="M166" t="str">
-        <v>NL phòng 104</v>
+        <v>NL phòng 101</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-47-RENO-RM-FULL</v>
       </c>
       <c r="B167" t="str">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C167" t="str">
         <v/>
@@ -12097,30 +12420,30 @@
         <v>1</v>
       </c>
       <c r="H167">
-        <v>4000000</v>
+        <v>4500000</v>
       </c>
       <c r="I167">
         <v>12</v>
       </c>
       <c r="J167" t="str">
-        <v>2026-10-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="K167" t="str">
-        <v>2027-10-01</v>
+        <v>2027-09-01</v>
       </c>
       <c r="L167">
-        <v>1200000</v>
+        <v>1350000</v>
       </c>
       <c r="M167" t="str">
-        <v>NT cơ bản phòng 101</v>
+        <v>Giường phòng 102</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-47-RENO-RM-FULL</v>
       </c>
       <c r="B168" t="str">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C168" t="str">
         <v/>
@@ -12138,30 +12461,30 @@
         <v>1</v>
       </c>
       <c r="H168">
-        <v>750000</v>
+        <v>800000</v>
       </c>
       <c r="I168">
         <v>12</v>
       </c>
       <c r="J168" t="str">
-        <v>2026-10-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="K168" t="str">
-        <v>2027-10-01</v>
+        <v>2027-09-01</v>
       </c>
       <c r="L168">
-        <v>225000</v>
+        <v>240000</v>
       </c>
       <c r="M168" t="str">
-        <v>Quạt phòng 101</v>
+        <v>Quạt phòng 102</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-47-RENO-RM-FULL</v>
       </c>
       <c r="B169" t="str">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C169" t="str">
         <v/>
@@ -12179,27 +12502,27 @@
         <v>1</v>
       </c>
       <c r="H169">
-        <v>8500000</v>
+        <v>9200000</v>
       </c>
       <c r="I169">
         <v>24</v>
       </c>
       <c r="J169" t="str">
-        <v>2026-10-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="K169" t="str">
-        <v>2028-10-01</v>
+        <v>2028-09-01</v>
       </c>
       <c r="L169">
-        <v>2550000</v>
+        <v>2760000</v>
       </c>
       <c r="M169" t="str">
-        <v>ĐH phòng 101</v>
+        <v>ĐH phòng 102</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-47-RENO-RM-FULL</v>
       </c>
       <c r="B170" t="str">
         <v>102</v>
@@ -12208,7 +12531,7 @@
         <v/>
       </c>
       <c r="D170" t="str">
-        <v>Giường</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E170" t="str">
         <v>NEW</v>
@@ -12220,36 +12543,36 @@
         <v>1</v>
       </c>
       <c r="H170">
-        <v>4000000</v>
+        <v>2600000</v>
       </c>
       <c r="I170">
         <v>12</v>
       </c>
       <c r="J170" t="str">
-        <v>2026-10-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="K170" t="str">
-        <v>2027-10-01</v>
+        <v>2027-09-01</v>
       </c>
       <c r="L170">
-        <v>1200000</v>
+        <v>780000</v>
       </c>
       <c r="M170" t="str">
-        <v>NT cơ bản phòng 102</v>
+        <v>NL phòng 102</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-47-RENO-RM-FULL</v>
       </c>
       <c r="B171" t="str">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C171" t="str">
         <v/>
       </c>
       <c r="D171" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="E171" t="str">
         <v>NEW</v>
@@ -12261,27 +12584,27 @@
         <v>1</v>
       </c>
       <c r="H171">
-        <v>750000</v>
+        <v>4500000</v>
       </c>
       <c r="I171">
         <v>12</v>
       </c>
       <c r="J171" t="str">
-        <v>2026-10-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="K171" t="str">
-        <v>2027-10-01</v>
+        <v>2027-09-01</v>
       </c>
       <c r="L171">
-        <v>225000</v>
+        <v>1350000</v>
       </c>
       <c r="M171" t="str">
-        <v>Quạt phòng 102</v>
+        <v>Giường phòng 103</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-47-RENO-RM-FULL</v>
       </c>
       <c r="B172" t="str">
         <v>103</v>
@@ -12290,7 +12613,7 @@
         <v/>
       </c>
       <c r="D172" t="str">
-        <v>Giường</v>
+        <v>Quạt</v>
       </c>
       <c r="E172" t="str">
         <v>NEW</v>
@@ -12302,27 +12625,27 @@
         <v>1</v>
       </c>
       <c r="H172">
-        <v>4000000</v>
+        <v>800000</v>
       </c>
       <c r="I172">
         <v>12</v>
       </c>
       <c r="J172" t="str">
-        <v>2026-10-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="K172" t="str">
-        <v>2027-10-01</v>
+        <v>2027-09-01</v>
       </c>
       <c r="L172">
-        <v>1200000</v>
+        <v>240000</v>
       </c>
       <c r="M172" t="str">
-        <v>NT cơ bản phòng 103</v>
+        <v>Quạt phòng 103</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-47-RENO-RM-FULL</v>
       </c>
       <c r="B173" t="str">
         <v>103</v>
@@ -12331,7 +12654,7 @@
         <v/>
       </c>
       <c r="D173" t="str">
-        <v>Quạt</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E173" t="str">
         <v>NEW</v>
@@ -12343,27 +12666,27 @@
         <v>1</v>
       </c>
       <c r="H173">
-        <v>750000</v>
+        <v>9200000</v>
       </c>
       <c r="I173">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J173" t="str">
-        <v>2026-10-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="K173" t="str">
-        <v>2027-10-01</v>
+        <v>2028-09-01</v>
       </c>
       <c r="L173">
-        <v>225000</v>
+        <v>2760000</v>
       </c>
       <c r="M173" t="str">
-        <v>Quạt phòng 103</v>
+        <v>ĐH phòng 103</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-47-RENO-RM-FULL</v>
       </c>
       <c r="B174" t="str">
         <v>103</v>
@@ -12372,7 +12695,7 @@
         <v/>
       </c>
       <c r="D174" t="str">
-        <v>Điều hòa</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E174" t="str">
         <v>NEW</v>
@@ -12384,30 +12707,30 @@
         <v>1</v>
       </c>
       <c r="H174">
-        <v>8500000</v>
+        <v>2600000</v>
       </c>
       <c r="I174">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J174" t="str">
-        <v>2026-10-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="K174" t="str">
-        <v>2028-10-01</v>
+        <v>2027-09-01</v>
       </c>
       <c r="L174">
-        <v>2550000</v>
+        <v>780000</v>
       </c>
       <c r="M174" t="str">
-        <v>ĐH phòng 103</v>
+        <v>NL phòng 103</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-47-RENO-RM-FULL</v>
       </c>
       <c r="B175" t="str">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C175" t="str">
         <v/>
@@ -12425,30 +12748,30 @@
         <v>1</v>
       </c>
       <c r="H175">
-        <v>4000000</v>
+        <v>4500000</v>
       </c>
       <c r="I175">
         <v>12</v>
       </c>
       <c r="J175" t="str">
-        <v>2026-03-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="K175" t="str">
-        <v>2027-03-01</v>
+        <v>2027-09-01</v>
       </c>
       <c r="L175">
-        <v>1200000</v>
+        <v>1350000</v>
       </c>
       <c r="M175" t="str">
-        <v>NT cơ bản phòng 101</v>
+        <v>Giường phòng 104</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-47-RENO-RM-FULL</v>
       </c>
       <c r="B176" t="str">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C176" t="str">
         <v/>
@@ -12466,30 +12789,30 @@
         <v>1</v>
       </c>
       <c r="H176">
-        <v>750000</v>
+        <v>800000</v>
       </c>
       <c r="I176">
         <v>12</v>
       </c>
       <c r="J176" t="str">
-        <v>2026-03-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="K176" t="str">
-        <v>2027-03-01</v>
+        <v>2027-09-01</v>
       </c>
       <c r="L176">
-        <v>225000</v>
+        <v>240000</v>
       </c>
       <c r="M176" t="str">
-        <v>Quạt phòng 101</v>
+        <v>Quạt phòng 104</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-47-RENO-RM-FULL</v>
       </c>
       <c r="B177" t="str">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C177" t="str">
         <v/>
@@ -12507,36 +12830,36 @@
         <v>1</v>
       </c>
       <c r="H177">
-        <v>8500000</v>
+        <v>9200000</v>
       </c>
       <c r="I177">
         <v>24</v>
       </c>
       <c r="J177" t="str">
-        <v>2026-03-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="K177" t="str">
-        <v>2028-03-01</v>
+        <v>2028-09-01</v>
       </c>
       <c r="L177">
-        <v>2550000</v>
+        <v>2760000</v>
       </c>
       <c r="M177" t="str">
-        <v>ĐH phòng 101</v>
+        <v>ĐH phòng 104</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-47-RENO-RM-FULL</v>
       </c>
       <c r="B178" t="str">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C178" t="str">
         <v/>
       </c>
       <c r="D178" t="str">
-        <v>Giường</v>
+        <v>Nóng lạnh</v>
       </c>
       <c r="E178" t="str">
         <v>NEW</v>
@@ -12548,36 +12871,36 @@
         <v>1</v>
       </c>
       <c r="H178">
-        <v>4000000</v>
+        <v>2600000</v>
       </c>
       <c r="I178">
         <v>12</v>
       </c>
       <c r="J178" t="str">
-        <v>2026-03-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="K178" t="str">
-        <v>2027-03-01</v>
+        <v>2027-09-01</v>
       </c>
       <c r="L178">
-        <v>1200000</v>
+        <v>780000</v>
       </c>
       <c r="M178" t="str">
-        <v>NT cơ bản phòng 102</v>
+        <v>NL phòng 104</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-47-RENO-RM-FULL</v>
       </c>
       <c r="B179" t="str">
-        <v>102</v>
+        <v/>
       </c>
       <c r="C179" t="str">
-        <v/>
+        <v>KITCHEN</v>
       </c>
       <c r="D179" t="str">
-        <v>Quạt</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="E179" t="str">
         <v>NEW</v>
@@ -12589,36 +12912,36 @@
         <v>1</v>
       </c>
       <c r="H179">
-        <v>750000</v>
+        <v>8000000</v>
       </c>
       <c r="I179">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J179" t="str">
-        <v>2026-03-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="K179" t="str">
-        <v>2027-03-01</v>
+        <v>2028-09-01</v>
       </c>
       <c r="L179">
-        <v>225000</v>
+        <v>2400000</v>
       </c>
       <c r="M179" t="str">
-        <v>Quạt phòng 102</v>
+        <v>Tủ dùng chung — full NT</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-47-RENO-RM-FULL</v>
       </c>
       <c r="B180" t="str">
-        <v>103</v>
+        <v/>
       </c>
       <c r="C180" t="str">
-        <v/>
+        <v>BALCONY</v>
       </c>
       <c r="D180" t="str">
-        <v>Giường</v>
+        <v>Máy giặt</v>
       </c>
       <c r="E180" t="str">
         <v>NEW</v>
@@ -12630,36 +12953,36 @@
         <v>1</v>
       </c>
       <c r="H180">
-        <v>4000000</v>
+        <v>9000000</v>
       </c>
       <c r="I180">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J180" t="str">
-        <v>2026-03-01</v>
+        <v>2026-09-01</v>
       </c>
       <c r="K180" t="str">
-        <v>2027-03-01</v>
+        <v>2028-09-01</v>
       </c>
       <c r="L180">
-        <v>1200000</v>
+        <v>2700000</v>
       </c>
       <c r="M180" t="str">
-        <v>NT cơ bản phòng 103</v>
+        <v>Máy giặt dùng chung — full NT</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
       </c>
       <c r="B181" t="str">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C181" t="str">
         <v/>
       </c>
       <c r="D181" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="E181" t="str">
         <v>NEW</v>
@@ -12671,36 +12994,36 @@
         <v>1</v>
       </c>
       <c r="H181">
-        <v>750000</v>
+        <v>4000000</v>
       </c>
       <c r="I181">
         <v>12</v>
       </c>
       <c r="J181" t="str">
-        <v>2026-03-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="K181" t="str">
-        <v>2027-03-01</v>
+        <v>2027-10-01</v>
       </c>
       <c r="L181">
-        <v>225000</v>
+        <v>1200000</v>
       </c>
       <c r="M181" t="str">
-        <v>Quạt phòng 103</v>
+        <v>Giường phòng 101 — NT cơ bản</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
       </c>
       <c r="B182" t="str">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C182" t="str">
         <v/>
       </c>
       <c r="D182" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="E182" t="str">
         <v>NEW</v>
@@ -12712,27 +13035,27 @@
         <v>1</v>
       </c>
       <c r="H182">
-        <v>8500000</v>
+        <v>750000</v>
       </c>
       <c r="I182">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J182" t="str">
-        <v>2026-03-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="K182" t="str">
-        <v>2028-03-01</v>
+        <v>2027-10-01</v>
       </c>
       <c r="L182">
-        <v>2550000</v>
+        <v>225000</v>
       </c>
       <c r="M182" t="str">
-        <v>ĐH phòng 103</v>
+        <v>Quạt phòng 101</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
       </c>
       <c r="B183" t="str">
         <v>101</v>
@@ -12741,7 +13064,7 @@
         <v/>
       </c>
       <c r="D183" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E183" t="str">
         <v>NEW</v>
@@ -12753,36 +13076,36 @@
         <v>1</v>
       </c>
       <c r="H183">
-        <v>4000000</v>
+        <v>8500000</v>
       </c>
       <c r="I183">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J183" t="str">
-        <v>2026-04-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="K183" t="str">
-        <v>2027-04-01</v>
+        <v>2028-10-01</v>
       </c>
       <c r="L183">
-        <v>1200000</v>
+        <v>2550000</v>
       </c>
       <c r="M183" t="str">
-        <v>NT cơ bản phòng 101</v>
+        <v>ĐH phòng 101</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
       </c>
       <c r="B184" t="str">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C184" t="str">
         <v/>
       </c>
       <c r="D184" t="str">
-        <v>Quạt</v>
+        <v>Giường</v>
       </c>
       <c r="E184" t="str">
         <v>NEW</v>
@@ -12794,36 +13117,36 @@
         <v>1</v>
       </c>
       <c r="H184">
-        <v>750000</v>
+        <v>4000000</v>
       </c>
       <c r="I184">
         <v>12</v>
       </c>
       <c r="J184" t="str">
-        <v>2026-04-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="K184" t="str">
-        <v>2027-04-01</v>
+        <v>2027-10-01</v>
       </c>
       <c r="L184">
-        <v>225000</v>
+        <v>1200000</v>
       </c>
       <c r="M184" t="str">
-        <v>Quạt phòng 101</v>
+        <v>Giường phòng 102 — NT cơ bản</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
       </c>
       <c r="B185" t="str">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C185" t="str">
         <v/>
       </c>
       <c r="D185" t="str">
-        <v>Điều hòa</v>
+        <v>Quạt</v>
       </c>
       <c r="E185" t="str">
         <v>NEW</v>
@@ -12835,30 +13158,30 @@
         <v>1</v>
       </c>
       <c r="H185">
-        <v>8500000</v>
+        <v>750000</v>
       </c>
       <c r="I185">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J185" t="str">
-        <v>2026-04-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="K185" t="str">
-        <v>2028-04-01</v>
+        <v>2027-10-01</v>
       </c>
       <c r="L185">
-        <v>2550000</v>
+        <v>225000</v>
       </c>
       <c r="M185" t="str">
-        <v>ĐH phòng 101</v>
+        <v>Quạt phòng 102</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
       </c>
       <c r="B186" t="str">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C186" t="str">
         <v/>
@@ -12882,24 +13205,24 @@
         <v>12</v>
       </c>
       <c r="J186" t="str">
-        <v>2026-04-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="K186" t="str">
-        <v>2027-04-01</v>
+        <v>2027-10-01</v>
       </c>
       <c r="L186">
         <v>1200000</v>
       </c>
       <c r="M186" t="str">
-        <v>NT cơ bản phòng 102</v>
+        <v>Giường phòng 103 — NT cơ bản</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
       </c>
       <c r="B187" t="str">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C187" t="str">
         <v/>
@@ -12923,21 +13246,21 @@
         <v>12</v>
       </c>
       <c r="J187" t="str">
-        <v>2026-04-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="K187" t="str">
-        <v>2027-04-01</v>
+        <v>2027-10-01</v>
       </c>
       <c r="L187">
         <v>225000</v>
       </c>
       <c r="M187" t="str">
-        <v>Quạt phòng 102</v>
+        <v>Quạt phòng 103</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
       </c>
       <c r="B188" t="str">
         <v>103</v>
@@ -12946,7 +13269,7 @@
         <v/>
       </c>
       <c r="D188" t="str">
-        <v>Giường</v>
+        <v>Điều hòa</v>
       </c>
       <c r="E188" t="str">
         <v>NEW</v>
@@ -12958,36 +13281,36 @@
         <v>1</v>
       </c>
       <c r="H188">
-        <v>4000000</v>
+        <v>8500000</v>
       </c>
       <c r="I188">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J188" t="str">
-        <v>2026-04-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="K188" t="str">
-        <v>2027-04-01</v>
+        <v>2028-10-01</v>
       </c>
       <c r="L188">
-        <v>1200000</v>
+        <v>2550000</v>
       </c>
       <c r="M188" t="str">
-        <v>NT cơ bản phòng 103</v>
+        <v>ĐH phòng 103</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+        <v>HD-MTX-48-RENO-RM-HO-BUY</v>
       </c>
       <c r="B189" t="str">
-        <v>103</v>
+        <v/>
       </c>
       <c r="C189" t="str">
-        <v/>
+        <v>KITCHEN</v>
       </c>
       <c r="D189" t="str">
-        <v>Quạt</v>
+        <v>Tủ lạnh</v>
       </c>
       <c r="E189" t="str">
         <v>NEW</v>
@@ -12999,68 +13322,765 @@
         <v>1</v>
       </c>
       <c r="H189">
-        <v>750000</v>
+        <v>6500000</v>
       </c>
       <c r="I189">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J189" t="str">
-        <v>2026-04-01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="K189" t="str">
-        <v>2027-04-01</v>
+        <v>2028-10-01</v>
       </c>
       <c r="L189">
-        <v>225000</v>
+        <v>1950000</v>
       </c>
       <c r="M189" t="str">
-        <v>Quạt phòng 103</v>
+        <v>Tủ dùng chung — NT cơ bản</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
+        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B190" t="str">
+        <v>101</v>
+      </c>
+      <c r="C190" t="str">
+        <v/>
+      </c>
+      <c r="D190" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E190" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F190" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G190">
+        <v>1</v>
+      </c>
+      <c r="H190">
+        <v>4000000</v>
+      </c>
+      <c r="I190">
+        <v>12</v>
+      </c>
+      <c r="J190" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="K190" t="str">
+        <v>2027-03-01</v>
+      </c>
+      <c r="L190">
+        <v>1200000</v>
+      </c>
+      <c r="M190" t="str">
+        <v>Giường phòng 101 — NT cơ bản</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B191" t="str">
+        <v>101</v>
+      </c>
+      <c r="C191" t="str">
+        <v/>
+      </c>
+      <c r="D191" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E191" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F191" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G191">
+        <v>1</v>
+      </c>
+      <c r="H191">
+        <v>750000</v>
+      </c>
+      <c r="I191">
+        <v>12</v>
+      </c>
+      <c r="J191" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="K191" t="str">
+        <v>2027-03-01</v>
+      </c>
+      <c r="L191">
+        <v>225000</v>
+      </c>
+      <c r="M191" t="str">
+        <v>Quạt phòng 101</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B192" t="str">
+        <v>101</v>
+      </c>
+      <c r="C192" t="str">
+        <v/>
+      </c>
+      <c r="D192" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="E192" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F192" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G192">
+        <v>1</v>
+      </c>
+      <c r="H192">
+        <v>8500000</v>
+      </c>
+      <c r="I192">
+        <v>24</v>
+      </c>
+      <c r="J192" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="K192" t="str">
+        <v>2028-03-01</v>
+      </c>
+      <c r="L192">
+        <v>2550000</v>
+      </c>
+      <c r="M192" t="str">
+        <v>ĐH phòng 101</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B193" t="str">
+        <v>102</v>
+      </c>
+      <c r="C193" t="str">
+        <v/>
+      </c>
+      <c r="D193" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E193" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F193" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G193">
+        <v>1</v>
+      </c>
+      <c r="H193">
+        <v>4000000</v>
+      </c>
+      <c r="I193">
+        <v>12</v>
+      </c>
+      <c r="J193" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="K193" t="str">
+        <v>2027-03-01</v>
+      </c>
+      <c r="L193">
+        <v>1200000</v>
+      </c>
+      <c r="M193" t="str">
+        <v>Giường phòng 102 — NT cơ bản</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B194" t="str">
+        <v>102</v>
+      </c>
+      <c r="C194" t="str">
+        <v/>
+      </c>
+      <c r="D194" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E194" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F194" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G194">
+        <v>1</v>
+      </c>
+      <c r="H194">
+        <v>750000</v>
+      </c>
+      <c r="I194">
+        <v>12</v>
+      </c>
+      <c r="J194" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="K194" t="str">
+        <v>2027-03-01</v>
+      </c>
+      <c r="L194">
+        <v>225000</v>
+      </c>
+      <c r="M194" t="str">
+        <v>Quạt phòng 102</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B195" t="str">
+        <v>103</v>
+      </c>
+      <c r="C195" t="str">
+        <v/>
+      </c>
+      <c r="D195" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E195" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F195" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G195">
+        <v>1</v>
+      </c>
+      <c r="H195">
+        <v>4000000</v>
+      </c>
+      <c r="I195">
+        <v>12</v>
+      </c>
+      <c r="J195" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="K195" t="str">
+        <v>2027-03-01</v>
+      </c>
+      <c r="L195">
+        <v>1200000</v>
+      </c>
+      <c r="M195" t="str">
+        <v>Giường phòng 103 — NT cơ bản</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B196" t="str">
+        <v>103</v>
+      </c>
+      <c r="C196" t="str">
+        <v/>
+      </c>
+      <c r="D196" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E196" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F196" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G196">
+        <v>1</v>
+      </c>
+      <c r="H196">
+        <v>750000</v>
+      </c>
+      <c r="I196">
+        <v>12</v>
+      </c>
+      <c r="J196" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="K196" t="str">
+        <v>2027-03-01</v>
+      </c>
+      <c r="L196">
+        <v>225000</v>
+      </c>
+      <c r="M196" t="str">
+        <v>Quạt phòng 103</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B197" t="str">
+        <v>103</v>
+      </c>
+      <c r="C197" t="str">
+        <v/>
+      </c>
+      <c r="D197" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="E197" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F197" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G197">
+        <v>1</v>
+      </c>
+      <c r="H197">
+        <v>8500000</v>
+      </c>
+      <c r="I197">
+        <v>24</v>
+      </c>
+      <c r="J197" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="K197" t="str">
+        <v>2028-03-01</v>
+      </c>
+      <c r="L197">
+        <v>2550000</v>
+      </c>
+      <c r="M197" t="str">
+        <v>ĐH phòng 103</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>HD-MTX-49-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B198" t="str">
+        <v/>
+      </c>
+      <c r="C198" t="str">
+        <v>KITCHEN</v>
+      </c>
+      <c r="D198" t="str">
+        <v>Tủ lạnh</v>
+      </c>
+      <c r="E198" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F198" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G198">
+        <v>1</v>
+      </c>
+      <c r="H198">
+        <v>6500000</v>
+      </c>
+      <c r="I198">
+        <v>24</v>
+      </c>
+      <c r="J198" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="K198" t="str">
+        <v>2028-03-01</v>
+      </c>
+      <c r="L198">
+        <v>1950000</v>
+      </c>
+      <c r="M198" t="str">
+        <v>Tủ dùng chung — NT cơ bản</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
         <v>HD-MTX-50-RENO-RM-HO-BUY</v>
       </c>
-      <c r="B190" t="str">
+      <c r="B199" t="str">
+        <v>101</v>
+      </c>
+      <c r="C199" t="str">
+        <v/>
+      </c>
+      <c r="D199" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E199" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F199" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G199">
+        <v>1</v>
+      </c>
+      <c r="H199">
+        <v>4000000</v>
+      </c>
+      <c r="I199">
+        <v>12</v>
+      </c>
+      <c r="J199" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="K199" t="str">
+        <v>2027-04-01</v>
+      </c>
+      <c r="L199">
+        <v>1200000</v>
+      </c>
+      <c r="M199" t="str">
+        <v>Giường phòng 101 — NT cơ bản</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B200" t="str">
+        <v>101</v>
+      </c>
+      <c r="C200" t="str">
+        <v/>
+      </c>
+      <c r="D200" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E200" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F200" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G200">
+        <v>1</v>
+      </c>
+      <c r="H200">
+        <v>750000</v>
+      </c>
+      <c r="I200">
+        <v>12</v>
+      </c>
+      <c r="J200" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="K200" t="str">
+        <v>2027-04-01</v>
+      </c>
+      <c r="L200">
+        <v>225000</v>
+      </c>
+      <c r="M200" t="str">
+        <v>Quạt phòng 101</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B201" t="str">
+        <v>101</v>
+      </c>
+      <c r="C201" t="str">
+        <v/>
+      </c>
+      <c r="D201" t="str">
+        <v>Điều hòa</v>
+      </c>
+      <c r="E201" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F201" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G201">
+        <v>1</v>
+      </c>
+      <c r="H201">
+        <v>8500000</v>
+      </c>
+      <c r="I201">
+        <v>24</v>
+      </c>
+      <c r="J201" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="K201" t="str">
+        <v>2028-04-01</v>
+      </c>
+      <c r="L201">
+        <v>2550000</v>
+      </c>
+      <c r="M201" t="str">
+        <v>ĐH phòng 101</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B202" t="str">
+        <v>102</v>
+      </c>
+      <c r="C202" t="str">
+        <v/>
+      </c>
+      <c r="D202" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E202" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F202" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G202">
+        <v>1</v>
+      </c>
+      <c r="H202">
+        <v>4000000</v>
+      </c>
+      <c r="I202">
+        <v>12</v>
+      </c>
+      <c r="J202" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="K202" t="str">
+        <v>2027-04-01</v>
+      </c>
+      <c r="L202">
+        <v>1200000</v>
+      </c>
+      <c r="M202" t="str">
+        <v>Giường phòng 102 — NT cơ bản</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B203" t="str">
+        <v>102</v>
+      </c>
+      <c r="C203" t="str">
+        <v/>
+      </c>
+      <c r="D203" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E203" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F203" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G203">
+        <v>1</v>
+      </c>
+      <c r="H203">
+        <v>750000</v>
+      </c>
+      <c r="I203">
+        <v>12</v>
+      </c>
+      <c r="J203" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="K203" t="str">
+        <v>2027-04-01</v>
+      </c>
+      <c r="L203">
+        <v>225000</v>
+      </c>
+      <c r="M203" t="str">
+        <v>Quạt phòng 102</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B204" t="str">
         <v>103</v>
       </c>
-      <c r="C190" t="str">
-        <v/>
-      </c>
-      <c r="D190" t="str">
+      <c r="C204" t="str">
+        <v/>
+      </c>
+      <c r="D204" t="str">
+        <v>Giường</v>
+      </c>
+      <c r="E204" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F204" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G204">
+        <v>1</v>
+      </c>
+      <c r="H204">
+        <v>4000000</v>
+      </c>
+      <c r="I204">
+        <v>12</v>
+      </c>
+      <c r="J204" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="K204" t="str">
+        <v>2027-04-01</v>
+      </c>
+      <c r="L204">
+        <v>1200000</v>
+      </c>
+      <c r="M204" t="str">
+        <v>Giường phòng 103 — NT cơ bản</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B205" t="str">
+        <v>103</v>
+      </c>
+      <c r="C205" t="str">
+        <v/>
+      </c>
+      <c r="D205" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E205" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F205" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G205">
+        <v>1</v>
+      </c>
+      <c r="H205">
+        <v>750000</v>
+      </c>
+      <c r="I205">
+        <v>12</v>
+      </c>
+      <c r="J205" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="K205" t="str">
+        <v>2027-04-01</v>
+      </c>
+      <c r="L205">
+        <v>225000</v>
+      </c>
+      <c r="M205" t="str">
+        <v>Quạt phòng 103</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B206" t="str">
+        <v>103</v>
+      </c>
+      <c r="C206" t="str">
+        <v/>
+      </c>
+      <c r="D206" t="str">
         <v>Điều hòa</v>
       </c>
-      <c r="E190" t="str">
-        <v>NEW</v>
-      </c>
-      <c r="F190" t="str">
-        <v>THEM_MOI</v>
-      </c>
-      <c r="G190">
-        <v>1</v>
-      </c>
-      <c r="H190">
+      <c r="E206" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F206" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G206">
+        <v>1</v>
+      </c>
+      <c r="H206">
         <v>8500000</v>
       </c>
-      <c r="I190">
+      <c r="I206">
         <v>24</v>
       </c>
-      <c r="J190" t="str">
+      <c r="J206" t="str">
         <v>2026-04-01</v>
       </c>
-      <c r="K190" t="str">
+      <c r="K206" t="str">
         <v>2028-04-01</v>
       </c>
-      <c r="L190">
+      <c r="L206">
         <v>2550000</v>
       </c>
-      <c r="M190" t="str">
+      <c r="M206" t="str">
         <v>ĐH phòng 103</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>HD-MTX-50-RENO-RM-HO-BUY</v>
+      </c>
+      <c r="B207" t="str">
+        <v/>
+      </c>
+      <c r="C207" t="str">
+        <v>KITCHEN</v>
+      </c>
+      <c r="D207" t="str">
+        <v>Tủ lạnh</v>
+      </c>
+      <c r="E207" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="F207" t="str">
+        <v>THEM_MOI</v>
+      </c>
+      <c r="G207">
+        <v>1</v>
+      </c>
+      <c r="H207">
+        <v>6500000</v>
+      </c>
+      <c r="I207">
+        <v>24</v>
+      </c>
+      <c r="J207" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="K207" t="str">
+        <v>2028-04-01</v>
+      </c>
+      <c r="L207">
+        <v>1950000</v>
+      </c>
+      <c r="M207" t="str">
+        <v>Tủ dùng chung — NT cơ bản</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M190"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M207"/>
   </ignoredErrors>
 </worksheet>
 </file>